--- a/evaluation_results.xlsx
+++ b/evaluation_results.xlsx
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +35,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -46,21 +43,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -426,91 +414,106 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q50"/>
+  <dimension ref="A1:T95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>input</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>source_file_type</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>text_case_category</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>security_input</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>family_query_to_es</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
         <is>
           <t>expected_family</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>predicted_family</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>family_correct</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>family_topk_correct</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>family_rank</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
         <is>
           <t>expected_security</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>predicted_family</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>predicted_security</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>family_correct</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>family_topk_correct</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>family_rank</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>security_correct</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>security_topk_correct</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>security_rank</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>family_score</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>security_score</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
         <is>
           <t>top_family_matches</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>top_security_matches</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>matched_flag</t>
         </is>
@@ -534,63 +537,76 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>Events Buyer T/L</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>events buyer</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>360DG</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>360DG</t>
+        </is>
+      </c>
+      <c r="H2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="inlineStr">
         <is>
           <t>360DG (Term Loan)</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Marketplace Events</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Marketplace Events (USD Term Loan)</t>
-        </is>
-      </c>
-      <c r="H2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I2" t="b">
-        <v>1</v>
-      </c>
-      <c r="J2" t="n">
-        <v>2</v>
-      </c>
-      <c r="K2" t="b">
-        <v>0</v>
-      </c>
-      <c r="L2" t="b">
-        <v>1</v>
-      </c>
-      <c r="M2" t="n">
-        <v>3</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0.9176</v>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>Marketplace Events | 360DG | APRA | Watchtower Buyer | APHIX</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>Marketplace Events (USD Term Loan) | Marketplace Events (DDTL) | 360DG (Term Loan) | 360DG (DDTL B) | 360DG (DDTL A)</t>
-        </is>
-      </c>
-      <c r="Q2" t="b">
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>360DG (Term Loan)</t>
+        </is>
+      </c>
+      <c r="M2" t="b">
+        <v>1</v>
+      </c>
+      <c r="N2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.9293</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>263.8432</v>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>360DG | Watchtower Buyer | Marketplace Events | APRA | APHIX</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>360DG (Term Loan) | 360DG (DDTL B) | 360DG (DDTL A) | 360DG (Revolver) | 360DG (Common Equity)</t>
+        </is>
+      </c>
+      <c r="T2" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Burgess Point Purchaser Corporation</t>
+          <t>48forty Intermediate Holdings, Inc.</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -600,27 +616,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Company Match</t>
+          <t>Security Match</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>BBB Industries</t>
+          <t>48Forty Intermediate Holdings C/S</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>BBB Industries (First Lien Term Loan)</t>
+          <t>48forty intermediate holdings</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>BBB Industries</t>
+          <t>48Forty</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>BBB Industries (First Lien Term Loan)</t>
+          <t>48Forty</t>
         </is>
       </c>
       <c r="H3" t="b">
@@ -632,36 +648,49 @@
       <c r="J3" t="n">
         <v>1</v>
       </c>
-      <c r="K3" t="b">
-        <v>1</v>
-      </c>
-      <c r="L3" t="b">
-        <v>1</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0.9744</v>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>BBB Industries | STG Logistics | Adweek | Aspect Software | Health-E Commerce</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>BBB Industries (First Lien Term Loan) | BBB Industries (Second Lien Term Loan) | BBB Industries (Common Equity) | STG (TL) | Adweek (Term Loan)</t>
-        </is>
-      </c>
-      <c r="Q3" t="b">
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>48Forty (Common Equity)</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>48Forty (Common Equity)</t>
+        </is>
+      </c>
+      <c r="M3" t="b">
+        <v>1</v>
+      </c>
+      <c r="N3" t="b">
+        <v>1</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>286.0734</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>48Forty | Smartronix / Trident | Altamira | Douglas | Engine &amp; Transmission Exchange</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>48Forty (Common Equity) | 48Forty (Term Loan) | Smartronix / Trident (TL) | 48Forty (DDTL) | Altamira (Common Equity)</t>
+        </is>
+      </c>
+      <c r="T3" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BLC Holding Company, Inc.</t>
+          <t>Ad.net Acquisition, LLC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -671,27 +700,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Company Match</t>
+          <t>Security Match</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Bland Landscaping</t>
+          <t>Ad.net Acquisition T/L</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bland Landscaping (DDTL)</t>
+          <t>ad net acquisition</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bland Landscaping</t>
+          <t>Ad.net</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bland Landscaping (DDTL)</t>
+          <t>Ad.net</t>
         </is>
       </c>
       <c r="H4" t="b">
@@ -703,36 +732,49 @@
       <c r="J4" t="n">
         <v>1</v>
       </c>
-      <c r="K4" t="b">
-        <v>1</v>
-      </c>
-      <c r="L4" t="b">
-        <v>1</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0.9187</v>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Bland Landscaping</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Bland Landscaping (DDTL) | Bland Landscaping (Revolver) | Bland Landscaping (Term Loan)</t>
-        </is>
-      </c>
-      <c r="Q4" t="b">
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Ad.net (Term Loan)</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Ad.net (Term Loan)</t>
+        </is>
+      </c>
+      <c r="M4" t="b">
+        <v>1</v>
+      </c>
+      <c r="N4" t="b">
+        <v>1</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>463.4119</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Ad.net | Arcfield | C5MI | Duggal Visual Solutions | GCOM</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>Ad.net (Term Loan) | Ad.net (Revolver) | Ad.net (Common Equity) | Ad.net (Preferred Equity) | Arcfield (Term Loan)</t>
+        </is>
+      </c>
+      <c r="T4" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Aegis Technologies Group, LLC, The</t>
+          <t>Aechelon Technology Inc.</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -742,27 +784,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Company Match</t>
+          <t>Security Match</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>BlueHalo</t>
+          <t>Aechelon Technology  T/L</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>BlueHalo (Term Loan)</t>
+          <t>aechelon technology</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>BlueHalo</t>
+          <t>Aechelon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>BlueHalo (Term Loan)</t>
+          <t>Aechelon</t>
         </is>
       </c>
       <c r="H5" t="b">
@@ -774,36 +816,49 @@
       <c r="J5" t="n">
         <v>1</v>
       </c>
-      <c r="K5" t="b">
-        <v>1</v>
-      </c>
-      <c r="L5" t="b">
-        <v>1</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0.9520999999999999</v>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>BlueHalo | API Technologies | Altamira | Nuvei | Beta+</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>BlueHalo (Term Loan) | API Technologies (TL) | API Technologies (Revolver) | Altamira (Common Equity) | Altamira (TL)</t>
-        </is>
-      </c>
-      <c r="Q5" t="b">
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Aechelon (Term Loan)</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Aechelon (Term Loan)</t>
+        </is>
+      </c>
+      <c r="M5" t="b">
+        <v>1</v>
+      </c>
+      <c r="N5" t="b">
+        <v>1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>425.9401</v>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Aechelon | Intellectual Technology | Sabel Systems</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>Aechelon (Term Loan) | Aechelon (Revolver) | Aechelon (Common Equity) | Intellectual Technology, Inc. (TL) | Sabel Systems (Term Loan)</t>
+        </is>
+      </c>
+      <c r="T5" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Lightspeed Buyer, Inc.</t>
+          <t>AFC-Dell Holding Corp.</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -813,27 +868,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Company Match</t>
+          <t>Company Knowledge Match</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Centauri Health</t>
+          <t>AFC-Dell Holding DD T/L (12/23)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Centauri Health (Revolver)</t>
+          <t>afc dell holding</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Centauri Health</t>
+          <t>AFC Acquisitions</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Centauri Health (TL)</t>
+          <t>AFC Acquisitions</t>
         </is>
       </c>
       <c r="H6" t="b">
@@ -845,36 +900,49 @@
       <c r="J6" t="n">
         <v>1</v>
       </c>
-      <c r="K6" t="b">
-        <v>0</v>
-      </c>
-      <c r="L6" t="b">
-        <v>1</v>
-      </c>
-      <c r="M6" t="n">
-        <v>3</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0.9392</v>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>Centauri Health | Watchtower Buyer | APHIX | Carisk Partners | Connatix</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Centauri Health (TL) | Centauri Health (DDTL) | Centauri Health (Revolver) | Watchtower Buyer (TL) | Watchtower Buyer (DDTL)</t>
-        </is>
-      </c>
-      <c r="Q6" t="b">
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>AFC Industries (DDTL)</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>AFC Industries (DDTL)</t>
+        </is>
+      </c>
+      <c r="M6" t="b">
+        <v>1</v>
+      </c>
+      <c r="N6" t="b">
+        <v>1</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.8579</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>314.2243</v>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>AFC Acquisitions | Watchtower Holdings</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>AFC Industries (DDTL) | AFC Industries (Common Equity) | AFC Industries (TL) | Watchtower Holding (Common Equity)</t>
+        </is>
+      </c>
+      <c r="T6" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GGG Midco, LLC</t>
+          <t>AFC-Dell Holding Corp.</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -884,27 +952,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Company Match</t>
+          <t>Company Knowledge Match</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Guild Garage Group</t>
+          <t>AFC-Dell Holding T/L</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Guild Garage Group (DDTL)</t>
+          <t>afc dell holding</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Guild Garage Group</t>
+          <t>AFC Acquisitions</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Guild Garage Group (DDTL)</t>
+          <t>AFC Acquisitions</t>
         </is>
       </c>
       <c r="H7" t="b">
@@ -916,36 +984,49 @@
       <c r="J7" t="n">
         <v>1</v>
       </c>
-      <c r="K7" t="b">
-        <v>1</v>
-      </c>
-      <c r="L7" t="b">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0.9669</v>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>Guild Garage Group | PCS Retirement | Total Pool Care Network</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Guild Garage Group (DDTL) | Guild Garage Group (Term Loan) | Guild Garage Group (Revolver) | TPCN (DDTL) | PCS Retirement (DDTL)</t>
-        </is>
-      </c>
-      <c r="Q7" t="b">
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>AFC Industries (TL)</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>AFC Industries (TL)</t>
+        </is>
+      </c>
+      <c r="M7" t="b">
+        <v>1</v>
+      </c>
+      <c r="N7" t="b">
+        <v>1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.8579</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>230.7481</v>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>AFC Acquisitions | Watchtower Holdings</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>AFC Industries (TL) | AFC Industries (DDTL) | AFC Industries (Common Equity) | Watchtower Holding (Common Equity)</t>
+        </is>
+      </c>
+      <c r="T7" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Lash Opco, LLC</t>
+          <t>Burgess Point Purchaser Corporation</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -960,22 +1041,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Lilly Lashes</t>
+          <t>Burgess Point Purchaser Corporation (BBB)  T/L (06/22)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Lilly Lashes (TL)</t>
+          <t>burgess point purchaser corporation</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lilly Lashes</t>
+          <t>BBB Industries</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lilly Lashes (TL)</t>
+          <t>BBB Industries</t>
         </is>
       </c>
       <c r="H8" t="b">
@@ -987,36 +1068,49 @@
       <c r="J8" t="n">
         <v>1</v>
       </c>
-      <c r="K8" t="b">
-        <v>1</v>
-      </c>
-      <c r="L8" t="b">
-        <v>1</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0.9639</v>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>Lilly Lashes | APT Healthcare</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Lilly Lashes (TL) | Lilly Lashes (Revolver) | APT Healthcare (Term Loan) | APT Healthcare (Incr. DDTL) | Lilly Lashes (Equity)</t>
-        </is>
-      </c>
-      <c r="Q8" t="b">
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>BBB Industries (First Lien Term Loan)</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>BBB Industries (First Lien Term Loan)</t>
+        </is>
+      </c>
+      <c r="M8" t="b">
+        <v>1</v>
+      </c>
+      <c r="N8" t="b">
+        <v>1</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>621.1671</v>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>BBB Industries | STG Logistics | Adweek | Aspect Software | Health-E Commerce</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>BBB Industries (First Lien Term Loan) | BBB Industries (Second Lien Term Loan) | STG (TL) | Adweek (Term Loan) | Adweek (DDTL)</t>
+        </is>
+      </c>
+      <c r="T8" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>OSP EMBEDDED PURCHASER, LLC</t>
+          <t>BLC Holding Company, Inc.</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1031,22 +1125,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Lynx Technologies</t>
+          <t>BLC Holding Company DD T/L</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Lynx Technologies (TL)</t>
+          <t>blc holding</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lynx Technologies</t>
+          <t>Bland Landscaping</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lynx Technologies (TL)</t>
+          <t>Bland Landscaping</t>
         </is>
       </c>
       <c r="H9" t="b">
@@ -1058,36 +1152,49 @@
       <c r="J9" t="n">
         <v>1</v>
       </c>
-      <c r="K9" t="b">
-        <v>1</v>
-      </c>
-      <c r="L9" t="b">
-        <v>1</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0.9885</v>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>Lynx Technologies | PAR Excellence | STG Logistics | Adweek | Aspect Software</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Lynx Technologies (TL) | Lynx Technologies (Revolver) | Lynx Technologies (Common Equity) | STG (TL) | Adweek (Term Loan)</t>
-        </is>
-      </c>
-      <c r="Q9" t="b">
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Bland Landscaping (DDTL)</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Bland Landscaping (DDTL)</t>
+        </is>
+      </c>
+      <c r="M9" t="b">
+        <v>1</v>
+      </c>
+      <c r="N9" t="b">
+        <v>1</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.9023</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>423.274</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Bland Landscaping | Watchtower Holdings</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>Bland Landscaping (DDTL) | Bland Landscaping (Term Loan) | Bland Landscaping (Revolver) | Watchtower Holding (Common Equity)</t>
+        </is>
+      </c>
+      <c r="T9" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Anteriad, LLC</t>
+          <t>Bluebird Group LLC, The</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1097,27 +1204,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Company Match</t>
+          <t>Security Match</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>MeritDirect</t>
+          <t>Bluebird Group T/L</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MeritDirect (Term Loan)</t>
+          <t>bluebird group the</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MeritDirect</t>
+          <t>Bluebird</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>MeritDirect (Term Loan)</t>
+          <t>Bluebird</t>
         </is>
       </c>
       <c r="H10" t="b">
@@ -1129,36 +1236,49 @@
       <c r="J10" t="n">
         <v>1</v>
       </c>
-      <c r="K10" t="b">
-        <v>1</v>
-      </c>
-      <c r="L10" t="b">
-        <v>1</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0.886</v>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>MeritDirect</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>MeritDirect (Term Loan) | MeritDirect (Common Equity) | MeritDirect (Preferred Equity) | MeritDirect (Revolver)</t>
-        </is>
-      </c>
-      <c r="Q10" t="b">
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Bluebird (Term Loan)</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Bluebird (Term Loan)</t>
+        </is>
+      </c>
+      <c r="M10" t="b">
+        <v>1</v>
+      </c>
+      <c r="N10" t="b">
+        <v>1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>344.7419</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Bluebird | The Creative Group | The Original Cakerie | Simplicity Group | None</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>Bluebird (Term Loan) | Bluebird (Revolver) | Simplicity Group (TL) | The Creative Group (Term Loan) | Simplicity Group (DDTL)</t>
+        </is>
+      </c>
+      <c r="T10" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Paving Lessor Corp.</t>
+          <t>Aegis Technologies Group, LLC, The</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1173,22 +1293,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>C&amp;K Paving Contractors</t>
+          <t>Aegis Technologies Group (BlueHalo) 4th Amend T/L</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>C&amp;K Paving Contractors (Term Loan)</t>
+          <t>aegis technologies group the</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>C&amp;K Paving Contractors</t>
+          <t>BlueHalo</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>C&amp;K Paving Contractors (Term Loan)</t>
+          <t>BlueHalo</t>
         </is>
       </c>
       <c r="H11" t="b">
@@ -1200,36 +1320,49 @@
       <c r="J11" t="n">
         <v>1</v>
       </c>
-      <c r="K11" t="b">
-        <v>1</v>
-      </c>
-      <c r="L11" t="b">
-        <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1</v>
-      </c>
-      <c r="N11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>C&amp;K Paving Contractors</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>C&amp;K Paving Contractors (Term Loan) | C&amp;K Paving Contractors (DDTL) | C&amp;K Paving Contractors (Common Equity)</t>
-        </is>
-      </c>
-      <c r="Q11" t="b">
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>BlueHalo (Term Loan)</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>BlueHalo (Term Loan)</t>
+        </is>
+      </c>
+      <c r="M11" t="b">
+        <v>1</v>
+      </c>
+      <c r="N11" t="b">
+        <v>1</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.9736</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>587.9376</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>BlueHalo | API Technologies | Altamira | Nuvei | Lynx Technologies</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>BlueHalo (Term Loan) | API Technologies (TL) | API Technologies (Revolver) | Altamira (Common Equity) | Altamira (TL)</t>
+        </is>
+      </c>
+      <c r="T11" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Lightspeed Buyer, Inc.</t>
+          <t>BlueHalo Global Holdings, LLC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1239,68 +1372,77 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Company Match</t>
+          <t>Security Match</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Centauri Health</t>
+          <t>BlueHalo Global (Aegis) T/L 4th Amend  **DUPLICATE - PLEASE USE BL0623316**</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Centauri Health (TL)</t>
+          <t>bluehalo global holdings</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Centauri Health</t>
+          <t>BlueHalo</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Centauri Health (DDTL)</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="H12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" t="b">
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" t="b">
+        <v>2</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>BlueHalo (Term Loan)</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="b">
         <v>0</v>
       </c>
-      <c r="L12" t="b">
-        <v>1</v>
-      </c>
-      <c r="M12" t="n">
-        <v>2</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0.9392</v>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>Centauri Health | Watchtower Buyer | APHIX | Carisk Partners | Connatix</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Centauri Health (DDTL) | Centauri Health (TL) | Connatix (DDTL) | Centauri Health (Revolver) | Watchtower Buyer (TL)</t>
-        </is>
-      </c>
-      <c r="Q12" t="b">
-        <v>1</v>
+      <c r="N12" t="b">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>8</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.8575</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Global | BlueHalo | Insight Global | Schlesinger | UniTek</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>Schlesinger (Term Loan) | Schlesinger (Equity) | Global (Term Loan) | Insight Global (TL) | Insight Global (Rev)</t>
+        </is>
+      </c>
+      <c r="T12" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NFS - CFP Holdings LLC</t>
+          <t>By Light Professional IT Services LLC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1310,27 +1452,27 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Company Match</t>
+          <t>Security Match</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Commercial Fire Protection</t>
+          <t>By Light Professional R/C 2</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Commercial Fire Protection (Term Loan)</t>
+          <t>by light professional it services</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Commercial Fire Protection</t>
+          <t>By Light</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Commercial Fire Protection (Term Loan)</t>
+          <t>By Light</t>
         </is>
       </c>
       <c r="H13" t="b">
@@ -1342,36 +1484,49 @@
       <c r="J13" t="n">
         <v>1</v>
       </c>
-      <c r="K13" t="b">
-        <v>1</v>
-      </c>
-      <c r="L13" t="b">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0.9549</v>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>Commercial Fire Protection</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Commercial Fire Protection (Term Loan) | Commercial Fire Protection (DDTL) | Commercial Fire Protection (Revolver) | Commercial Fire Protection (Common Equity)</t>
-        </is>
-      </c>
-      <c r="Q13" t="b">
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>By Light (Revolver)</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>By Light (Revolver)</t>
+        </is>
+      </c>
+      <c r="M13" t="b">
+        <v>1</v>
+      </c>
+      <c r="N13" t="b">
+        <v>1</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>465.409</v>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>By Light | Integrated Data Services | Any Hour Services | Applied Technical Services | IDC Infusion Services</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>By Light (Revolver) | By Light (Term Loan) | By Light (DDTL) | By Light (Equity) | By Light (HoldCo Note)</t>
+        </is>
+      </c>
+      <c r="T13" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DRS Holdings III, Inc.</t>
+          <t>Lightspeed Buyer, Inc.</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1386,22 +1541,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Dr. Scholl's</t>
+          <t>Lightspeed Buyer VT1 R/C</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dr. Scholl's (Term Loan)</t>
+          <t>lightspeed buyer</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dr. Scholl's</t>
+          <t>Centauri Health</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dr. Scholl's (Term Loan)</t>
+          <t>Centauri Health</t>
         </is>
       </c>
       <c r="H14" t="b">
@@ -1413,36 +1568,49 @@
       <c r="J14" t="n">
         <v>1</v>
       </c>
-      <c r="K14" t="b">
-        <v>1</v>
-      </c>
-      <c r="L14" t="b">
-        <v>1</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0.8823</v>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>Dr. Scholl's | API Technologies | Wheel Pros | Paris Presents | Apex Service Partners</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Dr. Scholl's (Term Loan) | Apex (DDTL III) | Dr. Scholl's (Revolver) | API Technologies (TL) | Wheel Pros (1L)</t>
-        </is>
-      </c>
-      <c r="Q14" t="b">
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Centauri Health (Revolver)</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Centauri Health (TL)</t>
+        </is>
+      </c>
+      <c r="M14" t="b">
+        <v>0</v>
+      </c>
+      <c r="N14" t="b">
+        <v>1</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.9533</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>247.061</v>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Centauri Health | Watchtower Buyer | APHIX | Carisk Partners | Connatix</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>Centauri Health (TL) | Centauri Health (Revolver) | Centauri Health (DDTL) | Watchtower Buyer (Revolver) | Carisk Partners (Revolver)</t>
+        </is>
+      </c>
+      <c r="T14" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Management Consulting &amp; Research, LLC</t>
+          <t>Dr. Squatch, LLC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1452,27 +1620,27 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Company Match</t>
+          <t>Security Match</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>MCR</t>
+          <t>Dr. Squatch T/L</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>MCR (Term Loan)</t>
+          <t>dr squatch</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MCR</t>
+          <t>Dr. Squatch</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>MCR (Term Loan)</t>
+          <t>Dr. Squatch</t>
         </is>
       </c>
       <c r="H15" t="b">
@@ -1484,41 +1652,54 @@
       <c r="J15" t="n">
         <v>1</v>
       </c>
-      <c r="K15" t="b">
-        <v>1</v>
-      </c>
-      <c r="L15" t="b">
-        <v>1</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0.9645</v>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>MCR | Paradigm Oral Surgery | Solaris Health |  | New Gulf Resources</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>MCR (Term Loan) | Research Horizons (DDTL) | MCR (Revolver) | Paradigm Oral Surgery (DDTL) | IMIA (Term Loan)</t>
-        </is>
-      </c>
-      <c r="Q15" t="b">
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Dr. Squatch (Term Loan)</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Dr. Squatch (Term Loan)</t>
+        </is>
+      </c>
+      <c r="M15" t="b">
+        <v>1</v>
+      </c>
+      <c r="N15" t="b">
+        <v>1</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>392.2633</v>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Dr. Squatch | Dr. Scholl's</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>Dr. Squatch (Term Loan) | Dr. Squatch (Revolver) | Dr. Squatch (DDTL) | Dr. Scholl's (Term Loan) | Dr. Scholl's (Revolver)</t>
+        </is>
+      </c>
+      <c r="T15" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LAV Gear Holdings Inc</t>
+          <t>GGG Midco, LLC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>watc_holdings</t>
+          <t>us bank cashfile</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1528,22 +1709,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>4Wall Entertainment</t>
+          <t>GGG Midco DD T/L</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>4Wall Entertainment (Term Loan)</t>
+          <t>ggg midco</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>4Wall Entertainment</t>
+          <t>Guild Garage Group</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>4Wall Entertainment (DDTL)</t>
+          <t>Guild Garage Group</t>
         </is>
       </c>
       <c r="H16" t="b">
@@ -1555,66 +1736,79 @@
       <c r="J16" t="n">
         <v>1</v>
       </c>
-      <c r="K16" t="b">
-        <v>0</v>
-      </c>
-      <c r="L16" t="b">
-        <v>1</v>
-      </c>
-      <c r="M16" t="n">
-        <v>2</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0.9549</v>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>4Wall Entertainment</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>4Wall Entertainment (DDTL) | 4Wall Entertainment (Term Loan) | 4Wall Entertainment (Revolver)</t>
-        </is>
-      </c>
-      <c r="Q16" t="b">
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Guild Garage Group (DDTL)</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Guild Garage Group (DDTL)</t>
+        </is>
+      </c>
+      <c r="M16" t="b">
+        <v>1</v>
+      </c>
+      <c r="N16" t="b">
+        <v>1</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.9911</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>438.3659</v>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Guild Garage Group | PCS Retirement | Total Pool Care Network</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>Guild Garage Group (DDTL) | Guild Garage Group (Term Loan) | TPCN (DDTL) | PCS Retirement (DDTL) | TPCN (Term Loan)</t>
+        </is>
+      </c>
+      <c r="T16" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Burgess Point Purchaser Corporation</t>
+          <t>Infinity Home Services Holdco, Inc</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>watc_holdings</t>
+          <t>us bank cashfile</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Company Match</t>
+          <t>Security Match</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>BBB Industries</t>
+          <t>Infinity Home Services Holdco Amend. 1 DD T/L</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>BBB Industries (First Lien Term Loan)</t>
+          <t>infinity home services holdco</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>BBB Industries</t>
+          <t>Infinity Home Services</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>BBB Industries (First Lien Term Loan)</t>
+          <t>Infinity Home Services</t>
         </is>
       </c>
       <c r="H17" t="b">
@@ -1626,41 +1820,54 @@
       <c r="J17" t="n">
         <v>1</v>
       </c>
-      <c r="K17" t="b">
-        <v>1</v>
-      </c>
-      <c r="L17" t="b">
-        <v>1</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0.9744</v>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>BBB Industries | STG Logistics | Adweek | Aspect Software | Health-E Commerce</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>BBB Industries (First Lien Term Loan) | BBB Industries (Second Lien Term Loan) | BBB Industries (Common Equity) | STG (TL) | Adweek (Term Loan)</t>
-        </is>
-      </c>
-      <c r="Q17" t="b">
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Infinity Home Services (DDTL)</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Infinity Home Services (DDTL)</t>
+        </is>
+      </c>
+      <c r="M17" t="b">
+        <v>1</v>
+      </c>
+      <c r="N17" t="b">
+        <v>1</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>516.9478</v>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Infinity Home Services | United Land Services | Any Hour Services | Applied Technical Services | IDC Infusion Services</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>Infinity Home Services (DDTL) | Infinity Home Services (DDTL) CAD | Infinity Home Services (Term Loan) | United Land Services (HoldCo Notes DDTL) | Any Hour Services (DDTL)</t>
+        </is>
+      </c>
+      <c r="T17" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Big Top Holdings LLC</t>
+          <t>Lash Opco, LLC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>watc_holdings</t>
+          <t>us bank cashfile</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1670,22 +1877,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Big Top Manufacturing</t>
+          <t>Lash Opco Restatement T/L--MC178414</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Big Top Manufacturing (Term Loan)</t>
+          <t>lash opco</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Big Top Manufacturing</t>
+          <t>Lilly Lashes</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Big Top Manufacturing (Term Loan)</t>
+          <t>Lilly Lashes</t>
         </is>
       </c>
       <c r="H18" t="b">
@@ -1697,41 +1904,54 @@
       <c r="J18" t="n">
         <v>1</v>
       </c>
-      <c r="K18" t="b">
-        <v>1</v>
-      </c>
-      <c r="L18" t="b">
-        <v>1</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1</v>
-      </c>
-      <c r="N18" t="n">
-        <v>1</v>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Big Top Manufacturing | </t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Big Top Manufacturing (Term Loan) | Big Top Manufacturing (Revolver) | Big Top Manufacturing (Common Equity) | IMIA (Term Loan) | Hard Rock Gary (DDTL)</t>
-        </is>
-      </c>
-      <c r="Q18" t="b">
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Lilly Lashes (TL)</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Lilly Lashes (TL)</t>
+        </is>
+      </c>
+      <c r="M18" t="b">
+        <v>1</v>
+      </c>
+      <c r="N18" t="b">
+        <v>1</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.9896</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>350.5145</v>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Lilly Lashes | APT Healthcare | Zips</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>Lilly Lashes (TL) | APT Healthcare (Term Loan) | APT Healthcare (Incr. DDTL) | Zips (New OpCo Term Loan) | APT Healthcare (Common Equity)</t>
+        </is>
+      </c>
+      <c r="T18" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ACP Falcon Buyer Inc</t>
+          <t>OSP EMBEDDED PURCHASER, LLC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>watc_holdings</t>
+          <t>us bank cashfile</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1741,22 +1961,22 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Integrated Data Services</t>
+          <t>OSP Embedded Purchaser Incremental T/L (11/24)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Integrated Data Services (TL)</t>
+          <t>osp embedded purchaser</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Integrated Data Services</t>
+          <t>Lynx Technologies</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Integrated Data Services (Rev)</t>
+          <t>Lynx Technologies</t>
         </is>
       </c>
       <c r="H19" t="b">
@@ -1768,41 +1988,54 @@
       <c r="J19" t="n">
         <v>1</v>
       </c>
-      <c r="K19" t="b">
-        <v>0</v>
-      </c>
-      <c r="L19" t="b">
-        <v>1</v>
-      </c>
-      <c r="M19" t="n">
-        <v>2</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0.9807</v>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>Integrated Data Services | Big Top Manufacturing | Watchtower Buyer | nThrive | APHIX</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>Integrated Data Services (Rev) | Integrated Data Services (TL) | Watchtower Buyer (TL) | Watchtower Buyer (DDTL) | Big Top Manufacturing (Common Equity)</t>
-        </is>
-      </c>
-      <c r="Q19" t="b">
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Lynx Technologies (TL)</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Lynx Technologies (TL)</t>
+        </is>
+      </c>
+      <c r="M19" t="b">
+        <v>1</v>
+      </c>
+      <c r="N19" t="b">
+        <v>1</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>446.1023</v>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Lynx Technologies | PAR Excellence | STG Logistics | Adweek | Aspect Software</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>Lynx Technologies (TL) | STG (TL) | Adweek (Term Loan) | Adweek (DDTL) | Aspect Software (Equity)</t>
+        </is>
+      </c>
+      <c r="T19" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Kinetic Purchaser LLC</t>
+          <t>Anteriad, LLC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>watc_holdings</t>
+          <t>us bank cashfile</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1812,22 +2045,22 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>KNS</t>
+          <t>Anteriad (MeritDirect) Incremental T/L B</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>KNS (Term Loan)</t>
+          <t>anteriad</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>KNS</t>
+          <t>MeritDirect</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>KNS (Term Loan)</t>
+          <t>MeritDirect</t>
         </is>
       </c>
       <c r="H20" t="b">
@@ -1839,66 +2072,79 @@
       <c r="J20" t="n">
         <v>1</v>
       </c>
-      <c r="K20" t="b">
-        <v>1</v>
-      </c>
-      <c r="L20" t="b">
-        <v>1</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0.9571</v>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>KNS | STG Logistics | Adweek | Aspect Software | Health-E Commerce</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>KNS (Term Loan) | KNS (Equity) | KNS (Revolver) | STG (TL) | Adweek (Term Loan)</t>
-        </is>
-      </c>
-      <c r="Q20" t="b">
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>MeritDirect (Term Loan)</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>MeritDirect (Term Loan)</t>
+        </is>
+      </c>
+      <c r="M20" t="b">
+        <v>1</v>
+      </c>
+      <c r="N20" t="b">
+        <v>1</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.8696</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>360.7486</v>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>MeritDirect</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>MeritDirect (Term Loan) | MeritDirect (Common Equity) | MeritDirect (Preferred Equity) | MeritDirect (Revolver)</t>
+        </is>
+      </c>
+      <c r="T20" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>RRA Corporate LLC</t>
+          <t>MeritDirect, LLC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>watc_holdings</t>
+          <t>us bank cashfile</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Company Match</t>
+          <t>Security Match</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Roofed Right America</t>
+          <t>MeritDirect T/L A (MeritB2B/Anteriad)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Roofed Right America (Term Loan)</t>
+          <t>meritdirect</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Roofed Right America</t>
+          <t>MeritDirect</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Roofed Right America (Term Loan)</t>
+          <t>MeritDirect</t>
         </is>
       </c>
       <c r="H21" t="b">
@@ -1910,66 +2156,79 @@
       <c r="J21" t="n">
         <v>1</v>
       </c>
-      <c r="K21" t="b">
-        <v>1</v>
-      </c>
-      <c r="L21" t="b">
-        <v>1</v>
-      </c>
-      <c r="M21" t="n">
-        <v>1</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0.975</v>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>Roofed Right America</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>Roofed Right America (Term Loan) | Roofed Right America (DDTL 2) | Roofed Right America (DDTL 1) | Roofed Right America (Revolver)</t>
-        </is>
-      </c>
-      <c r="Q21" t="b">
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>MeritDirect (Term Loan)</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>MeritDirect (Term Loan)</t>
+        </is>
+      </c>
+      <c r="M21" t="b">
+        <v>1</v>
+      </c>
+      <c r="N21" t="b">
+        <v>1</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>454.5237</v>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>MeritDirect</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>MeritDirect (Term Loan) | MeritDirect (Common Equity) | MeritDirect (Preferred Equity) | MeritDirect (Revolver)</t>
+        </is>
+      </c>
+      <c r="T21" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>DRS Holdings III Inc</t>
+          <t>OSG Topco Holdings LLC - Class A Unit</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>watc_holdings</t>
+          <t>us bank cashfile</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Company Match</t>
+          <t>Security Match</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Dr. Scholl's</t>
+          <t>OSG Topco Holdings LLC - Class A Unit</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dr. Scholl's (Term Loan)</t>
+          <t>osg topco holdings class a unit</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dr. Scholl's</t>
+          <t>OSG Billing Services</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Apex (DDTL III)</t>
+          <t>OSG Billing Services</t>
         </is>
       </c>
       <c r="H22" t="b">
@@ -1981,66 +2240,73 @@
       <c r="J22" t="n">
         <v>1</v>
       </c>
-      <c r="K22" t="b">
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>OSG (Common Equity)</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="b">
         <v>0</v>
       </c>
-      <c r="L22" t="b">
-        <v>1</v>
-      </c>
-      <c r="M22" t="n">
-        <v>2</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0.8823</v>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>Dr. Scholl's | API Technologies | Wheel Pros | Paris Presents | Apex Service Partners</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>Apex (DDTL III) | Dr. Scholl's (Term Loan) | Dr. Scholl's (Revolver) | Wheel Pros (1L) | API Technologies (TL)</t>
-        </is>
-      </c>
-      <c r="Q22" t="b">
-        <v>1</v>
+      <c r="N22" t="b">
+        <v>0</v>
+      </c>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="n">
+        <v>0.8529</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>OSG Billing Services | U.S. Well | ImagineAcquisitionCo | AKW Holdings | None</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>A1 Garage (DDTL) | AKW Holdings (Term Loan) | AKW Holdings (Common) | Learning Care Group (Common) | CEA (Common)</t>
+        </is>
+      </c>
+      <c r="T22" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>LAV Gear Holdings, Inc.</t>
+          <t>Pragmatic Institute, LLC</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>market_value</t>
+          <t>us bank cashfile</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Company Match</t>
+          <t>Security Match</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>4Wall Entertainment</t>
+          <t>Pragmatic Institute C/S (03/25)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>4Wall Entertainment (Term Loan)</t>
+          <t>pragmatic institute</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>4Wall Entertainment</t>
+          <t>Pragmatic Institute</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>4Wall Entertainment (DDTL)</t>
+          <t>Pragmatic Institute</t>
         </is>
       </c>
       <c r="H23" t="b">
@@ -2052,41 +2318,50 @@
       <c r="J23" t="n">
         <v>1</v>
       </c>
-      <c r="K23" t="b">
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Pragmatic Institute (Common)</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="b">
         <v>0</v>
       </c>
-      <c r="L23" t="b">
-        <v>1</v>
-      </c>
-      <c r="M23" t="n">
-        <v>2</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0.9549</v>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>4Wall Entertainment</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>4Wall Entertainment (DDTL) | 4Wall Entertainment (Term Loan) | 4Wall Entertainment (Revolver)</t>
-        </is>
-      </c>
-      <c r="Q23" t="b">
-        <v>1</v>
+      <c r="N23" t="b">
+        <v>1</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>Pragmatic Institute</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>Pragmatic Institute (Common) | Pragmatic Institute (TL) | Pragmatic Institute (Revolver) | Pragmatic Institute (DDTL)</t>
+        </is>
+      </c>
+      <c r="T23" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TCG 3.0 Jogger Acquisitionco, Inc.</t>
+          <t>Paving Lessor Corp.</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>market_value</t>
+          <t>us bank cashfile</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2096,22 +2371,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>BiggerPockets</t>
+          <t>Paving Lessor Initial T/L</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>BiggerPockets (Revolver)</t>
+          <t>paving lessor</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>BiggerPockets</t>
+          <t>C&amp;K Paving Contractors</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>BiggerPockets (TL)</t>
+          <t>C&amp;K Paving Contractors</t>
         </is>
       </c>
       <c r="H24" t="b">
@@ -2123,41 +2398,54 @@
       <c r="J24" t="n">
         <v>1</v>
       </c>
-      <c r="K24" t="b">
-        <v>0</v>
-      </c>
-      <c r="L24" t="b">
-        <v>1</v>
-      </c>
-      <c r="M24" t="n">
-        <v>2</v>
-      </c>
-      <c r="N24" t="n">
-        <v>1</v>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>BiggerPockets</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>BiggerPockets (TL) | BiggerPockets (Revolver) | BiggerPockets (Common Equity)</t>
-        </is>
-      </c>
-      <c r="Q24" t="b">
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>C&amp;K Paving Contractors (Term Loan)</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>C&amp;K Paving Contractors (Term Loan)</t>
+        </is>
+      </c>
+      <c r="M24" t="b">
+        <v>1</v>
+      </c>
+      <c r="N24" t="b">
+        <v>1</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>423.655</v>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>C&amp;K Paving Contractors</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>C&amp;K Paving Contractors (Term Loan) | C&amp;K Paving Contractors (DDTL) | C&amp;K Paving Contractors (Common Equity)</t>
+        </is>
+      </c>
+      <c r="T24" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Medina Health, LLC</t>
+          <t>Lightspeed Buyer, Inc.</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>market_value</t>
+          <t>us bank cashfile</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2167,22 +2455,22 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Comprehensive Rehab Consultants</t>
+          <t>Lightspeed Buyer T/L</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Comprehensive Rehab Consultants (Revolver)</t>
+          <t>lightspeed buyer</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Comprehensive Rehab Consultants</t>
+          <t>Centauri Health</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Comprehensive Rehab Consultants (Term Loan)</t>
+          <t>Centauri Health</t>
         </is>
       </c>
       <c r="H25" t="b">
@@ -2194,41 +2482,48 @@
       <c r="J25" t="n">
         <v>1</v>
       </c>
-      <c r="K25" t="b">
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Centauri Health (TL)</t>
+        </is>
+      </c>
+      <c r="M25" t="b">
         <v>0</v>
       </c>
-      <c r="L25" t="b">
-        <v>1</v>
-      </c>
-      <c r="M25" t="n">
-        <v>2</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0.9631</v>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>Comprehensive Rehab Consultants | Confluent Health | Ro Health | Cano Health | Nevada Behavioral Health Systems</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>Comprehensive Rehab Consultants (Term Loan) | Comprehensive Rehab Consultants (Revolver) | Comprehensive Rehab Consultants (Common Equity) | Confluent Health (DDTL) | Confluent Health (TL)</t>
-        </is>
-      </c>
-      <c r="Q25" t="b">
+      <c r="N25" t="b">
+        <v>0</v>
+      </c>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="n">
+        <v>0.9533</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>293.4885</v>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>Centauri Health | Watchtower Buyer | APHIX | Carisk Partners | Connatix</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>Centauri Health (TL) | Centauri Health (DDTL) | Centauri Health (Revolver) | Watchtower Buyer (TL) | Watchtower Buyer (DDTL)</t>
+        </is>
+      </c>
+      <c r="T25" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>GAUGE ETE BLOCKER LLC</t>
+          <t>NFS - CFP Holdings LLC</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>market_value</t>
+          <t>us bank cashfile</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2238,22 +2533,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Engine &amp; Transmission Exchange</t>
+          <t>NFS - CFP Holdings Incremental T/L</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Engine &amp; Transmission Exchange (Common Equity)</t>
+          <t>nfs cfp holdings</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Engine &amp; Transmission Exchange</t>
+          <t>Commercial Fire Protection</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Engine &amp; Transmission Exchange (Common Equity)</t>
+          <t>Commercial Fire Protection</t>
         </is>
       </c>
       <c r="H26" t="b">
@@ -2265,41 +2560,54 @@
       <c r="J26" t="n">
         <v>1</v>
       </c>
-      <c r="K26" t="b">
-        <v>1</v>
-      </c>
-      <c r="L26" t="b">
-        <v>1</v>
-      </c>
-      <c r="M26" t="n">
-        <v>1</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0.9933</v>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>Engine &amp; Transmission Exchange | Infosoft | Lilly Lashes | Loving Tan | Schlesinger</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>Engine &amp; Transmission Exchange (Common Equity) | Engine &amp; Transmission Exchange (Promissory Note) | Infosoft (Common Equity) | Engine &amp; Transmission Exchange (Term Loan) | Engine &amp; Transmission Exchange (Revolver)</t>
-        </is>
-      </c>
-      <c r="Q26" t="b">
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Commercial Fire Protection (Term Loan)</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Commercial Fire Protection (Term Loan)</t>
+        </is>
+      </c>
+      <c r="M26" t="b">
+        <v>1</v>
+      </c>
+      <c r="N26" t="b">
+        <v>1</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0.9834000000000001</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>381.1502</v>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>Commercial Fire Protection | AKW Holdings</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>Commercial Fire Protection (Term Loan) | Commercial Fire Protection (DDTL) | Commercial Fire Protection (Revolver) | Commercial Fire Protection (Common Equity) | AKW Holdings (Term Loan)</t>
+        </is>
+      </c>
+      <c r="T26" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>EDS TOPCO, LP</t>
+          <t>DRS Holdings III, Inc.</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>market_value</t>
+          <t>us bank cashfile</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2309,22 +2617,22 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Epiq</t>
+          <t>DRS Holdings III Amendment No. 4 Incremental T/L</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Epiq (Common)</t>
+          <t>drs holdings iii</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Epiq</t>
+          <t>Dr. Scholl's</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Epiq (Common)</t>
+          <t>Dr. Scholl's</t>
         </is>
       </c>
       <c r="H27" t="b">
@@ -2336,112 +2644,130 @@
       <c r="J27" t="n">
         <v>1</v>
       </c>
-      <c r="K27" t="b">
-        <v>1</v>
-      </c>
-      <c r="L27" t="b">
-        <v>1</v>
-      </c>
-      <c r="M27" t="n">
-        <v>1</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0.9607</v>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>Epiq | 360DG | Guild Garage Group | Northwinds | Seaway Plastics</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>Epiq (Common) | Seaway (Equity) | 360DG (Common Equity) | Northwinds (Common Equity) | Guild Garage Group (Common Equity)</t>
-        </is>
-      </c>
-      <c r="Q27" t="b">
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Dr. Scholl's (Term Loan)</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Dr. Scholl's (Term Loan)</t>
+        </is>
+      </c>
+      <c r="M27" t="b">
+        <v>1</v>
+      </c>
+      <c r="N27" t="b">
+        <v>1</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0.8377</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>349.8867</v>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>Dr. Scholl's | Apex Service Partners | API Technologies | Wheel Pros | Paris Presents</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>Dr. Scholl's (Term Loan) | API Technologies (TL) | API Technologies (Revolver) | Apex (Term Loan) | Apex (Incremental Term Loan)</t>
+        </is>
+      </c>
+      <c r="T27" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ENC Parent Corporation</t>
+          <t>Arcline FM Holdings LLC</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>market_value</t>
+          <t>us bank cashfile</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Company Match</t>
+          <t>Company Knowledge Match</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Evans Network</t>
+          <t>Arcline FM Holdings T/L (7/24) (Fairbanks Morse) - Target</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Evans Network (1L)</t>
+          <t>arcline fm holdings</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Evans Network</t>
+          <t>Fairbanks Morse Defense</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Evans Network (1L)</t>
+          <t>AKW Holdings</t>
         </is>
       </c>
       <c r="H28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I28" t="b">
-        <v>1</v>
-      </c>
-      <c r="J28" t="n">
-        <v>1</v>
-      </c>
-      <c r="K28" t="b">
-        <v>1</v>
-      </c>
-      <c r="L28" t="b">
-        <v>1</v>
-      </c>
-      <c r="M28" t="n">
-        <v>1</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0.9448</v>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>Evans Network | Connatix | Planview | Rancho Medical | Rosco</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>Evans Network (1L) | Evans Network (2L) | Connatix (Term Loan) | Connatix (Revolver) | Connatix (DDTL)</t>
-        </is>
-      </c>
-      <c r="Q28" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Fairbanks Morse Defense (Term Loan)</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="b">
+        <v>0</v>
+      </c>
+      <c r="N28" t="b">
+        <v>0</v>
+      </c>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="n">
+        <v>0.6244</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>AKW Holdings</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>AKW Holdings (Term Loan) | AKW Holdings (Common)</t>
+        </is>
+      </c>
+      <c r="T28" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Best Practice Associates, LLC</t>
+          <t>Management Consulting &amp; Research, LLC</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>market_value</t>
+          <t>us bank cashfile</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2451,22 +2777,22 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Federal Advisory Partners</t>
+          <t>Management Consulting &amp; Research T/L (Systems Planning and Analysis)</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Federal Advisory Partners (First Lien Term Loan)</t>
+          <t>management consulting research</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Federal Advisory Partners</t>
+          <t>MCR</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Federal Advisory Partners (First Lien Term Loan)</t>
+          <t>MCR</t>
         </is>
       </c>
       <c r="H29" t="b">
@@ -2478,137 +2804,159 @@
       <c r="J29" t="n">
         <v>1</v>
       </c>
-      <c r="K29" t="b">
-        <v>1</v>
-      </c>
-      <c r="L29" t="b">
-        <v>1</v>
-      </c>
-      <c r="M29" t="n">
-        <v>1</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0.9984</v>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>Federal Advisory Partners |  | First Medical Associates</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>Federal Advisory Partners (First Lien Term Loan) | Federal Advisory Partners (Revolver) | Federal Advisory Partners (Term Loan) | First Medical Associates (Term Loan) | First Medical Associates (DDTL)</t>
-        </is>
-      </c>
-      <c r="Q29" t="b">
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>MCR (Term Loan)</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>MCR (Term Loan)</t>
+        </is>
+      </c>
+      <c r="M29" t="b">
+        <v>1</v>
+      </c>
+      <c r="N29" t="b">
+        <v>1</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>466.0747</v>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>MCR | Research Now/SSI | PhaseWell Research | Pinnacle Clinical Research | CHA Consulting</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>MCR (Term Loan) | MCR (Revolver) | CHA Consulting (TL) | CHA Consulting (DDTL) | Research Now / SSI (Common Equity)</t>
+        </is>
+      </c>
+      <c r="T29" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MidOcean JF Holdings Corp.</t>
+          <t>PlayPower, Inc.</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>market_value</t>
+          <t>us bank cashfile</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Company Match</t>
+          <t>Company Knowledge Match</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Jones &amp; Frank</t>
+          <t>PlayPower T/L (5/19)</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Jones &amp; Frank (TL)</t>
+          <t>playpower</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Jones &amp; Frank</t>
+          <t>Planview</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Jones &amp; Frank (TL)</t>
+          <t>PlayPower</t>
         </is>
       </c>
       <c r="H30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I30" t="b">
-        <v>1</v>
-      </c>
-      <c r="J30" t="n">
-        <v>1</v>
-      </c>
-      <c r="K30" t="b">
-        <v>1</v>
-      </c>
-      <c r="L30" t="b">
-        <v>1</v>
-      </c>
-      <c r="M30" t="n">
-        <v>1</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0.9549</v>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>Jones &amp; Frank</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>Jones &amp; Frank (TL) | Jones &amp; Frank (Common) | Jones &amp; Frank (Preferred) | Jones &amp; Frank (Series B)</t>
-        </is>
-      </c>
-      <c r="Q30" t="b">
+        <v>0</v>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Planview (TL)</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>PlayPower (Term Loan)</t>
+        </is>
+      </c>
+      <c r="M30" t="b">
+        <v>0</v>
+      </c>
+      <c r="N30" t="b">
+        <v>0</v>
+      </c>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>324.8272</v>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>PlayPower</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>PlayPower (Term Loan)</t>
+        </is>
+      </c>
+      <c r="T30" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>4Wall Entertainment</t>
+          <t>PlayPower, Inc.</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>master_ratings</t>
+          <t>us bank cashfile</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Company Match</t>
+          <t>Security Match</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>4Wall Entertainment</t>
+          <t>PlayPower T/L (08/24)</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>4Wall Entertainment (Term Loan)</t>
+          <t>playpower</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>4Wall Entertainment</t>
+          <t>PlayPower</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>4Wall Entertainment (Revolver)</t>
+          <t>PlayPower</t>
         </is>
       </c>
       <c r="H31" t="b">
@@ -2620,208 +2968,243 @@
       <c r="J31" t="n">
         <v>1</v>
       </c>
-      <c r="K31" t="b">
-        <v>0</v>
-      </c>
-      <c r="L31" t="b">
-        <v>1</v>
-      </c>
-      <c r="M31" t="n">
-        <v>2</v>
-      </c>
-      <c r="N31" t="n">
-        <v>1</v>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>4Wall Entertainment | ECL Entertainment | Peninsula Pacific Entertainment |  | Mom And Pop</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>4Wall Entertainment (Revolver) | 4Wall Entertainment (Term Loan) | 4Wall Entertainment (DDTL) | ECL Entertainment (Term Loan) | Peninsula Pacific Entertainment (Term Loan B)</t>
-        </is>
-      </c>
-      <c r="Q31" t="b">
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>PlayPower (Term Loan)</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>PlayPower (Term Loan)</t>
+        </is>
+      </c>
+      <c r="M31" t="b">
+        <v>1</v>
+      </c>
+      <c r="N31" t="b">
+        <v>1</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>324.8272</v>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>PlayPower</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>PlayPower (Term Loan)</t>
+        </is>
+      </c>
+      <c r="T31" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Aeronix</t>
+          <t>The Track Branson Opco, LLC</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>master_ratings</t>
+          <t>us bank cashfile</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Company Match</t>
+          <t>Company Knowledge Match</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Aeronix</t>
+          <t>The Track Branson Opco DDTL</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Aeronix (Common Equity)</t>
+          <t>the track branson opco</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Aeronix</t>
+          <t>The Creative Group</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Aeronix (Revolver)</t>
+          <t>APT Healthcare</t>
         </is>
       </c>
       <c r="H32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I32" t="b">
         <v>1</v>
       </c>
       <c r="J32" t="n">
-        <v>1</v>
-      </c>
-      <c r="K32" t="b">
+        <v>4</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>The Creative Group (Term Loan)</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>APT Healthcare (Incr. DDTL)</t>
+        </is>
+      </c>
+      <c r="M32" t="b">
         <v>0</v>
       </c>
-      <c r="L32" t="b">
-        <v>1</v>
-      </c>
-      <c r="M32" t="n">
-        <v>3</v>
-      </c>
-      <c r="N32" t="n">
-        <v>1</v>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>Aeronix</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>Aeronix (Revolver) | Aeronix (TL) | Aeronix (Common Equity) | Aeronix (DDTL)</t>
-        </is>
-      </c>
-      <c r="Q32" t="b">
+      <c r="N32" t="b">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>6</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0.7469</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>270.9943</v>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>APT Healthcare | Lilly Lashes | Zips | The Creative Group | The Original Cakerie</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>APT Healthcare (Incr. DDTL) | Zips (DDTL) | APT Healthcare (Term Loan) | APT Healthcare (Common Equity) | APT Healthcare (Revolver)</t>
+        </is>
+      </c>
+      <c r="T32" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Any Hour Services</t>
+          <t>Sath Industries LLC</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>master_ratings</t>
+          <t>watc_holdings</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Company Match</t>
+          <t>Company Knowledge Match</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Any Hour Services</t>
+          <t>Sath Industries LLC Delayed Draw Term Loan (360DG)</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Any Hour Services (DDTL II)</t>
+          <t>sath industries</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Any Hour Services</t>
+          <t>360DG</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Any Hour Services (Revolver)</t>
+          <t>Boss Industries</t>
         </is>
       </c>
       <c r="H33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I33" t="b">
-        <v>1</v>
-      </c>
-      <c r="J33" t="n">
-        <v>1</v>
-      </c>
-      <c r="K33" t="b">
         <v>0</v>
       </c>
-      <c r="L33" t="b">
-        <v>1</v>
-      </c>
-      <c r="M33" t="n">
-        <v>5</v>
-      </c>
-      <c r="N33" t="n">
-        <v>1</v>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>Any Hour Services | Applied Technical Services | IDC Infusion Services | OSG Billing Services | TEAM Services Group</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>Any Hour Services (Revolver) | Any Hour Services (Term Loan) | Any Hour Services (Common Equity) | Any Hour Services (DDTL) | Any Hour Services (DDTL II)</t>
-        </is>
-      </c>
-      <c r="Q33" t="b">
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>360DG (DDTL A)</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>AFC Industries (DDTL)</t>
+        </is>
+      </c>
+      <c r="M33" t="b">
+        <v>0</v>
+      </c>
+      <c r="N33" t="b">
+        <v>0</v>
+      </c>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="n">
+        <v>0.8356</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>265.6984</v>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>Boss Industries | ECM Industries | AFC Acquisitions | DermaRite | Nsi Industries</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>AFC Industries (DDTL) | Nsi Industries (DDTL) | AFC Industries (TL) | Boss Industries (Term Loan) | ECM Industries (TL)</t>
+        </is>
+      </c>
+      <c r="T33" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Any Hour Services</t>
+          <t>48Forty Intermediate Holdings Inc</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>master_ratings</t>
+          <t>watc_holdings</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Company Match</t>
+          <t>Security Match</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Any Hour Services</t>
+          <t>48Forty Intermediate Holdings Inc Common Equity</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Any Hour Services (Common Equity)</t>
+          <t>48forty intermediate holdings</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Any Hour Services</t>
+          <t>48Forty</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Any Hour Services (Revolver)</t>
+          <t>48Forty</t>
         </is>
       </c>
       <c r="H34" t="b">
@@ -2833,41 +3216,54 @@
       <c r="J34" t="n">
         <v>1</v>
       </c>
-      <c r="K34" t="b">
-        <v>0</v>
-      </c>
-      <c r="L34" t="b">
-        <v>1</v>
-      </c>
-      <c r="M34" t="n">
-        <v>3</v>
-      </c>
-      <c r="N34" t="n">
-        <v>1</v>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>Any Hour Services | Applied Technical Services | IDC Infusion Services | OSG Billing Services | TEAM Services Group</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>Any Hour Services (Revolver) | Any Hour Services (Term Loan) | Any Hour Services (Common Equity) | Any Hour Services (DDTL) | Any Hour Services (DDTL II)</t>
-        </is>
-      </c>
-      <c r="Q34" t="b">
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>48Forty (Common Equity)</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>48Forty (Common Equity)</t>
+        </is>
+      </c>
+      <c r="M34" t="b">
+        <v>1</v>
+      </c>
+      <c r="N34" t="b">
+        <v>1</v>
+      </c>
+      <c r="O34" t="n">
+        <v>1</v>
+      </c>
+      <c r="P34" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>429.7589</v>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>48Forty | Smartronix / Trident | Altamira | Douglas | Engine &amp; Transmission Exchange</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>48Forty (Common Equity) | 48Forty (Term Loan) | Altamira (Common Equity) | Smartronix / Trident (Common Equity) | Engine &amp; Transmission Exchange (Common Equity)</t>
+        </is>
+      </c>
+      <c r="T34" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Cano Health</t>
+          <t>LAV Gear Holdings Inc</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>master_ratings</t>
+          <t>watc_holdings</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2877,22 +3273,22 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Cano Health</t>
+          <t>LAV Gear Holdings Inc Fourteenth Amendment Priority Term Loan</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Cano Health (Equity)</t>
+          <t>lav gear holdings</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Cano Health</t>
+          <t>4Wall Entertainment</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cano Health (Equity)</t>
+          <t>4Wall Entertainment</t>
         </is>
       </c>
       <c r="H35" t="b">
@@ -2904,41 +3300,54 @@
       <c r="J35" t="n">
         <v>1</v>
       </c>
-      <c r="K35" t="b">
-        <v>1</v>
-      </c>
-      <c r="L35" t="b">
-        <v>1</v>
-      </c>
-      <c r="M35" t="n">
-        <v>1</v>
-      </c>
-      <c r="N35" t="n">
-        <v>1</v>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>Cano Health |  | Confluent Health | Ro Health | Nevada Behavioral Health Systems</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>Cano Health (Equity) | Cano Health (Term Loan) | Ro Health (Revolver) | Confluent Health (TL) | Ro Health (Term Loan)</t>
-        </is>
-      </c>
-      <c r="Q35" t="b">
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>4Wall Entertainment (Term Loan)</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>4Wall Entertainment (Term Loan)</t>
+        </is>
+      </c>
+      <c r="M35" t="b">
+        <v>1</v>
+      </c>
+      <c r="N35" t="b">
+        <v>1</v>
+      </c>
+      <c r="O35" t="n">
+        <v>1</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0.9834000000000001</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>384.8888</v>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>4Wall Entertainment | AKW Holdings</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>4Wall Entertainment (Term Loan) | 4Wall Entertainment (DDTL) | AKW Holdings (Term Loan) | AKW Holdings (Common) | 4Wall Entertainment (Revolver)</t>
+        </is>
+      </c>
+      <c r="T35" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Dr. Scholl's</t>
+          <t>Burgess Point Purchaser Corporation</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>master_ratings</t>
+          <t>watc_holdings</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2948,22 +3357,22 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Dr. Scholl's</t>
+          <t>Burgess Point Purchaser Corporation Initial Term Loan</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Dr. Scholl's (Revolver)</t>
+          <t>burgess point purchaser corporation</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dr. Scholl's</t>
+          <t>BBB Industries</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dr. Scholl's (Revolver)</t>
+          <t>BBB Industries</t>
         </is>
       </c>
       <c r="H36" t="b">
@@ -2975,41 +3384,54 @@
       <c r="J36" t="n">
         <v>1</v>
       </c>
-      <c r="K36" t="b">
-        <v>1</v>
-      </c>
-      <c r="L36" t="b">
-        <v>1</v>
-      </c>
-      <c r="M36" t="n">
-        <v>1</v>
-      </c>
-      <c r="N36" t="n">
-        <v>1</v>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>Dr. Scholl's | Dr. Squatch</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>Dr. Scholl's (Revolver) | Dr. Scholl's (Term Loan) | Dr. Squatch (Term Loan) | Dr. Squatch (Revolver) | Dr. Squatch (DDTL)</t>
-        </is>
-      </c>
-      <c r="Q36" t="b">
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>BBB Industries (First Lien Term Loan)</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>BBB Industries (First Lien Term Loan)</t>
+        </is>
+      </c>
+      <c r="M36" t="b">
+        <v>1</v>
+      </c>
+      <c r="N36" t="b">
+        <v>1</v>
+      </c>
+      <c r="O36" t="n">
+        <v>1</v>
+      </c>
+      <c r="P36" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>505.2237</v>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>BBB Industries | STG Logistics | Adweek | Aspect Software | Health-E Commerce</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>BBB Industries (First Lien Term Loan) | BBB Industries (Second Lien Term Loan) | STG (TL) | Adweek (Term Loan) | Adweek (DDTL)</t>
+        </is>
+      </c>
+      <c r="T36" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Infinity Home Services</t>
+          <t>Big Top Holdings LLC</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>master_ratings</t>
+          <t>watc_holdings</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3019,22 +3441,22 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Infinity Home Services</t>
+          <t>Big Top Holdings LLC Term Loan</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Infinity Home Services (DDTL)</t>
+          <t>big top holdings</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Infinity Home Services</t>
+          <t>Big Top Manufacturing</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Infinity Home Services (Revolver)</t>
+          <t>Big Top Manufacturing</t>
         </is>
       </c>
       <c r="H37" t="b">
@@ -3046,112 +3468,138 @@
       <c r="J37" t="n">
         <v>1</v>
       </c>
-      <c r="K37" t="b">
-        <v>0</v>
-      </c>
-      <c r="L37" t="b">
-        <v>1</v>
-      </c>
-      <c r="M37" t="n">
-        <v>4</v>
-      </c>
-      <c r="N37" t="n">
-        <v>1</v>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>Infinity Home Services | Any Hour Services | Applied Technical Services | IDC Infusion Services | OSG Billing Services</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>Infinity Home Services (Revolver) | Infinity Home Services (Common Equity) | Infinity Home Services (Term Loan) | Infinity Home Services (DDTL) | Infinity Home Services (DDTL) CAD</t>
-        </is>
-      </c>
-      <c r="Q37" t="b">
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Big Top Manufacturing (Term Loan)</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Big Top Manufacturing (Term Loan)</t>
+        </is>
+      </c>
+      <c r="M37" t="b">
+        <v>1</v>
+      </c>
+      <c r="N37" t="b">
+        <v>1</v>
+      </c>
+      <c r="O37" t="n">
+        <v>1</v>
+      </c>
+      <c r="P37" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>445.7695</v>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>Big Top Manufacturing | None | AKW Holdings</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>Big Top Manufacturing (Term Loan) | Big Top Manufacturing (Revolver) | Big Top Manufacturing (Common Equity) | AKW Holdings (Term Loan) | IMIA (Term Loan)</t>
+        </is>
+      </c>
+      <c r="T37" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>KNS</t>
+          <t>BlueHalo Global Holdings LLC</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>master_ratings</t>
+          <t>watc_holdings</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Company Match</t>
+          <t>Security Match</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>KNS</t>
+          <t>BlueHalo Global Holdings LLC Initial Term Loan</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>KNS (Term Loan)</t>
+          <t>bluehalo global holdings</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>KNS</t>
+          <t>BlueHalo</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>KNS (Equity)</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="H38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I38" t="b">
         <v>1</v>
       </c>
       <c r="J38" t="n">
-        <v>1</v>
-      </c>
-      <c r="K38" t="b">
-        <v>0</v>
-      </c>
-      <c r="L38" t="b">
-        <v>1</v>
-      </c>
-      <c r="M38" t="n">
-        <v>3</v>
-      </c>
-      <c r="N38" t="n">
-        <v>1</v>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>KNS</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>KNS (Equity) | KNS (Revolver) | KNS (Term Loan)</t>
-        </is>
-      </c>
-      <c r="Q38" t="b">
+        <v>2</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>BlueHalo (Term Loan)</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>BlueHalo (Term Loan)</t>
+        </is>
+      </c>
+      <c r="M38" t="b">
+        <v>1</v>
+      </c>
+      <c r="N38" t="b">
+        <v>1</v>
+      </c>
+      <c r="O38" t="n">
+        <v>1</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0.8575</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>268.6741</v>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>Global | BlueHalo | Insight Global | Schlesinger | UniTek</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>BlueHalo (Term Loan) | Global (Term Loan) | Insight Global (TL) | Schlesinger (Term Loan) | Schlesinger (DDTL)</t>
+        </is>
+      </c>
+      <c r="T38" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Recteq</t>
+          <t>ACP Falcon Buyer Inc</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>master_ratings</t>
+          <t>watc_holdings</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3161,22 +3609,22 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Recteq</t>
+          <t>ACP Falcon Buyer Inc Initial Term Loan</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Recteq (Equity)</t>
+          <t>acp falcon buyer</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Recteq</t>
+          <t>Integrated Data Services</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Recteq (Revolver)</t>
+          <t>Integrated Data Services</t>
         </is>
       </c>
       <c r="H39" t="b">
@@ -3188,41 +3636,54 @@
       <c r="J39" t="n">
         <v>1</v>
       </c>
-      <c r="K39" t="b">
-        <v>0</v>
-      </c>
-      <c r="L39" t="b">
-        <v>1</v>
-      </c>
-      <c r="M39" t="n">
-        <v>3</v>
-      </c>
-      <c r="N39" t="n">
-        <v>1</v>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>Recteq</t>
-        </is>
-      </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>Recteq (Revolver) | Recteq (TL) | Recteq (Equity)</t>
-        </is>
-      </c>
-      <c r="Q39" t="b">
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Integrated Data Services (TL)</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Integrated Data Services (TL)</t>
+        </is>
+      </c>
+      <c r="M39" t="b">
+        <v>1</v>
+      </c>
+      <c r="N39" t="b">
+        <v>1</v>
+      </c>
+      <c r="O39" t="n">
+        <v>1</v>
+      </c>
+      <c r="P39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>408.6695</v>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>Integrated Data Services | Watchtower Buyer | nThrive | Big Top Manufacturing | APHIX</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>Integrated Data Services (TL) | Integrated Data Services (Rev) | Watchtower Buyer (TL) | Watchtower Buyer (DDTL) | Aphix (Term Loan)</t>
+        </is>
+      </c>
+      <c r="T39" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Project Granite Buyer, Inc.</t>
+          <t>Kinetic Purchaser LLC</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>consolidated_soi</t>
+          <t>watc_holdings</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3232,22 +3693,22 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Tranzact</t>
+          <t>Kinetic Purchaser LLC Closing Date Term Loan</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Tranzact (Term Loan)</t>
+          <t>kinetic purchaser</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tranzact</t>
+          <t>KNS</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tranzact (DDTL)</t>
+          <t>KNS</t>
         </is>
       </c>
       <c r="H40" t="b">
@@ -3259,66 +3720,79 @@
       <c r="J40" t="n">
         <v>1</v>
       </c>
-      <c r="K40" t="b">
-        <v>0</v>
-      </c>
-      <c r="L40" t="b">
-        <v>1</v>
-      </c>
-      <c r="M40" t="n">
-        <v>3</v>
-      </c>
-      <c r="N40" t="n">
-        <v>0.9797</v>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>Tranzact | Watchtower Buyer | APHIX | Carisk Partners | Connatix</t>
-        </is>
-      </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>Tranzact (DDTL) | Tranzact (Revolver) | Tranzact (Term Loan) | Tranzact (Common Equity) | Watchtower Buyer (Revolver)</t>
-        </is>
-      </c>
-      <c r="Q40" t="b">
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>KNS (Term Loan)</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>KNS (Term Loan)</t>
+        </is>
+      </c>
+      <c r="M40" t="b">
+        <v>1</v>
+      </c>
+      <c r="N40" t="b">
+        <v>1</v>
+      </c>
+      <c r="O40" t="n">
+        <v>1</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0.9758</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>328.7208</v>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>KNS | STG Logistics | Adweek | Aspect Software | Health-E Commerce</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>KNS (Term Loan) | STG (TL) | Adweek (Term Loan) | Adweek (DDTL) | Health-E Commerce (Term Loan)</t>
+        </is>
+      </c>
+      <c r="T40" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>TransGo, LLC</t>
+          <t>Radius Aerospace Inc</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>consolidated_soi</t>
+          <t>watc_holdings</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Company Match</t>
+          <t>Security Match</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>TransGo</t>
+          <t>Radius Aerospace Inc UK Term Loan</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>TransGo (Equity)</t>
+          <t>radius aerospace</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>TransGo</t>
+          <t>Radius Aerospace</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>TransGo (Revolver)</t>
+          <t>Radius Aerospace</t>
         </is>
       </c>
       <c r="H41" t="b">
@@ -3330,41 +3804,54 @@
       <c r="J41" t="n">
         <v>1</v>
       </c>
-      <c r="K41" t="b">
-        <v>0</v>
-      </c>
-      <c r="L41" t="b">
-        <v>1</v>
-      </c>
-      <c r="M41" t="n">
-        <v>3</v>
-      </c>
-      <c r="N41" t="n">
-        <v>1</v>
-      </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>TransGo</t>
-        </is>
-      </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>TransGo (Revolver) | TransGo (TL) | TransGo (Equity)</t>
-        </is>
-      </c>
-      <c r="Q41" t="b">
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Radius Aerospace (Term Loan)</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Radius Aerospace (Term Loan)</t>
+        </is>
+      </c>
+      <c r="M41" t="b">
+        <v>1</v>
+      </c>
+      <c r="N41" t="b">
+        <v>1</v>
+      </c>
+      <c r="O41" t="n">
+        <v>1</v>
+      </c>
+      <c r="P41" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>437.8485</v>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>Radius Aerospace | Cadence Aerospace | MAG Aerospace</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>Radius Aerospace (Term Loan) | Radius Aerospace (Revolver) | MAG Aerospace (TL) | Cadence Aerospace</t>
+        </is>
+      </c>
+      <c r="T41" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Schlesinger Global, Inc.</t>
+          <t>RRA Corporate LLC</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>consolidated_soi</t>
+          <t>watc_holdings</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3374,22 +3861,22 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Schlesinger</t>
+          <t>RRA Corporate LLC Initial Term Loan</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Schlesinger (Equity)</t>
+          <t>rra corporate</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Schlesinger</t>
+          <t>Roofed Right America</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Schlesinger (Term Loan)</t>
+          <t>Roofed Right America</t>
         </is>
       </c>
       <c r="H42" t="b">
@@ -3401,208 +3888,239 @@
       <c r="J42" t="n">
         <v>1</v>
       </c>
-      <c r="K42" t="b">
-        <v>0</v>
-      </c>
-      <c r="L42" t="b">
-        <v>1</v>
-      </c>
-      <c r="M42" t="n">
-        <v>4</v>
-      </c>
-      <c r="N42" t="n">
-        <v>1</v>
-      </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>Schlesinger | Global | Insight Global | UniTek | Premiere Global Services (PGi)</t>
-        </is>
-      </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>Schlesinger (Term Loan) | Schlesinger (Revolver) | Schlesinger (DDTL) | Schlesinger (Equity) | Global (Term Loan)</t>
-        </is>
-      </c>
-      <c r="Q42" t="b">
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Roofed Right America (Term Loan)</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Roofed Right America (Term Loan)</t>
+        </is>
+      </c>
+      <c r="M42" t="b">
+        <v>1</v>
+      </c>
+      <c r="N42" t="b">
+        <v>1</v>
+      </c>
+      <c r="O42" t="n">
+        <v>1</v>
+      </c>
+      <c r="P42" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>382.8196</v>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>Roofed Right America</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>Roofed Right America (Term Loan) | Roofed Right America (DDTL 2) | Roofed Right America (DDTL 1) | Roofed Right America (Revolver)</t>
+        </is>
+      </c>
+      <c r="T42" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Pacific Purchaser, LLC</t>
+          <t>TMII Enterprises LLC</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>consolidated_soi</t>
+          <t>watc_holdings</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Company Match</t>
+          <t>Company Knowledge Match</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>ProSearch</t>
+          <t>TMII Enterprises LLC DDTL</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>ProSearch (TL)</t>
+          <t>tmii enterprises</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>ProSearch</t>
+          <t>A1 Garage</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>ProSearch (TL)</t>
+          <t>TVC</t>
         </is>
       </c>
       <c r="H43" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I43" t="b">
-        <v>1</v>
-      </c>
-      <c r="J43" t="n">
-        <v>1</v>
-      </c>
-      <c r="K43" t="b">
-        <v>1</v>
-      </c>
-      <c r="L43" t="b">
-        <v>1</v>
-      </c>
-      <c r="M43" t="n">
-        <v>1</v>
-      </c>
-      <c r="N43" t="n">
-        <v>0.9432</v>
-      </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>ProSearch | Peninsula Pacific Entertainment |  | STG Logistics | Adweek</t>
-        </is>
-      </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>ProSearch (TL) | ProSearch (Revolver) | ProSearch (DDTL) | Peninsula Pacific Entertainment (Term Loan B) | Peninsula Pacific Entertainment (DDTL B)</t>
-        </is>
-      </c>
-      <c r="Q43" t="b">
+        <v>0</v>
+      </c>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>A1 Garage (DDTL)</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>US Fertility (DDTL)</t>
+        </is>
+      </c>
+      <c r="M43" t="b">
+        <v>0</v>
+      </c>
+      <c r="N43" t="b">
+        <v>0</v>
+      </c>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="n">
+        <v>0.7544</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>270.3769</v>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>TVC | US Fertility</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>US Fertility (DDTL) | TVC (DDTL) | TVC (TL) | US Fertility (Term Loan) | TVC (Equity)</t>
+        </is>
+      </c>
+      <c r="T43" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>TCG 3.0 Jogger Acquisitionco, Inc.</t>
+          <t>TMII Enterprises LLC</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>daily_long_short</t>
+          <t>watc_holdings</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Company Match</t>
+          <t>Company Knowledge Match</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>BiggerPockets</t>
+          <t>TMII Enterprises LLC Term Loan A</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>BiggerPockets (Common Equity)</t>
+          <t>tmii enterprises</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>BiggerPockets</t>
+          <t>A1 Garage</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>BiggerPockets (TL)</t>
+          <t>TVC</t>
         </is>
       </c>
       <c r="H44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I44" t="b">
-        <v>1</v>
-      </c>
-      <c r="J44" t="n">
-        <v>1</v>
-      </c>
-      <c r="K44" t="b">
         <v>0</v>
       </c>
-      <c r="L44" t="b">
-        <v>1</v>
-      </c>
-      <c r="M44" t="n">
-        <v>3</v>
-      </c>
-      <c r="N44" t="n">
-        <v>1</v>
-      </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>BiggerPockets</t>
-        </is>
-      </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>BiggerPockets (TL) | BiggerPockets (Revolver) | BiggerPockets (Common Equity)</t>
-        </is>
-      </c>
-      <c r="Q44" t="b">
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>A1 Garage (Term Loan)</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>TVC (TL)</t>
+        </is>
+      </c>
+      <c r="M44" t="b">
+        <v>0</v>
+      </c>
+      <c r="N44" t="b">
+        <v>0</v>
+      </c>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="n">
+        <v>0.7544</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>206.7704</v>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>TVC | US Fertility</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>TVC (TL) | US Fertility (Term Loan) | US Fertility (DDTL) | TVC (DDTL) | TVC (Equity)</t>
+        </is>
+      </c>
+      <c r="T44" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Rancho Health MSO, Inc.</t>
+          <t>SV-Aero Holdings LLC</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>daily_long_short</t>
+          <t>watc_holdings</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Company Match</t>
+          <t>Company Knowledge Match</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Rancho Medical</t>
+          <t>SV-Aero Holdings LLC Term Loan</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Rancho (Equity)</t>
+          <t>sv aero holdings</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rancho Medical</t>
+          <t>Aeronix</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Rancho (TL)</t>
+          <t>Aeronix</t>
         </is>
       </c>
       <c r="H45" t="b">
@@ -3614,41 +4132,54 @@
       <c r="J45" t="n">
         <v>1</v>
       </c>
-      <c r="K45" t="b">
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Aeronix (TL)</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Aeronix (DDTL)</t>
+        </is>
+      </c>
+      <c r="M45" t="b">
         <v>0</v>
       </c>
-      <c r="L45" t="b">
-        <v>0</v>
-      </c>
-      <c r="M45" t="n">
-        <v>12</v>
-      </c>
-      <c r="N45" t="n">
-        <v>1</v>
-      </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>Rancho Medical | Confluent Health | Ro Health | Cano Health | Nevada Behavioral Health Systems</t>
-        </is>
-      </c>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>Rancho (TL) | Rancho (Revolver) | Rancho (DDTL) | Ro Health (Revolver) | Confluent Health (TL)</t>
-        </is>
-      </c>
-      <c r="Q45" t="b">
+      <c r="N45" t="b">
+        <v>1</v>
+      </c>
+      <c r="O45" t="n">
+        <v>4</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>419.8098</v>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>Aeronix | AKW Holdings</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>Aeronix (DDTL) | Aeronix (Common Equity) | AKW Holdings (Term Loan) | Aeronix (TL) | Aeronix (Revolver)</t>
+        </is>
+      </c>
+      <c r="T45" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Project Granite Buyer, Inc.</t>
+          <t>DRS Holdings III Inc</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>daily_long_short</t>
+          <t>watc_holdings</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3658,22 +4189,22 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Tranzact</t>
+          <t>DRS Holdings III Inc 3/25 Term Loan</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Tranzact (Common Equity)</t>
+          <t>drs holdings iii</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tranzact</t>
+          <t>Dr. Scholl's</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tranzact (DDTL)</t>
+          <t>Dr. Scholl's</t>
         </is>
       </c>
       <c r="H46" t="b">
@@ -3685,66 +4216,79 @@
       <c r="J46" t="n">
         <v>1</v>
       </c>
-      <c r="K46" t="b">
-        <v>0</v>
-      </c>
-      <c r="L46" t="b">
-        <v>1</v>
-      </c>
-      <c r="M46" t="n">
-        <v>4</v>
-      </c>
-      <c r="N46" t="n">
-        <v>0.9797</v>
-      </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>Tranzact | Watchtower Buyer | APHIX | Carisk Partners | Connatix</t>
-        </is>
-      </c>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>Tranzact (DDTL) | Tranzact (Revolver) | Tranzact (Term Loan) | Tranzact (Common Equity) | Watchtower Buyer (Revolver)</t>
-        </is>
-      </c>
-      <c r="Q46" t="b">
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Dr. Scholl's (Term Loan)</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Dr. Scholl's (Term Loan)</t>
+        </is>
+      </c>
+      <c r="M46" t="b">
+        <v>1</v>
+      </c>
+      <c r="N46" t="b">
+        <v>1</v>
+      </c>
+      <c r="O46" t="n">
+        <v>1</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0.8377</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>349.8867</v>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>Dr. Scholl's | Apex Service Partners | API Technologies | Wheel Pros | Paris Presents</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>Dr. Scholl's (Term Loan) | Dr. Scholl's (Revolver) | API Technologies (TL) | Apex (DDTL III) | Wheel Pros (1L)</t>
+        </is>
+      </c>
+      <c r="T46" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Tyto Athene, LLC</t>
+          <t>Systems Planning and Analysis Inc</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>daily_long_short</t>
+          <t>watc_holdings</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Company Match</t>
+          <t>Company Knowledge Match</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Tyto Athene</t>
+          <t>Systems Planning and Analysis Inc Delayed Draw Term Loan A</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Tyto Athene (Equity)</t>
+          <t>systems planning and analysis</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tyto Athene</t>
+          <t>MCR</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tyto Athene (Revolver)</t>
+          <t>MCR</t>
         </is>
       </c>
       <c r="H47" t="b">
@@ -3756,137 +4300,159 @@
       <c r="J47" t="n">
         <v>1</v>
       </c>
-      <c r="K47" t="b">
-        <v>0</v>
-      </c>
-      <c r="L47" t="b">
-        <v>1</v>
-      </c>
-      <c r="M47" t="n">
-        <v>3</v>
-      </c>
-      <c r="N47" t="n">
-        <v>1</v>
-      </c>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>Tyto Athene | Athene</t>
-        </is>
-      </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>Tyto Athene (Revolver) | Tyto Athene (Term Loan) | Tyto Athene (Equity) | Tyto Athene (Pref) | Athene (Equity)</t>
-        </is>
-      </c>
-      <c r="Q47" t="b">
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>MCR (Term Loan)</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>MCR (Term Loan)</t>
+        </is>
+      </c>
+      <c r="M47" t="b">
+        <v>1</v>
+      </c>
+      <c r="N47" t="b">
+        <v>1</v>
+      </c>
+      <c r="O47" t="n">
+        <v>1</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0.8461</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>417.5949</v>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>MCR | Sabel Systems | Signature Systems Group | Nevada Behavioral Health Systems | None</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>MCR (Term Loan) | MCR (Revolver) | Kentucky Downs (DDTL A) | FlexPrint (DDTL) | Research Horizons (DDTL)</t>
+        </is>
+      </c>
+      <c r="T47" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Tyto Athene, LLC</t>
+          <t>SMX Group LLC</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>daily_long_short</t>
+          <t>watc_holdings</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Company Match</t>
+          <t>Company Knowledge Match</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Tyto Athene</t>
+          <t>SMX Group LLC Term Loan (Smartronix/Trident)</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Tyto Athene (Pref)</t>
+          <t>smx group</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tyto Athene</t>
+          <t>Smartronix / Trident</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tyto Athene (Revolver)</t>
+          <t>Simplicity Group</t>
         </is>
       </c>
       <c r="H48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I48" t="b">
-        <v>1</v>
-      </c>
-      <c r="J48" t="n">
-        <v>1</v>
-      </c>
-      <c r="K48" t="b">
         <v>0</v>
       </c>
-      <c r="L48" t="b">
-        <v>1</v>
-      </c>
-      <c r="M48" t="n">
-        <v>4</v>
-      </c>
-      <c r="N48" t="n">
-        <v>1</v>
-      </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>Tyto Athene | Athene</t>
-        </is>
-      </c>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>Tyto Athene (Revolver) | Tyto Athene (Term Loan) | Tyto Athene (Equity) | Tyto Athene (Pref) | Athene (Equity)</t>
-        </is>
-      </c>
-      <c r="Q48" t="b">
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Smartronix / Trident (TL)</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>STV Group (TL)</t>
+        </is>
+      </c>
+      <c r="M48" t="b">
+        <v>0</v>
+      </c>
+      <c r="N48" t="b">
+        <v>0</v>
+      </c>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="n">
+        <v>0.549</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>157.2802</v>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>Simplicity Group | None | Case Works Group | Guild Garage Group | STV Group</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>STV Group (TL) | Simplicity Group (TL) | Case Works Group (Term Loan) | Guild Garage Group (Term Loan) | Simplicity Group (DDTL)</t>
+        </is>
+      </c>
+      <c r="T48" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>The Vertex Companies, LLC</t>
+          <t>STG Distribution LLC</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>daily_long_short</t>
+          <t>watc_holdings</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Company Match</t>
+          <t>Security Match</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Vertex</t>
+          <t>STG Distribution LLC First Out New Money Term Loan</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Vertex (Common Equity)</t>
+          <t>stg distribution</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vertex</t>
+          <t>STG Logistics</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Vertex (Term Loan)</t>
+          <t>STG Logistics</t>
         </is>
       </c>
       <c r="H49" t="b">
@@ -3898,100 +4464,3906 @@
       <c r="J49" t="n">
         <v>1</v>
       </c>
-      <c r="K49" t="b">
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>STG (TL)</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>STG (First Out New Money Term Loans)</t>
+        </is>
+      </c>
+      <c r="M49" t="b">
         <v>0</v>
       </c>
-      <c r="L49" t="b">
-        <v>1</v>
-      </c>
-      <c r="M49" t="n">
-        <v>4</v>
-      </c>
-      <c r="N49" t="n">
-        <v>1</v>
-      </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>Vertex</t>
-        </is>
-      </c>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>Vertex (Term Loan) | Vertex (Revolver) | Vertex (DDTL) | Vertex (Common Equity) | Vertex (Preferred Equity)</t>
-        </is>
-      </c>
-      <c r="Q49" t="b">
+      <c r="N49" t="b">
+        <v>1</v>
+      </c>
+      <c r="O49" t="n">
+        <v>2</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0.7583</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>582.932</v>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>STG Logistics | Plimpton &amp; Hills | BlackHawk Industrial | WhiteHawk Industrial</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>STG (First Out New Money Term Loans) | STG (TL) | BlackHawk Industrial (Incremental TL) | BlackHawk Industrial (TL) | BlackHawk Industrial (Revolver)</t>
+        </is>
+      </c>
+      <c r="T49" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>The Vertex Companies, LLC</t>
+          <t>Zips Car Wash LLC</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
+          <t>watc_holdings</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Security Match</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Zips Car Wash LLC Roll Up Term Loan</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>zips car wash</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Zips</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Zips</t>
+        </is>
+      </c>
+      <c r="H50" t="b">
+        <v>1</v>
+      </c>
+      <c r="I50" t="b">
+        <v>1</v>
+      </c>
+      <c r="J50" t="n">
+        <v>1</v>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Zips (Rollup DIP Term Loan)</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Zips (Term Loan)</t>
+        </is>
+      </c>
+      <c r="M50" t="b">
+        <v>0</v>
+      </c>
+      <c r="N50" t="b">
+        <v>1</v>
+      </c>
+      <c r="O50" t="n">
+        <v>3</v>
+      </c>
+      <c r="P50" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>461.5108</v>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>Zips | Magnolia</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>Zips (Term Loan) | Zips (New OpCo Term Loan) | Zips (Rollup DIP Term Loan) | Zips (New Money DIP Term Loan) | Zips (Revolver)</t>
+        </is>
+      </c>
+      <c r="T50" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>LAV Gear Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>market_value</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Company Match</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LAV Gear Holdings, Inc. First Lien - Term Loan - 12th Amend. - Priority FOTL</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>lav gear holdings</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>4Wall Entertainment</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>4Wall Entertainment</t>
+        </is>
+      </c>
+      <c r="H51" t="b">
+        <v>1</v>
+      </c>
+      <c r="I51" t="b">
+        <v>1</v>
+      </c>
+      <c r="J51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>4Wall Entertainment (Term Loan)</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>4Wall Entertainment (Term Loan)</t>
+        </is>
+      </c>
+      <c r="M51" t="b">
+        <v>1</v>
+      </c>
+      <c r="N51" t="b">
+        <v>1</v>
+      </c>
+      <c r="O51" t="n">
+        <v>1</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0.9834000000000001</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>384.8888</v>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>4Wall Entertainment | AKW Holdings</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>4Wall Entertainment (Term Loan) | 4Wall Entertainment (DDTL) | AKW Holdings (Term Loan) | AKW Holdings (Common) | 4Wall Entertainment (Revolver)</t>
+        </is>
+      </c>
+      <c r="T51" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>A1 Garage Equity, LLC</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>market_value</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Security Match</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>A1 Garage Equity, LLC Common Equity</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>a1 garage equity</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>A1 Garage</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>A1 Garage</t>
+        </is>
+      </c>
+      <c r="H52" t="b">
+        <v>1</v>
+      </c>
+      <c r="I52" t="b">
+        <v>1</v>
+      </c>
+      <c r="J52" t="n">
+        <v>1</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>A1 Garage (Common Equity)</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>A1 Garage (Common Equity)</t>
+        </is>
+      </c>
+      <c r="M52" t="b">
+        <v>1</v>
+      </c>
+      <c r="N52" t="b">
+        <v>1</v>
+      </c>
+      <c r="O52" t="n">
+        <v>1</v>
+      </c>
+      <c r="P52" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>459.0776</v>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>A1 Garage | Guild Garage Group | A2 Garge | None | Omnia</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>A1 Garage (Common Equity) | A1 Garage (Revolver) | A1 Garage (Term Loan) | A1 Garage (DDTL) | Guild Garage Group (Common Equity)</t>
+        </is>
+      </c>
+      <c r="T52" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Archer Lewis, LLC</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>market_value</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Security Match</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Archer Lewis, LLC First Lien - Revolver - Revolver</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>archer lewis</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Archer Lewis</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Archer Lewis</t>
+        </is>
+      </c>
+      <c r="H53" t="b">
+        <v>1</v>
+      </c>
+      <c r="I53" t="b">
+        <v>1</v>
+      </c>
+      <c r="J53" t="n">
+        <v>1</v>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Archer Lewis (Revolver)</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Archer Lewis (Revolver)</t>
+        </is>
+      </c>
+      <c r="M53" t="b">
+        <v>1</v>
+      </c>
+      <c r="N53" t="b">
+        <v>1</v>
+      </c>
+      <c r="O53" t="n">
+        <v>1</v>
+      </c>
+      <c r="P53" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>471.6733</v>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>Archer Lewis</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>Archer Lewis (Revolver) | Archer Lewis (Term Loan) | Archer Lewis (Unfunded DDTL B) | Archer Lewis (Unfunded DDTL A) | Archer Lewis (Common Equity)</t>
+        </is>
+      </c>
+      <c r="T53" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Beta Plus Technologies, Inc.</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>market_value</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Security Match</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Beta Plus Technologies, Inc. Initial Term Loan</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>beta plus technologies</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Beta+</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Beta+</t>
+        </is>
+      </c>
+      <c r="H54" t="b">
+        <v>1</v>
+      </c>
+      <c r="I54" t="b">
+        <v>1</v>
+      </c>
+      <c r="J54" t="n">
+        <v>1</v>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Beta+ (TL)</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Beta+ (TL)</t>
+        </is>
+      </c>
+      <c r="M54" t="b">
+        <v>1</v>
+      </c>
+      <c r="N54" t="b">
+        <v>1</v>
+      </c>
+      <c r="O54" t="n">
+        <v>1</v>
+      </c>
+      <c r="P54" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>567.4974999999999</v>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>Beta+ | API Technologies | Altamira | Nuvei | Lynx Technologies</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>Beta+ (TL) | Altamira (TL) | Nuvei (Term Loan) | API Technologies (TL) | Lynx Technologies (TL)</t>
+        </is>
+      </c>
+      <c r="T54" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Rural Sourcing Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>market_value</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Company Knowledge Match</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Rural Sourcing Holdings, Inc. Amendment No. 1 Incremental Term Loans</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>rural sourcing holdings</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Sparq</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Sparq</t>
+        </is>
+      </c>
+      <c r="H55" t="b">
+        <v>1</v>
+      </c>
+      <c r="I55" t="b">
+        <v>1</v>
+      </c>
+      <c r="J55" t="n">
+        <v>1</v>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Sparq (TL)</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Sparq (TL)</t>
+        </is>
+      </c>
+      <c r="M55" t="b">
+        <v>1</v>
+      </c>
+      <c r="N55" t="b">
+        <v>1</v>
+      </c>
+      <c r="O55" t="n">
+        <v>1</v>
+      </c>
+      <c r="P55" t="n">
+        <v>0.9499</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>294.7243</v>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>Sparq | AKW Holdings</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>Sparq (TL) | AKW Holdings (Term Loan) | AKW Holdings (Common) | Sparq (Common Equity) | Sparq (DDTL)</t>
+        </is>
+      </c>
+      <c r="T55" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>TCG 3.0 Jogger Acquisitionco, Inc.</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>market_value</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Company Match</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>TCG 3.0 Jogger Acquisitionco, Inc. First Lien - Revolver - Revolver</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>tcg 3 0 jogger acquisitionco</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>BiggerPockets</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>BiggerPockets</t>
+        </is>
+      </c>
+      <c r="H56" t="b">
+        <v>1</v>
+      </c>
+      <c r="I56" t="b">
+        <v>1</v>
+      </c>
+      <c r="J56" t="n">
+        <v>1</v>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>BiggerPockets (Revolver)</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>BiggerPockets (Revolver)</t>
+        </is>
+      </c>
+      <c r="M56" t="b">
+        <v>1</v>
+      </c>
+      <c r="N56" t="b">
+        <v>1</v>
+      </c>
+      <c r="O56" t="n">
+        <v>1</v>
+      </c>
+      <c r="P56" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>670.9543</v>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>BiggerPockets</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>BiggerPockets (Revolver) | BiggerPockets (TL) | BiggerPockets (Common Equity)</t>
+        </is>
+      </c>
+      <c r="T56" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Carnegie Dartlet, LLC</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>market_value</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Security Match</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Carnegie Dartlet, LLC First Lien - DDTL - DDTL</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>carnegie dartlet</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Carnegie Dartlet</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Carnegie Dartlet</t>
+        </is>
+      </c>
+      <c r="H57" t="b">
+        <v>1</v>
+      </c>
+      <c r="I57" t="b">
+        <v>1</v>
+      </c>
+      <c r="J57" t="n">
+        <v>1</v>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Carnegie Dartlet (DDTL)</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Carnegie Dartlet (DDTL)</t>
+        </is>
+      </c>
+      <c r="M57" t="b">
+        <v>1</v>
+      </c>
+      <c r="N57" t="b">
+        <v>1</v>
+      </c>
+      <c r="O57" t="n">
+        <v>1</v>
+      </c>
+      <c r="P57" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>634.9015000000001</v>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>Carnegie Dartlet</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>Carnegie Dartlet (DDTL) | Carnegie Dartlet (Term Loan) | Carnegie Dartlet (Revolver) | Carnegie Dartlet (Common Equity)</t>
+        </is>
+      </c>
+      <c r="T57" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Medina Health, LLC</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>market_value</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Company Match</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Medina Health, LLC Revolving Loan</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>medina health</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Comprehensive Rehab Consultants</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Comprehensive Rehab Consultants</t>
+        </is>
+      </c>
+      <c r="H58" t="b">
+        <v>1</v>
+      </c>
+      <c r="I58" t="b">
+        <v>1</v>
+      </c>
+      <c r="J58" t="n">
+        <v>1</v>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Comprehensive Rehab Consultants (Revolver)</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Comprehensive Rehab Consultants (Term Loan)</t>
+        </is>
+      </c>
+      <c r="M58" t="b">
+        <v>0</v>
+      </c>
+      <c r="N58" t="b">
+        <v>1</v>
+      </c>
+      <c r="O58" t="n">
+        <v>2</v>
+      </c>
+      <c r="P58" t="n">
+        <v>0.9812</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>310.6171</v>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>Comprehensive Rehab Consultants | Ro Health | Confluent Health | Cano Health | Nevada Behavioral Health Systems</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>Comprehensive Rehab Consultants (Term Loan) | Comprehensive Rehab Consultants (Revolver) | Comprehensive Rehab Consultants (Common Equity) | Confluent Health (TL) | Ro Health (Term Loan)</t>
+        </is>
+      </c>
+      <c r="T58" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>GAUGE ETE BLOCKER LLC</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>market_value</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Company Match</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>GAUGE ETE BLOCKER LLC Common Equity</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>gauge ete blocker</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Engine &amp; Transmission Exchange</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Engine &amp; Transmission Exchange</t>
+        </is>
+      </c>
+      <c r="H59" t="b">
+        <v>1</v>
+      </c>
+      <c r="I59" t="b">
+        <v>1</v>
+      </c>
+      <c r="J59" t="n">
+        <v>1</v>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Engine &amp; Transmission Exchange (Common Equity)</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Engine &amp; Transmission Exchange (Common Equity)</t>
+        </is>
+      </c>
+      <c r="M59" t="b">
+        <v>1</v>
+      </c>
+      <c r="N59" t="b">
+        <v>1</v>
+      </c>
+      <c r="O59" t="n">
+        <v>1</v>
+      </c>
+      <c r="P59" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>536.6979</v>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>Engine &amp; Transmission Exchange | Infosoft | Lilly Lashes | Loving Tan | Schlesinger</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>Engine &amp; Transmission Exchange (Common Equity) | Engine &amp; Transmission Exchange (Promissory Note) | Infosoft (Common Equity) | Schlesinger (Equity) | Lilly Lashes (Equity)</t>
+        </is>
+      </c>
+      <c r="T59" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>EDS TOPCO, LP</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>market_value</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Company Match</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>EDS TOPCO, LP Common Equity</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>eds topco</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Epiq</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Epiq</t>
+        </is>
+      </c>
+      <c r="H60" t="b">
+        <v>1</v>
+      </c>
+      <c r="I60" t="b">
+        <v>1</v>
+      </c>
+      <c r="J60" t="n">
+        <v>1</v>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Epiq (Common)</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Epiq (Common)</t>
+        </is>
+      </c>
+      <c r="M60" t="b">
+        <v>1</v>
+      </c>
+      <c r="N60" t="b">
+        <v>1</v>
+      </c>
+      <c r="O60" t="n">
+        <v>1</v>
+      </c>
+      <c r="P60" t="n">
+        <v>0.8954</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>356.2388</v>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>Epiq | ImagineAcquisitionCo</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>Epiq (Common) | Imagine Topco. L.P. (Common Equity - Series B) | Imagine Topco. L.P. (Preferred Equity - Series A) | Epiq (TL) | Epiq (Revolver)</t>
+        </is>
+      </c>
+      <c r="T60" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>ENC Parent Corporation</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>market_value</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Company Match</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>ENC Parent Corporation Initial Term Loan (First Lien)</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>enc parent corporation</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Evans Network</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Evans Network</t>
+        </is>
+      </c>
+      <c r="H61" t="b">
+        <v>1</v>
+      </c>
+      <c r="I61" t="b">
+        <v>1</v>
+      </c>
+      <c r="J61" t="n">
+        <v>1</v>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Evans Network (1L)</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>Evans Network (1L)</t>
+        </is>
+      </c>
+      <c r="M61" t="b">
+        <v>1</v>
+      </c>
+      <c r="N61" t="b">
+        <v>1</v>
+      </c>
+      <c r="O61" t="n">
+        <v>1</v>
+      </c>
+      <c r="P61" t="n">
+        <v>0.9586</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>553.5313</v>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>Evans Network | Connatix | Planview | Rancho Medical | Rosco</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>Evans Network (1L) | Evans Network (2L) | Connatix (Term Loan) | Connatix (Revolver) | Connatix (DDTL)</t>
+        </is>
+      </c>
+      <c r="T61" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Best Practice Associates, LLC</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>market_value</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Company Match</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Best Practice Associates, LLC First Lien - Term Loan</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>best practice associates</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Federal Advisory Partners</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Federal Advisory Partners</t>
+        </is>
+      </c>
+      <c r="H62" t="b">
+        <v>1</v>
+      </c>
+      <c r="I62" t="b">
+        <v>1</v>
+      </c>
+      <c r="J62" t="n">
+        <v>1</v>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Federal Advisory Partners (First Lien Term Loan)</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>Federal Advisory Partners (First Lien Term Loan)</t>
+        </is>
+      </c>
+      <c r="M62" t="b">
+        <v>1</v>
+      </c>
+      <c r="N62" t="b">
+        <v>1</v>
+      </c>
+      <c r="O62" t="n">
+        <v>1</v>
+      </c>
+      <c r="P62" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>643.9983</v>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>Federal Advisory Partners | None | First Medical Associates</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>Federal Advisory Partners (First Lien Term Loan) | Federal Advisory Partners (Term Loan) | Federal Advisory Partners (Revolver) | First Medical Associates (Term Loan) | First Medical Associates (DDTL)</t>
+        </is>
+      </c>
+      <c r="T62" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Infinity Home Services Holdco, Inc.</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>market_value</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Security Match</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Infinity Home Services Holdco, Inc. Revolving Loan</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>infinity home services holdco</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Infinity Home Services</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Infinity Home Services</t>
+        </is>
+      </c>
+      <c r="H63" t="b">
+        <v>1</v>
+      </c>
+      <c r="I63" t="b">
+        <v>1</v>
+      </c>
+      <c r="J63" t="n">
+        <v>1</v>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Infinity Home Services (Revolver)</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>Infinity Home Services (Term Loan)</t>
+        </is>
+      </c>
+      <c r="M63" t="b">
+        <v>0</v>
+      </c>
+      <c r="N63" t="b">
+        <v>1</v>
+      </c>
+      <c r="O63" t="n">
+        <v>2</v>
+      </c>
+      <c r="P63" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>461.2423</v>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>Infinity Home Services | United Land Services | Any Hour Services | Applied Technical Services | IDC Infusion Services</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>Infinity Home Services (Term Loan) | Infinity Home Services (Revolver) | Infinity Home Services (Common Equity) | Infinity Home Services (DDTL) | Infinity Home Services (DDTL) CAD</t>
+        </is>
+      </c>
+      <c r="T63" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>MidOcean JF Holdings Corp.</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>market_value</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Company Match</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>MidOcean JF Holdings Corp. 5th Amendment Term Loan</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>midocean jf holdings</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Jones &amp; Frank</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Jones &amp; Frank</t>
+        </is>
+      </c>
+      <c r="H64" t="b">
+        <v>1</v>
+      </c>
+      <c r="I64" t="b">
+        <v>1</v>
+      </c>
+      <c r="J64" t="n">
+        <v>1</v>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Jones &amp; Frank (TL)</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>Jones &amp; Frank (Common)</t>
+        </is>
+      </c>
+      <c r="M64" t="b">
+        <v>0</v>
+      </c>
+      <c r="N64" t="b">
+        <v>1</v>
+      </c>
+      <c r="O64" t="n">
+        <v>2</v>
+      </c>
+      <c r="P64" t="n">
+        <v>0.9834000000000001</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>346.1993</v>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>Jones &amp; Frank | AKW Holdings</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>Jones &amp; Frank (Common) | Jones &amp; Frank (TL) | Jones &amp; Frank (Preferred) | Jones &amp; Frank (Series B) | AKW Holdings (Term Loan)</t>
+        </is>
+      </c>
+      <c r="T64" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>4Wall Entertainment</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>master_ratings</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Company Match</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>4Wall Entertainment</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>4wall entertainment</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>4Wall Entertainment</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>4Wall Entertainment</t>
+        </is>
+      </c>
+      <c r="H65" t="b">
+        <v>1</v>
+      </c>
+      <c r="I65" t="b">
+        <v>1</v>
+      </c>
+      <c r="J65" t="n">
+        <v>1</v>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>4Wall Entertainment (Term Loan)</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>4Wall Entertainment (Revolver)</t>
+        </is>
+      </c>
+      <c r="M65" t="b">
+        <v>0</v>
+      </c>
+      <c r="N65" t="b">
+        <v>1</v>
+      </c>
+      <c r="O65" t="n">
+        <v>2</v>
+      </c>
+      <c r="P65" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>341.2175</v>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>4Wall Entertainment | ECL Entertainment | Peninsula Pacific Entertainment | None | Mom And Pop</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>4Wall Entertainment (Revolver) | 4Wall Entertainment (Term Loan) | 4Wall Entertainment (DDTL) | ECL Entertainment (Term Loan) | Peninsula Pacific Entertainment (Term Loan B)</t>
+        </is>
+      </c>
+      <c r="T65" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Aeronix</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>master_ratings</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Company Match</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Aeronix</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>aeronix</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Aeronix</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Aeronix</t>
+        </is>
+      </c>
+      <c r="H66" t="b">
+        <v>1</v>
+      </c>
+      <c r="I66" t="b">
+        <v>1</v>
+      </c>
+      <c r="J66" t="n">
+        <v>1</v>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Aeronix (Common Equity)</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>Aeronix (Revolver)</t>
+        </is>
+      </c>
+      <c r="M66" t="b">
+        <v>0</v>
+      </c>
+      <c r="N66" t="b">
+        <v>1</v>
+      </c>
+      <c r="O66" t="n">
+        <v>3</v>
+      </c>
+      <c r="P66" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>224.8001</v>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>Aeronix</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>Aeronix (Revolver) | Aeronix (TL) | Aeronix (Common Equity) | Aeronix (DDTL)</t>
+        </is>
+      </c>
+      <c r="T66" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Any Hour Services</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>master_ratings</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Company Match</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Any Hour Services</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>any hour services</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Any Hour Services</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Any Hour Services</t>
+        </is>
+      </c>
+      <c r="H67" t="b">
+        <v>1</v>
+      </c>
+      <c r="I67" t="b">
+        <v>1</v>
+      </c>
+      <c r="J67" t="n">
+        <v>1</v>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Any Hour Services (DDTL II)</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>Any Hour Services (Term Loan)</t>
+        </is>
+      </c>
+      <c r="M67" t="b">
+        <v>0</v>
+      </c>
+      <c r="N67" t="b">
+        <v>1</v>
+      </c>
+      <c r="O67" t="n">
+        <v>5</v>
+      </c>
+      <c r="P67" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>406.0594</v>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>Any Hour Services | Applied Technical Services | IDC Infusion Services | TEAM Services Group | Infinity Home Services</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>Any Hour Services (Term Loan) | Any Hour Services (Revolver) | Any Hour Services (Common Equity) | Any Hour Services (DDTL) | Any Hour Services (DDTL II)</t>
+        </is>
+      </c>
+      <c r="T67" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Any Hour Services</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>master_ratings</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Company Match</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Any Hour Services</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>any hour services</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Any Hour Services</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Any Hour Services</t>
+        </is>
+      </c>
+      <c r="H68" t="b">
+        <v>1</v>
+      </c>
+      <c r="I68" t="b">
+        <v>1</v>
+      </c>
+      <c r="J68" t="n">
+        <v>1</v>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Any Hour Services (Common Equity)</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>Any Hour Services (Term Loan)</t>
+        </is>
+      </c>
+      <c r="M68" t="b">
+        <v>0</v>
+      </c>
+      <c r="N68" t="b">
+        <v>1</v>
+      </c>
+      <c r="O68" t="n">
+        <v>3</v>
+      </c>
+      <c r="P68" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>406.0594</v>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>Any Hour Services | Applied Technical Services | IDC Infusion Services | TEAM Services Group | Infinity Home Services</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>Any Hour Services (Term Loan) | Any Hour Services (Revolver) | Any Hour Services (Common Equity) | Any Hour Services (DDTL) | Any Hour Services (DDTL II)</t>
+        </is>
+      </c>
+      <c r="T68" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Cano Health</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>master_ratings</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Company Match</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Cano Health</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>cano health</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Cano Health</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Cano Health</t>
+        </is>
+      </c>
+      <c r="H69" t="b">
+        <v>1</v>
+      </c>
+      <c r="I69" t="b">
+        <v>1</v>
+      </c>
+      <c r="J69" t="n">
+        <v>1</v>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Cano Health (Equity)</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>Cano Health (Term Loan)</t>
+        </is>
+      </c>
+      <c r="M69" t="b">
+        <v>0</v>
+      </c>
+      <c r="N69" t="b">
+        <v>1</v>
+      </c>
+      <c r="O69" t="n">
+        <v>2</v>
+      </c>
+      <c r="P69" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>317.6277</v>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>Cano Health | None | Ro Health | Confluent Health | Nevada Behavioral Health Systems</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>Cano Health (Term Loan) | Cano Health (Equity) | Ro Health (Revolver) | Confluent Health (TL) | Ro Health (Term Loan)</t>
+        </is>
+      </c>
+      <c r="T69" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Dr. Scholl's</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>master_ratings</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Company Match</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Dr. Scholl's</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>dr scholls</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Dr. Scholl's</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Dr. Scholl's</t>
+        </is>
+      </c>
+      <c r="H70" t="b">
+        <v>1</v>
+      </c>
+      <c r="I70" t="b">
+        <v>1</v>
+      </c>
+      <c r="J70" t="n">
+        <v>1</v>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Dr. Scholl's (Revolver)</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>Dr. Scholl's (Revolver)</t>
+        </is>
+      </c>
+      <c r="M70" t="b">
+        <v>1</v>
+      </c>
+      <c r="N70" t="b">
+        <v>1</v>
+      </c>
+      <c r="O70" t="n">
+        <v>1</v>
+      </c>
+      <c r="P70" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>324.8583</v>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>Dr. Scholl's | Dr. Squatch</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>Dr. Scholl's (Revolver) | Dr. Scholl's (Term Loan) | Dr. Squatch (Term Loan) | Dr. Squatch (Revolver) | Dr. Squatch (DDTL)</t>
+        </is>
+      </c>
+      <c r="T70" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Infinity Home Services</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>master_ratings</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Company Match</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Infinity Home Services</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>infinity home services</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Infinity Home Services</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Infinity Home Services</t>
+        </is>
+      </c>
+      <c r="H71" t="b">
+        <v>1</v>
+      </c>
+      <c r="I71" t="b">
+        <v>1</v>
+      </c>
+      <c r="J71" t="n">
+        <v>1</v>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Infinity Home Services (DDTL)</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>Infinity Home Services (Revolver)</t>
+        </is>
+      </c>
+      <c r="M71" t="b">
+        <v>0</v>
+      </c>
+      <c r="N71" t="b">
+        <v>1</v>
+      </c>
+      <c r="O71" t="n">
+        <v>4</v>
+      </c>
+      <c r="P71" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>367.8091</v>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>Infinity Home Services | Any Hour Services | Applied Technical Services | IDC Infusion Services | TEAM Services Group</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>Infinity Home Services (Revolver) | Infinity Home Services (Common Equity) | Infinity Home Services (Term Loan) | Infinity Home Services (DDTL) | Infinity Home Services (DDTL) CAD</t>
+        </is>
+      </c>
+      <c r="T71" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>KNS</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>master_ratings</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Company Match</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>KNS</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>kns</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>KNS</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>KNS</t>
+        </is>
+      </c>
+      <c r="H72" t="b">
+        <v>1</v>
+      </c>
+      <c r="I72" t="b">
+        <v>1</v>
+      </c>
+      <c r="J72" t="n">
+        <v>1</v>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>KNS (Term Loan)</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>KNS (Equity)</t>
+        </is>
+      </c>
+      <c r="M72" t="b">
+        <v>0</v>
+      </c>
+      <c r="N72" t="b">
+        <v>1</v>
+      </c>
+      <c r="O72" t="n">
+        <v>3</v>
+      </c>
+      <c r="P72" t="n">
+        <v>0.9462</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>205.575</v>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>KNS</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>KNS (Equity) | KNS (Revolver) | KNS (Term Loan)</t>
+        </is>
+      </c>
+      <c r="T72" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Recteq</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>master_ratings</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Company Match</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Recteq</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>recteq</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Recteq</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Recteq</t>
+        </is>
+      </c>
+      <c r="H73" t="b">
+        <v>1</v>
+      </c>
+      <c r="I73" t="b">
+        <v>1</v>
+      </c>
+      <c r="J73" t="n">
+        <v>1</v>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Recteq (Equity)</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>Recteq (TL)</t>
+        </is>
+      </c>
+      <c r="M73" t="b">
+        <v>0</v>
+      </c>
+      <c r="N73" t="b">
+        <v>1</v>
+      </c>
+      <c r="O73" t="n">
+        <v>2</v>
+      </c>
+      <c r="P73" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>197.82</v>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>Recteq</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>Recteq (TL) | Recteq (Equity) | Recteq (Revolver)</t>
+        </is>
+      </c>
+      <c r="T73" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>HV Watterson Holdings, LLC</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>consolidated_soi</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Security Match</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>HV Watterson Holdings, LLC - Unfunded Revolver</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>hv watterson holdings</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Watterson</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Watterson</t>
+        </is>
+      </c>
+      <c r="H74" t="b">
+        <v>1</v>
+      </c>
+      <c r="I74" t="b">
+        <v>1</v>
+      </c>
+      <c r="J74" t="n">
+        <v>1</v>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Watterson (Revolver)</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>Watterson (Revolver)</t>
+        </is>
+      </c>
+      <c r="M74" t="b">
+        <v>1</v>
+      </c>
+      <c r="N74" t="b">
+        <v>1</v>
+      </c>
+      <c r="O74" t="n">
+        <v>1</v>
+      </c>
+      <c r="P74" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>443.6071</v>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>Watterson | AKW Holdings</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>Watterson (Revolver) | Watterson (TL) | Watterson (Equity) | Watterson (DDTL) | AKW Holdings (Term Loan)</t>
+        </is>
+      </c>
+      <c r="T74" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Watchtower Buyer, LLC</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>consolidated_soi</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Security Match</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Watchtower Buyer, LLC - Unfunded Revolver</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>watchtower buyer</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Watchtower Buyer</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Watchtower Buyer</t>
+        </is>
+      </c>
+      <c r="H75" t="b">
+        <v>1</v>
+      </c>
+      <c r="I75" t="b">
+        <v>1</v>
+      </c>
+      <c r="J75" t="n">
+        <v>1</v>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Watchtower Buyer (Revolver)</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>Watchtower Buyer (Revolver)</t>
+        </is>
+      </c>
+      <c r="M75" t="b">
+        <v>1</v>
+      </c>
+      <c r="N75" t="b">
+        <v>1</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>349.183</v>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>Watchtower Buyer | Watchtower | Watchtower Holdings | APHIX | Carisk Partners</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>Watchtower Buyer (Revolver) | Watchtower Buyer (TL) | Watchtower Buyer (DDTL) | Watchtower (Revolver) | Carisk Partners (Revolver)</t>
+        </is>
+      </c>
+      <c r="T75" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>UniVista Insurance</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>consolidated_soi</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Security Match</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Univista Insurance - Common Equity</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>univista insurance</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>UniVista</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>UniVista</t>
+        </is>
+      </c>
+      <c r="H76" t="b">
+        <v>1</v>
+      </c>
+      <c r="I76" t="b">
+        <v>1</v>
+      </c>
+      <c r="J76" t="n">
+        <v>1</v>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>UniVista (Equity)</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>UniVista (Equity)</t>
+        </is>
+      </c>
+      <c r="M76" t="b">
+        <v>1</v>
+      </c>
+      <c r="N76" t="b">
+        <v>1</v>
+      </c>
+      <c r="O76" t="n">
+        <v>1</v>
+      </c>
+      <c r="P76" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>506.8933</v>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>UniVista</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>UniVista (Equity)</t>
+        </is>
+      </c>
+      <c r="T76" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Project Granite Buyer, Inc.</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>consolidated_soi</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Company Match</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Project Granite Buyer, Inc. - Unfunded Term Loan</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>project granite buyer</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Tranzact</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Tranzact</t>
+        </is>
+      </c>
+      <c r="H77" t="b">
+        <v>1</v>
+      </c>
+      <c r="I77" t="b">
+        <v>1</v>
+      </c>
+      <c r="J77" t="n">
+        <v>1</v>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Tranzact (Term Loan)</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>Tranzact (Term Loan)</t>
+        </is>
+      </c>
+      <c r="M77" t="b">
+        <v>1</v>
+      </c>
+      <c r="N77" t="b">
+        <v>1</v>
+      </c>
+      <c r="O77" t="n">
+        <v>1</v>
+      </c>
+      <c r="P77" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>420.1781</v>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>Tranzact | Watchtower Buyer | APHIX | Carisk Partners | Connatix</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>Tranzact (Term Loan) | Tranzact (DDTL) | Tranzact (Revolver) | Watchtower Buyer (TL) | Watchtower Buyer (DDTL)</t>
+        </is>
+      </c>
+      <c r="T77" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>TransGo, LLC</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>consolidated_soi</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Company Match</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Aftermarket Drivetrain Products Holdings, LLC - Common Equity</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>transgo</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>TransGo</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>TransGo</t>
+        </is>
+      </c>
+      <c r="H78" t="b">
+        <v>1</v>
+      </c>
+      <c r="I78" t="b">
+        <v>1</v>
+      </c>
+      <c r="J78" t="n">
+        <v>1</v>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>TransGo (Equity)</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>TransGo (Equity)</t>
+        </is>
+      </c>
+      <c r="M78" t="b">
+        <v>1</v>
+      </c>
+      <c r="N78" t="b">
+        <v>1</v>
+      </c>
+      <c r="O78" t="n">
+        <v>1</v>
+      </c>
+      <c r="P78" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>495.3074</v>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>TransGo</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>TransGo (Equity) | TransGo (TL) | TransGo (Revolver)</t>
+        </is>
+      </c>
+      <c r="T78" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>STG Distribution, LLC</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>consolidated_soi</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Security Match</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>STG Distribution, LLC - Second Out Term Loans</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>stg distribution</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>STG Logistics</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>STG Logistics</t>
+        </is>
+      </c>
+      <c r="H79" t="b">
+        <v>1</v>
+      </c>
+      <c r="I79" t="b">
+        <v>1</v>
+      </c>
+      <c r="J79" t="n">
+        <v>1</v>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>STG (TL)</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>STG (Second Out Term Loans)</t>
+        </is>
+      </c>
+      <c r="M79" t="b">
+        <v>0</v>
+      </c>
+      <c r="N79" t="b">
+        <v>1</v>
+      </c>
+      <c r="O79" t="n">
+        <v>3</v>
+      </c>
+      <c r="P79" t="n">
+        <v>0.7583</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>581.7938</v>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>STG Logistics | Plimpton &amp; Hills | BlackHawk Industrial | WhiteHawk Industrial</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>STG (Second Out Term Loans) | STG (First Out New Money Term Loans) | STG (TL) | BlackHawk Industrial (Incremental TL) | BlackHawk Industrial (TL)</t>
+        </is>
+      </c>
+      <c r="T79" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Rural Sourcing Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>consolidated_soi</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Company Knowledge Match</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Rural Sourcing Holdings, Inc. - Unfunded Revolver</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>rural sourcing holdings</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Sparq</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Sparq</t>
+        </is>
+      </c>
+      <c r="H80" t="b">
+        <v>1</v>
+      </c>
+      <c r="I80" t="b">
+        <v>1</v>
+      </c>
+      <c r="J80" t="n">
+        <v>1</v>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Sparq (Revolver)</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>Sparq (TL)</t>
+        </is>
+      </c>
+      <c r="M80" t="b">
+        <v>0</v>
+      </c>
+      <c r="N80" t="b">
+        <v>0</v>
+      </c>
+      <c r="O80" t="n">
+        <v>6</v>
+      </c>
+      <c r="P80" t="n">
+        <v>0.9499</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>273.1139</v>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>Sparq | AKW Holdings</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>Sparq (TL) | AKW Holdings (Term Loan) | AKW Holdings (Common) | Sparq (Common Equity) | Sparq (DDTL)</t>
+        </is>
+      </c>
+      <c r="T80" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Schlesinger Global, Inc.</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>consolidated_soi</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Company Match</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Gauge Schlesinger Coinvest, LLC - Common Equity</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>schlesinger global</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Schlesinger</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Schlesinger</t>
+        </is>
+      </c>
+      <c r="H81" t="b">
+        <v>1</v>
+      </c>
+      <c r="I81" t="b">
+        <v>1</v>
+      </c>
+      <c r="J81" t="n">
+        <v>1</v>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Schlesinger (Equity)</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>Schlesinger (Equity)</t>
+        </is>
+      </c>
+      <c r="M81" t="b">
+        <v>1</v>
+      </c>
+      <c r="N81" t="b">
+        <v>1</v>
+      </c>
+      <c r="O81" t="n">
+        <v>1</v>
+      </c>
+      <c r="P81" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>522.6645</v>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>Schlesinger | Global | Insight Global | UniTek | Premiere Global Services (PGi)</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>Schlesinger (Equity) | Schlesinger (Term Loan) | UniTek (Common Eq) | Premiere Global Services (PGi) (Term Loan) | Premiere Global Services (PGi) (Priority Revolver)</t>
+        </is>
+      </c>
+      <c r="T81" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Pacific Purchaser, LLC</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>consolidated_soi</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Company Match</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Pacific Purchaser, LLC - Unfunded Revolver</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>pacific purchaser</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>ProSearch</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>ProSearch</t>
+        </is>
+      </c>
+      <c r="H82" t="b">
+        <v>1</v>
+      </c>
+      <c r="I82" t="b">
+        <v>1</v>
+      </c>
+      <c r="J82" t="n">
+        <v>1</v>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>ProSearch (TL)</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>ProSearch (Revolver)</t>
+        </is>
+      </c>
+      <c r="M82" t="b">
+        <v>0</v>
+      </c>
+      <c r="N82" t="b">
+        <v>1</v>
+      </c>
+      <c r="O82" t="n">
+        <v>2</v>
+      </c>
+      <c r="P82" t="n">
+        <v>0.9647</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>310.9658</v>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>ProSearch | Peninsula Pacific Entertainment | None | STG Logistics | Adweek</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>ProSearch (Revolver) | ProSearch (TL) | ProSearch (DDTL) | Colonial Downs (DDTL) | Datalot (Revolver)</t>
+        </is>
+      </c>
+      <c r="T82" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Aechelon InvestCo, LP - Common Equity</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
           <t>daily_long_short</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Security Match</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Aechelon InvestCo, LP - Common Equity</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>aechelon investco common equity</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Aechelon</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Aechelon</t>
+        </is>
+      </c>
+      <c r="H83" t="b">
+        <v>1</v>
+      </c>
+      <c r="I83" t="b">
+        <v>1</v>
+      </c>
+      <c r="J83" t="n">
+        <v>1</v>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Aechelon (Common Equity)</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>Aechelon (Common Equity)</t>
+        </is>
+      </c>
+      <c r="M83" t="b">
+        <v>1</v>
+      </c>
+      <c r="N83" t="b">
+        <v>1</v>
+      </c>
+      <c r="O83" t="n">
+        <v>1</v>
+      </c>
+      <c r="P83" t="n">
+        <v>1.106</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>323.1901</v>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>Aechelon | GCOM | QuantiTech | Federal Advisory Partners | Athene</t>
+        </is>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>Aechelon (Common Equity) | GCOM (Common Equity) | QuantiTech (Common Equity I) | Federal Advisory Partners (Common Equity) | QuantiTech (Common Equity II)</t>
+        </is>
+      </c>
+      <c r="T83" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>TCG 3.0 Jogger Co-Invest, LP - Common Equity</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>daily_long_short</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
         <is>
           <t>Company Match</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>TCG 3.0 Jogger Co-Invest, LP - Common Equity</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>tcg 3 0 jogger invest common equity</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>BiggerPockets</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>BiggerPockets</t>
+        </is>
+      </c>
+      <c r="H84" t="b">
+        <v>1</v>
+      </c>
+      <c r="I84" t="b">
+        <v>1</v>
+      </c>
+      <c r="J84" t="n">
+        <v>1</v>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>BiggerPockets (Common Equity)</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>BiggerPockets (Common Equity)</t>
+        </is>
+      </c>
+      <c r="M84" t="b">
+        <v>1</v>
+      </c>
+      <c r="N84" t="b">
+        <v>1</v>
+      </c>
+      <c r="O84" t="n">
+        <v>1</v>
+      </c>
+      <c r="P84" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>686.5144</v>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>BiggerPockets | 48Forty | Harris | Aechelon | Altamira</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>BiggerPockets (Common Equity) | BiggerPockets (TL) | BiggerPockets (Revolver) | 48Forty (Common Equity) | 48Forty (Term Loan)</t>
+        </is>
+      </c>
+      <c r="T84" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Knexus Holdco, LLC - Preferred Equity</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>daily_long_short</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Company Knowledge Match</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Knexus Holdco, LLC - Preferred Equity</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>knexus holdco preferred equity</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>C5MI</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Harris</t>
+        </is>
+      </c>
+      <c r="H85" t="b">
+        <v>0</v>
+      </c>
+      <c r="I85" t="b">
+        <v>1</v>
+      </c>
+      <c r="J85" t="n">
+        <v>3</v>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>C5MI (Preferred Equity)</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>C5MI (Preferred Equity)</t>
+        </is>
+      </c>
+      <c r="M85" t="b">
+        <v>1</v>
+      </c>
+      <c r="N85" t="b">
+        <v>1</v>
+      </c>
+      <c r="O85" t="n">
+        <v>1</v>
+      </c>
+      <c r="P85" t="n">
+        <v>0.7903</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>263.9853</v>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>Harris | BioDerm | C5MI | Cascade | Northwinds</t>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>C5MI (Preferred Equity) | Harris (Preferred Equity) | BioDerm (Preferred Equity) | Cascade (Preferred Equity) | C5MI (Common Equity)</t>
+        </is>
+      </c>
+      <c r="T85" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Connatix Parent, LLC - Common Equity</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>daily_long_short</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Security Match</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Connatix Parent, LLC - Common Equity</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>connatix parent common equity</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Connatix</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Connatix</t>
+        </is>
+      </c>
+      <c r="H86" t="b">
+        <v>1</v>
+      </c>
+      <c r="I86" t="b">
+        <v>1</v>
+      </c>
+      <c r="J86" t="n">
+        <v>1</v>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Connatix (Common Equity)</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>Connatix (Common Equity)</t>
+        </is>
+      </c>
+      <c r="M86" t="b">
+        <v>1</v>
+      </c>
+      <c r="N86" t="b">
+        <v>1</v>
+      </c>
+      <c r="O86" t="n">
+        <v>1</v>
+      </c>
+      <c r="P86" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>409.2311</v>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>Connatix | Rosco | NORA | RTIC | Rancho Medical</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>Connatix (Common Equity) | Rosco (Common Equity) | NORA (Common Equity) | RTIC (Common Equity) | Rancho (Equity)</t>
+        </is>
+      </c>
+      <c r="T86" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Connatix Parent, LLC - Preferred Equity</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>daily_long_short</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Security Match</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Connatix Parent, LLC - Preferred Equity</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>connatix parent preferred equity</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Connatix</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Connatix</t>
+        </is>
+      </c>
+      <c r="H87" t="b">
+        <v>1</v>
+      </c>
+      <c r="I87" t="b">
+        <v>1</v>
+      </c>
+      <c r="J87" t="n">
+        <v>1</v>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Connatix (Common Equity)</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>Connatix (Common Equity)</t>
+        </is>
+      </c>
+      <c r="M87" t="b">
+        <v>1</v>
+      </c>
+      <c r="N87" t="b">
+        <v>1</v>
+      </c>
+      <c r="O87" t="n">
+        <v>1</v>
+      </c>
+      <c r="P87" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>345.5332</v>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>Connatix | RTIC | Vertex | Rancho Medical | Rosco</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>Connatix (Common Equity) | RTIC (Preferred Equity B) | RTIC (Preferred Equity A) | Vertex (Preferred Equity) | RTIC (Preferred Equity C)</t>
+        </is>
+      </c>
+      <c r="T87" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>RFMG Parent, LP - Common Equity</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>daily_long_short</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Company Match</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>RFMG Parent, LP - Common Equity</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>rfmg parent common equity</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Rancho Medical</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Rancho Medical</t>
+        </is>
+      </c>
+      <c r="H88" t="b">
+        <v>1</v>
+      </c>
+      <c r="I88" t="b">
+        <v>1</v>
+      </c>
+      <c r="J88" t="n">
+        <v>1</v>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Rancho (Equity)</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>Rancho (Equity)</t>
+        </is>
+      </c>
+      <c r="M88" t="b">
+        <v>1</v>
+      </c>
+      <c r="N88" t="b">
+        <v>1</v>
+      </c>
+      <c r="O88" t="n">
+        <v>1</v>
+      </c>
+      <c r="P88" t="n">
+        <v>1.1831</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>337.9748</v>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>Rancho Medical | Connatix | Rosco | NORA | RTIC</t>
+        </is>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>Rancho (Equity) | Connatix (Common Equity) | Rosco (Common Equity) | NORA (Common Equity) | RTIC (Common Equity)</t>
+        </is>
+      </c>
+      <c r="T88" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Project Granite Holdings, LLC - Common Equity</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>daily_long_short</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Company Match</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Project Granite Holdings, LLC - Common Equity</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>project granite holdings common equity</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Tranzact</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Tranzact</t>
+        </is>
+      </c>
+      <c r="H89" t="b">
+        <v>1</v>
+      </c>
+      <c r="I89" t="b">
+        <v>1</v>
+      </c>
+      <c r="J89" t="n">
+        <v>1</v>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Tranzact (Common Equity)</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>Tranzact (Common Equity)</t>
+        </is>
+      </c>
+      <c r="M89" t="b">
+        <v>1</v>
+      </c>
+      <c r="N89" t="b">
+        <v>1</v>
+      </c>
+      <c r="O89" t="n">
+        <v>1</v>
+      </c>
+      <c r="P89" t="n">
+        <v>1.1919</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>459.7261</v>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>Tranzact | 48Forty | Harris | Aechelon | AKW Holdings</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>Tranzact (Common Equity) | Tranzact (DDTL) | Tranzact (Revolver) | Tranzact (Term Loan) | AKW Holdings (Common)</t>
+        </is>
+      </c>
+      <c r="T89" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>NXOF Holdings, Inc. - Common Equity</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>daily_long_short</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Company Match</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NXOF Holdings, Inc. - Common Equity</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>nxof holdings common equity</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Tyto Athene</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Tyto Athene</t>
+        </is>
+      </c>
+      <c r="H90" t="b">
+        <v>1</v>
+      </c>
+      <c r="I90" t="b">
+        <v>1</v>
+      </c>
+      <c r="J90" t="n">
+        <v>1</v>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Tyto Athene (Equity)</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>Tyto Athene (Equity)</t>
+        </is>
+      </c>
+      <c r="M90" t="b">
+        <v>1</v>
+      </c>
+      <c r="N90" t="b">
+        <v>1</v>
+      </c>
+      <c r="O90" t="n">
+        <v>1</v>
+      </c>
+      <c r="P90" t="n">
+        <v>1.0656</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>254.6661</v>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>Tyto Athene | 48Forty | Harris | Aechelon | AKW Holdings</t>
+        </is>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>Tyto Athene (Equity) | AKW Holdings (Common) | Tyto Athene (Pref) | 48Forty (Common Equity) | Harris (Common Equity)</t>
+        </is>
+      </c>
+      <c r="T90" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>NXOF Holdings, Inc. - Preferred Equity</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>daily_long_short</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Company Match</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NXOF Holdings, Inc. - Preferred Equity</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>nxof holdings preferred equity</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Tyto Athene</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Tyto Athene</t>
+        </is>
+      </c>
+      <c r="H91" t="b">
+        <v>1</v>
+      </c>
+      <c r="I91" t="b">
+        <v>1</v>
+      </c>
+      <c r="J91" t="n">
+        <v>1</v>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Tyto Athene (Pref)</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>Tyto Athene (Pref)</t>
+        </is>
+      </c>
+      <c r="M91" t="b">
+        <v>1</v>
+      </c>
+      <c r="N91" t="b">
+        <v>1</v>
+      </c>
+      <c r="O91" t="n">
+        <v>1</v>
+      </c>
+      <c r="P91" t="n">
+        <v>1.0656</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>243.8015</v>
+      </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>Tyto Athene | Harris | BioDerm | C5MI | AKW Holdings</t>
+        </is>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>Tyto Athene (Pref) | BioDerm (Preferred Equity) | Tyto Athene (Equity) | Harris (Preferred Equity) | C5MI (Preferred Equity)</t>
+        </is>
+      </c>
+      <c r="T91" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>TWD Parent Holdings, LLC - Common Equity</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>daily_long_short</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Company Match</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>TWD Parent Holdings, LLC - Common Equity</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>twd parent holdings common equity</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
         <is>
           <t>Vertex</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Vertex</t>
+        </is>
+      </c>
+      <c r="H92" t="b">
+        <v>1</v>
+      </c>
+      <c r="I92" t="b">
+        <v>1</v>
+      </c>
+      <c r="J92" t="n">
+        <v>1</v>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Vertex (Common Equity)</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>Vertex (Common Equity)</t>
+        </is>
+      </c>
+      <c r="M92" t="b">
+        <v>1</v>
+      </c>
+      <c r="N92" t="b">
+        <v>1</v>
+      </c>
+      <c r="O92" t="n">
+        <v>1</v>
+      </c>
+      <c r="P92" t="n">
+        <v>1.1278</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>344.0517</v>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>Vertex | Connatix | Rosco | NORA | RTIC</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>Vertex (Common Equity) | Vertex (Preferred Equity) | NORA (Common Equity) | RTIC (Common Equity) | Connatix (Common Equity)</t>
+        </is>
+      </c>
+      <c r="T92" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>TWD Parent Holdings, LLC - Preferred Equity</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>daily_long_short</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Company Match</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>TWD Parent Holdings, LLC - Preferred Equity</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>twd parent holdings preferred equity</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Vertex</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Vertex</t>
+        </is>
+      </c>
+      <c r="H93" t="b">
+        <v>1</v>
+      </c>
+      <c r="I93" t="b">
+        <v>1</v>
+      </c>
+      <c r="J93" t="n">
+        <v>1</v>
+      </c>
+      <c r="K93" t="inlineStr">
         <is>
           <t>Vertex (Preferred Equity)</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Vertex</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Vertex (Term Loan)</t>
-        </is>
-      </c>
-      <c r="H50" t="b">
-        <v>1</v>
-      </c>
-      <c r="I50" t="b">
-        <v>1</v>
-      </c>
-      <c r="J50" t="n">
-        <v>1</v>
-      </c>
-      <c r="K50" t="b">
-        <v>0</v>
-      </c>
-      <c r="L50" t="b">
-        <v>1</v>
-      </c>
-      <c r="M50" t="n">
-        <v>5</v>
-      </c>
-      <c r="N50" t="n">
-        <v>1</v>
-      </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>Vertex</t>
-        </is>
-      </c>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>Vertex (Term Loan) | Vertex (Revolver) | Vertex (DDTL) | Vertex (Common Equity) | Vertex (Preferred Equity)</t>
-        </is>
-      </c>
-      <c r="Q50" t="b">
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>Vertex (Preferred Equity)</t>
+        </is>
+      </c>
+      <c r="M93" t="b">
+        <v>1</v>
+      </c>
+      <c r="N93" t="b">
+        <v>1</v>
+      </c>
+      <c r="O93" t="n">
+        <v>1</v>
+      </c>
+      <c r="P93" t="n">
+        <v>1.1329</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>390.6513</v>
+      </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>Vertex | RTIC | Rancho Medical | Connatix | Rosco</t>
+        </is>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>Vertex (Preferred Equity) | RTIC (Preferred Equity B) | RTIC (Preferred Equity A) | Vertex (Common Equity) | RTIC (Preferred Equity C)</t>
+        </is>
+      </c>
+      <c r="T93" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Watchtower Holdings, LLC - Common Equity</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>daily_long_short</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Security Match</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Watchtower Holdings, LLC - Common Equity</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>watchtower holdings common equity</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Watchtower Holdings</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Watchtower Holdings</t>
+        </is>
+      </c>
+      <c r="H94" t="b">
+        <v>1</v>
+      </c>
+      <c r="I94" t="b">
+        <v>1</v>
+      </c>
+      <c r="J94" t="n">
+        <v>1</v>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Watchtower Holding (Common Equity)</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>Watchtower Holding (Common Equity)</t>
+        </is>
+      </c>
+      <c r="M94" t="b">
+        <v>1</v>
+      </c>
+      <c r="N94" t="b">
+        <v>1</v>
+      </c>
+      <c r="O94" t="n">
+        <v>1</v>
+      </c>
+      <c r="P94" t="n">
+        <v>1.1889</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>333.6397</v>
+      </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>Watchtower Holdings | Watchtower | Watchtower Buyer | 48Forty | AKW Holdings</t>
+        </is>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>Watchtower Holding (Common Equity) | AKW Holdings (Common) | 48Forty (Common Equity) | 48Forty (Term Loan) | AKW Holdings (Term Loan)</t>
+        </is>
+      </c>
+      <c r="T94" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>HV Watterson Holdings, LLC - Common Equity</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>daily_long_short</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Security Match</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>HV Watterson Holdings, LLC - Common Equity</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>hv watterson holdings common equity</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Watterson</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Watterson</t>
+        </is>
+      </c>
+      <c r="H95" t="b">
+        <v>1</v>
+      </c>
+      <c r="I95" t="b">
+        <v>1</v>
+      </c>
+      <c r="J95" t="n">
+        <v>1</v>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Watterson (Equity)</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>Watterson (Equity)</t>
+        </is>
+      </c>
+      <c r="M95" t="b">
+        <v>1</v>
+      </c>
+      <c r="N95" t="b">
+        <v>1</v>
+      </c>
+      <c r="O95" t="n">
+        <v>1</v>
+      </c>
+      <c r="P95" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>471.985</v>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>Watterson | 48Forty | Harris | Aechelon | AKW Holdings</t>
+        </is>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>Watterson (Equity) | Watterson (TL) | Watterson (Revolver) | Watterson (DDTL) | AKW Holdings (Common)</t>
+        </is>
+      </c>
+      <c r="T95" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4010,72 +8382,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Source File Type</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Fam Top-1 Pass</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Fam Top-1 Fail</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Fam Top-1 %</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Fam Top-5 Pass</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Fam Top-5 Fail</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Fam Top-5 %</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Sec Top-1 Pass</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Sec Top-1 Fail</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Sec Top-1 %</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Sec Top-5 Pass</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Sec Top-5 Fail</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Sec Top-5 %</t>
         </is>
@@ -4088,10 +8460,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -4102,7 +8474,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -4113,25 +8485,25 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J2" t="n">
         <v>3</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>88.9%</t>
         </is>
       </c>
     </row>
@@ -4142,21 +8514,21 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>92.3%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -4167,25 +8539,25 @@
         </is>
       </c>
       <c r="I3" t="n">
+        <v>13</v>
+      </c>
+      <c r="J3" t="n">
         <v>0</v>
       </c>
-      <c r="J3" t="n">
-        <v>7</v>
-      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="M3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -4196,10 +8568,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -4210,7 +8582,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -4221,18 +8593,18 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="J4" t="n">
         <v>3</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>78.6%</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -4275,14 +8647,14 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -4304,50 +8676,50 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="C6" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>92.9%</t>
+          <t>87.1%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>93.5%</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>74.2%</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>80.6%</t>
         </is>
       </c>
     </row>
@@ -4358,50 +8730,50 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>13</v>
+      </c>
+      <c r="D7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>72.2%</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>14</v>
+      </c>
+      <c r="G7" t="n">
+        <v>4</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>77.8%</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>11</v>
+      </c>
+      <c r="J7" t="n">
         <v>7</v>
       </c>
-      <c r="C7" t="n">
-        <v>7</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>7</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>61.1%</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>14</v>
+      </c>
+      <c r="M7" t="n">
         <v>4</v>
       </c>
-      <c r="J7" t="n">
-        <v>3</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>57.1%</t>
-        </is>
-      </c>
-      <c r="L7" t="n">
-        <v>7</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>77.8%</t>
         </is>
       </c>
     </row>

--- a/evaluation_results.xlsx
+++ b/evaluation_results.xlsx
@@ -584,19 +584,19 @@
         <v>1</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9293</v>
+        <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>263.8432</v>
+        <v>1</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>360DG | Watchtower Buyer | Marketplace Events | APRA | APHIX</t>
+          <t>360DG</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>360DG (Term Loan) | 360DG (DDTL B) | 360DG (DDTL A) | 360DG (Revolver) | 360DG (Common Equity)</t>
+          <t>360DG (Term Loan)</t>
         </is>
       </c>
       <c r="T2" t="b">
@@ -671,16 +671,16 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>286.0734</v>
+        <v>1</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>48Forty | Smartronix / Trident | Altamira | Douglas | Engine &amp; Transmission Exchange</t>
+          <t>48Forty</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>48Forty (Common Equity) | 48Forty (Term Loan) | Smartronix / Trident (TL) | 48Forty (DDTL) | Altamira (Common Equity)</t>
+          <t>48Forty (Common Equity)</t>
         </is>
       </c>
       <c r="T3" t="b">
@@ -755,16 +755,16 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>463.4119</v>
+        <v>1</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Ad.net | Arcfield | C5MI | Duggal Visual Solutions | GCOM</t>
+          <t>Ad.net</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>Ad.net (Term Loan) | Ad.net (Revolver) | Ad.net (Common Equity) | Ad.net (Preferred Equity) | Arcfield (Term Loan)</t>
+          <t>Ad.net (Term Loan)</t>
         </is>
       </c>
       <c r="T4" t="b">
@@ -839,16 +839,16 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>425.9401</v>
+        <v>1</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Aechelon | Intellectual Technology | Sabel Systems</t>
+          <t>Aechelon</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>Aechelon (Term Loan) | Aechelon (Revolver) | Aechelon (Common Equity) | Intellectual Technology, Inc. (TL) | Sabel Systems (Term Loan)</t>
+          <t>Aechelon (Term Loan)</t>
         </is>
       </c>
       <c r="T5" t="b">
@@ -920,19 +920,19 @@
         <v>1</v>
       </c>
       <c r="P6" t="n">
-        <v>0.8579</v>
+        <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>314.2243</v>
+        <v>1</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>AFC Acquisitions | Watchtower Holdings</t>
+          <t>AFC Acquisitions</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>AFC Industries (DDTL) | AFC Industries (Common Equity) | AFC Industries (TL) | Watchtower Holding (Common Equity)</t>
+          <t>AFC Industries (DDTL)</t>
         </is>
       </c>
       <c r="T6" t="b">
@@ -1004,19 +1004,19 @@
         <v>1</v>
       </c>
       <c r="P7" t="n">
-        <v>0.8579</v>
+        <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>230.7481</v>
+        <v>1</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>AFC Acquisitions | Watchtower Holdings</t>
+          <t>AFC Acquisitions</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>AFC Industries (TL) | AFC Industries (DDTL) | AFC Industries (Common Equity) | Watchtower Holding (Common Equity)</t>
+          <t>AFC Industries (TL)</t>
         </is>
       </c>
       <c r="T7" t="b">
@@ -1091,16 +1091,16 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>621.1671</v>
+        <v>1</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>BBB Industries | STG Logistics | Adweek | Aspect Software | Health-E Commerce</t>
+          <t>BBB Industries</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>BBB Industries (First Lien Term Loan) | BBB Industries (Second Lien Term Loan) | STG (TL) | Adweek (Term Loan) | Adweek (DDTL)</t>
+          <t>BBB Industries (First Lien Term Loan)</t>
         </is>
       </c>
       <c r="T8" t="b">
@@ -1175,7 +1175,7 @@
         <v>0.9023</v>
       </c>
       <c r="Q9" t="n">
-        <v>423.274</v>
+        <v>605.7479</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -1259,16 +1259,16 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>344.7419</v>
+        <v>1</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>Bluebird | The Creative Group | The Original Cakerie | Simplicity Group | None</t>
+          <t>Bluebird</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>Bluebird (Term Loan) | Bluebird (Revolver) | Simplicity Group (TL) | The Creative Group (Term Loan) | Simplicity Group (DDTL)</t>
+          <t>Bluebird (Term Loan)</t>
         </is>
       </c>
       <c r="T10" t="b">
@@ -1340,19 +1340,19 @@
         <v>1</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9736</v>
+        <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>587.9376</v>
+        <v>1</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>BlueHalo | API Technologies | Altamira | Nuvei | Lynx Technologies</t>
+          <t>BlueHalo</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>BlueHalo (Term Loan) | API Technologies (TL) | API Technologies (Revolver) | Altamira (Common Equity) | Altamira (TL)</t>
+          <t>BlueHalo (Term Loan)</t>
         </is>
       </c>
       <c r="T11" t="b">
@@ -1392,51 +1392,55 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>BlueHalo</t>
         </is>
       </c>
       <c r="H12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="b">
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
           <t>BlueHalo (Term Loan)</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>BlueHalo (Term Loan)</t>
+        </is>
+      </c>
       <c r="M12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O12" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="P12" t="n">
-        <v>0.8575</v>
+        <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>Global | BlueHalo | Insight Global | Schlesinger | UniTek</t>
+          <t>BlueHalo</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>Schlesinger (Term Loan) | Schlesinger (Equity) | Global (Term Loan) | Insight Global (TL) | Insight Global (Rev)</t>
+          <t>BlueHalo (Term Loan)</t>
         </is>
       </c>
       <c r="T12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1507,16 +1511,16 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>465.409</v>
+        <v>1</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>By Light | Integrated Data Services | Any Hour Services | Applied Technical Services | IDC Infusion Services</t>
+          <t>By Light</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>By Light (Revolver) | By Light (Term Loan) | By Light (DDTL) | By Light (Equity) | By Light (HoldCo Note)</t>
+          <t>By Light (Revolver)</t>
         </is>
       </c>
       <c r="T13" t="b">
@@ -1591,7 +1595,7 @@
         <v>0.9533</v>
       </c>
       <c r="Q14" t="n">
-        <v>247.061</v>
+        <v>345.8854</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
@@ -1600,7 +1604,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>Centauri Health (TL) | Centauri Health (Revolver) | Centauri Health (DDTL) | Watchtower Buyer (Revolver) | Carisk Partners (Revolver)</t>
+          <t>Centauri Health (TL) | Centauri Health (Revolver) | Watchtower Buyer (Revolver) | Centauri Health (DDTL) | Carisk Partners (Revolver)</t>
         </is>
       </c>
       <c r="T14" t="b">
@@ -1675,16 +1679,16 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>392.2633</v>
+        <v>1</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>Dr. Squatch | Dr. Scholl's</t>
+          <t>Dr. Squatch</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>Dr. Squatch (Term Loan) | Dr. Squatch (Revolver) | Dr. Squatch (DDTL) | Dr. Scholl's (Term Loan) | Dr. Scholl's (Revolver)</t>
+          <t>Dr. Squatch (Term Loan)</t>
         </is>
       </c>
       <c r="T15" t="b">
@@ -1756,19 +1760,19 @@
         <v>1</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9911</v>
+        <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>438.3659</v>
+        <v>1</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>Guild Garage Group | PCS Retirement | Total Pool Care Network</t>
+          <t>Guild Garage Group</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>Guild Garage Group (DDTL) | Guild Garage Group (Term Loan) | TPCN (DDTL) | PCS Retirement (DDTL) | TPCN (Term Loan)</t>
+          <t>Guild Garage Group (DDTL)</t>
         </is>
       </c>
       <c r="T16" t="b">
@@ -1843,16 +1847,16 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>516.9478</v>
+        <v>1</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>Infinity Home Services | United Land Services | Any Hour Services | Applied Technical Services | IDC Infusion Services</t>
+          <t>Infinity Home Services</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>Infinity Home Services (DDTL) | Infinity Home Services (DDTL) CAD | Infinity Home Services (Term Loan) | United Land Services (HoldCo Notes DDTL) | Any Hour Services (DDTL)</t>
+          <t>Infinity Home Services (DDTL)</t>
         </is>
       </c>
       <c r="T17" t="b">
@@ -1924,19 +1928,19 @@
         <v>1</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9896</v>
+        <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>350.5145</v>
+        <v>1</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>Lilly Lashes | APT Healthcare | Zips</t>
+          <t>Lilly Lashes</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>Lilly Lashes (TL) | APT Healthcare (Term Loan) | APT Healthcare (Incr. DDTL) | Zips (New OpCo Term Loan) | APT Healthcare (Common Equity)</t>
+          <t>Lilly Lashes (TL)</t>
         </is>
       </c>
       <c r="T18" t="b">
@@ -2011,16 +2015,16 @@
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>446.1023</v>
+        <v>1</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>Lynx Technologies | PAR Excellence | STG Logistics | Adweek | Aspect Software</t>
+          <t>Lynx Technologies</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>Lynx Technologies (TL) | STG (TL) | Adweek (Term Loan) | Adweek (DDTL) | Aspect Software (Equity)</t>
+          <t>Lynx Technologies (TL)</t>
         </is>
       </c>
       <c r="T19" t="b">
@@ -2092,10 +2096,10 @@
         <v>1</v>
       </c>
       <c r="P20" t="n">
-        <v>0.8696</v>
+        <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>360.7486</v>
+        <v>1</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
@@ -2104,7 +2108,7 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>MeritDirect (Term Loan) | MeritDirect (Common Equity) | MeritDirect (Preferred Equity) | MeritDirect (Revolver)</t>
+          <t>MeritDirect (Term Loan)</t>
         </is>
       </c>
       <c r="T20" t="b">
@@ -2179,7 +2183,7 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>454.5237</v>
+        <v>1</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
@@ -2188,7 +2192,7 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>MeritDirect (Term Loan) | MeritDirect (Common Equity) | MeritDirect (Preferred Equity) | MeritDirect (Revolver)</t>
+          <t>MeritDirect (Term Loan)</t>
         </is>
       </c>
       <c r="T21" t="b">
@@ -2245,19 +2249,25 @@
           <t>OSG (Common Equity)</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>U.S. Well (Class A)</t>
+        </is>
+      </c>
       <c r="M22" t="b">
         <v>0</v>
       </c>
       <c r="N22" t="b">
-        <v>0</v>
-      </c>
-      <c r="O22" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="O22" t="n">
+        <v>5</v>
+      </c>
       <c r="P22" t="n">
-        <v>0.8529</v>
+        <v>0.8549</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>85.36020000000001</v>
       </c>
       <c r="R22" t="inlineStr">
         <is>
@@ -2266,11 +2276,11 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>A1 Garage (DDTL) | AKW Holdings (Term Loan) | AKW Holdings (Common) | Learning Care Group (Common) | CEA (Common)</t>
+          <t>U.S. Well (Class A) | Imagine Topco. L.P. (Preferred Equity - Series A) | U.S. Well (Class B) | Superior (Preferred A) | OSG (Common Equity)</t>
         </is>
       </c>
       <c r="T22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -2323,9 +2333,13 @@
           <t>Pragmatic Institute (Common)</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Pragmatic Institute (Common)</t>
+        </is>
+      </c>
       <c r="M23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N23" t="b">
         <v>1</v>
@@ -2337,7 +2351,7 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23" t="inlineStr">
         <is>
@@ -2346,11 +2360,11 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>Pragmatic Institute (Common) | Pragmatic Institute (TL) | Pragmatic Institute (Revolver) | Pragmatic Institute (DDTL)</t>
+          <t>Pragmatic Institute (Common)</t>
         </is>
       </c>
       <c r="T23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -2421,7 +2435,7 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>423.655</v>
+        <v>1</v>
       </c>
       <c r="R24" t="inlineStr">
         <is>
@@ -2430,7 +2444,7 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>C&amp;K Paving Contractors (Term Loan) | C&amp;K Paving Contractors (DDTL) | C&amp;K Paving Contractors (Common Equity)</t>
+          <t>C&amp;K Paving Contractors (Term Loan)</t>
         </is>
       </c>
       <c r="T24" t="b">
@@ -2496,19 +2510,19 @@
       </c>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="n">
-        <v>0.9533</v>
+        <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>293.4885</v>
+        <v>1</v>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>Centauri Health | Watchtower Buyer | APHIX | Carisk Partners | Connatix</t>
+          <t>Centauri Health</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>Centauri Health (TL) | Centauri Health (DDTL) | Centauri Health (Revolver) | Watchtower Buyer (TL) | Watchtower Buyer (DDTL)</t>
+          <t>Centauri Health (TL)</t>
         </is>
       </c>
       <c r="T25" t="b">
@@ -2580,19 +2594,19 @@
         <v>1</v>
       </c>
       <c r="P26" t="n">
-        <v>0.9834000000000001</v>
+        <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>381.1502</v>
+        <v>1</v>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>Commercial Fire Protection | AKW Holdings</t>
+          <t>Commercial Fire Protection</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>Commercial Fire Protection (Term Loan) | Commercial Fire Protection (DDTL) | Commercial Fire Protection (Revolver) | Commercial Fire Protection (Common Equity) | AKW Holdings (Term Loan)</t>
+          <t>Commercial Fire Protection (Term Loan)</t>
         </is>
       </c>
       <c r="T26" t="b">
@@ -2664,19 +2678,19 @@
         <v>1</v>
       </c>
       <c r="P27" t="n">
-        <v>0.8377</v>
+        <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>349.8867</v>
+        <v>1</v>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>Dr. Scholl's | Apex Service Partners | API Technologies | Wheel Pros | Paris Presents</t>
+          <t>Dr. Scholl's</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>Dr. Scholl's (Term Loan) | API Technologies (TL) | API Technologies (Revolver) | Apex (Term Loan) | Apex (Incremental Term Loan)</t>
+          <t>Dr. Scholl's (Term Loan)</t>
         </is>
       </c>
       <c r="T27" t="b">
@@ -2731,7 +2745,11 @@
           <t>Fairbanks Morse Defense (Term Loan)</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>AKW Holdings (Term Loan)</t>
+        </is>
+      </c>
       <c r="M28" t="b">
         <v>0</v>
       </c>
@@ -2740,10 +2758,10 @@
       </c>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="n">
-        <v>0.6244</v>
+        <v>0.6002999999999999</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>36.3303</v>
       </c>
       <c r="R28" t="inlineStr">
         <is>
@@ -2756,7 +2774,7 @@
         </is>
       </c>
       <c r="T28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2827,16 +2845,16 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>466.0747</v>
+        <v>1</v>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>MCR | Research Now/SSI | PhaseWell Research | Pinnacle Clinical Research | CHA Consulting</t>
+          <t>MCR</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>MCR (Term Loan) | MCR (Revolver) | CHA Consulting (TL) | CHA Consulting (DDTL) | Research Now / SSI (Common Equity)</t>
+          <t>MCR (Term Loan)</t>
         </is>
       </c>
       <c r="T29" t="b">
@@ -2907,7 +2925,7 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>324.8272</v>
+        <v>432.755</v>
       </c>
       <c r="R30" t="inlineStr">
         <is>
@@ -2991,7 +3009,7 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>324.8272</v>
+        <v>1</v>
       </c>
       <c r="R31" t="inlineStr">
         <is>
@@ -3069,13 +3087,13 @@
         <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="P32" t="n">
         <v>0.7469</v>
       </c>
       <c r="Q32" t="n">
-        <v>270.9943</v>
+        <v>391.6117</v>
       </c>
       <c r="R32" t="inlineStr">
         <is>
@@ -3084,7 +3102,7 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>APT Healthcare (Incr. DDTL) | Zips (DDTL) | APT Healthcare (Term Loan) | APT Healthcare (Common Equity) | APT Healthcare (Revolver)</t>
+          <t>APT Healthcare (Incr. DDTL) | Zips (DDTL) | APT Healthcare (Term Loan) | Lilly Lashes (TL) | APT Healthcare (Common Equity)</t>
         </is>
       </c>
       <c r="T32" t="b">
@@ -3152,10 +3170,10 @@
       </c>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="n">
-        <v>0.8356</v>
+        <v>0.8365</v>
       </c>
       <c r="Q33" t="n">
-        <v>265.6984</v>
+        <v>394.7907</v>
       </c>
       <c r="R33" t="inlineStr">
         <is>
@@ -3236,10 +3254,10 @@
         <v>1</v>
       </c>
       <c r="P34" t="n">
-        <v>1</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="Q34" t="n">
-        <v>429.7589</v>
+        <v>618.7388999999999</v>
       </c>
       <c r="R34" t="inlineStr">
         <is>
@@ -3323,7 +3341,7 @@
         <v>0.9834000000000001</v>
       </c>
       <c r="Q35" t="n">
-        <v>384.8888</v>
+        <v>537.6147</v>
       </c>
       <c r="R35" t="inlineStr">
         <is>
@@ -3332,7 +3350,7 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>4Wall Entertainment (Term Loan) | 4Wall Entertainment (DDTL) | AKW Holdings (Term Loan) | AKW Holdings (Common) | 4Wall Entertainment (Revolver)</t>
+          <t>4Wall Entertainment (Term Loan) | 4Wall Entertainment (DDTL) | 4Wall Entertainment (Revolver) | AKW Holdings (Term Loan) | AKW Holdings (Common)</t>
         </is>
       </c>
       <c r="T35" t="b">
@@ -3407,7 +3425,7 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>505.2237</v>
+        <v>706.376</v>
       </c>
       <c r="R36" t="inlineStr">
         <is>
@@ -3491,7 +3509,7 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>445.7695</v>
+        <v>658.7212</v>
       </c>
       <c r="R37" t="inlineStr">
         <is>
@@ -3559,23 +3577,23 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>BlueHalo (Term Loan)</t>
+          <t>Global (Term Loan)</t>
         </is>
       </c>
       <c r="M38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N38" t="b">
         <v>1</v>
       </c>
       <c r="O38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P38" t="n">
-        <v>0.8575</v>
+        <v>0.8559</v>
       </c>
       <c r="Q38" t="n">
-        <v>268.6741</v>
+        <v>374.5238</v>
       </c>
       <c r="R38" t="inlineStr">
         <is>
@@ -3584,7 +3602,7 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>BlueHalo (Term Loan) | Global (Term Loan) | Insight Global (TL) | Schlesinger (Term Loan) | Schlesinger (DDTL)</t>
+          <t>Global (Term Loan) | BlueHalo (Term Loan) | Insight Global (TL) | Schlesinger (Term Loan) | Schlesinger (DDTL)</t>
         </is>
       </c>
       <c r="T38" t="b">
@@ -3659,7 +3677,7 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>408.6695</v>
+        <v>571.072</v>
       </c>
       <c r="R39" t="inlineStr">
         <is>
@@ -3743,7 +3761,7 @@
         <v>0.9758</v>
       </c>
       <c r="Q40" t="n">
-        <v>328.7208</v>
+        <v>458.7628</v>
       </c>
       <c r="R40" t="inlineStr">
         <is>
@@ -3827,7 +3845,7 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>437.8485</v>
+        <v>649.8196</v>
       </c>
       <c r="R41" t="inlineStr">
         <is>
@@ -3911,7 +3929,7 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>382.8196</v>
+        <v>538.772</v>
       </c>
       <c r="R42" t="inlineStr">
         <is>
@@ -3991,7 +4009,7 @@
         <v>0.7544</v>
       </c>
       <c r="Q43" t="n">
-        <v>270.3769</v>
+        <v>391.6918</v>
       </c>
       <c r="R43" t="inlineStr">
         <is>
@@ -4000,7 +4018,7 @@
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>US Fertility (DDTL) | TVC (DDTL) | TVC (TL) | US Fertility (Term Loan) | TVC (Equity)</t>
+          <t>US Fertility (DDTL) | TVC (DDTL) | TVC (TL) | US Fertility (Term Loan) | TVC (Revolver)</t>
         </is>
       </c>
       <c r="T43" t="b">
@@ -4071,7 +4089,7 @@
         <v>0.7544</v>
       </c>
       <c r="Q44" t="n">
-        <v>206.7704</v>
+        <v>292.8177</v>
       </c>
       <c r="R44" t="inlineStr">
         <is>
@@ -4080,7 +4098,7 @@
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>TVC (TL) | US Fertility (Term Loan) | US Fertility (DDTL) | TVC (DDTL) | TVC (Equity)</t>
+          <t>TVC (TL) | US Fertility (Term Loan) | US Fertility (DDTL) | TVC (DDTL) | TVC (Revolver)</t>
         </is>
       </c>
       <c r="T44" t="b">
@@ -4155,7 +4173,7 @@
         <v>0.999</v>
       </c>
       <c r="Q45" t="n">
-        <v>419.8098</v>
+        <v>590.5582000000001</v>
       </c>
       <c r="R45" t="inlineStr">
         <is>
@@ -4164,7 +4182,7 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>Aeronix (DDTL) | Aeronix (Common Equity) | AKW Holdings (Term Loan) | Aeronix (TL) | Aeronix (Revolver)</t>
+          <t>Aeronix (DDTL) | Aeronix (Common Equity) | AKW Holdings (Term Loan) | Aeronix (TL) | AKW Holdings (Common)</t>
         </is>
       </c>
       <c r="T45" t="b">
@@ -4239,7 +4257,7 @@
         <v>0.8377</v>
       </c>
       <c r="Q46" t="n">
-        <v>349.8867</v>
+        <v>488.6119</v>
       </c>
       <c r="R46" t="inlineStr">
         <is>
@@ -4323,7 +4341,7 @@
         <v>0.8461</v>
       </c>
       <c r="Q47" t="n">
-        <v>417.5949</v>
+        <v>583.1864</v>
       </c>
       <c r="R47" t="inlineStr">
         <is>
@@ -4400,10 +4418,10 @@
       </c>
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="n">
-        <v>0.549</v>
+        <v>0.5482</v>
       </c>
       <c r="Q48" t="n">
-        <v>157.2802</v>
+        <v>233.9925</v>
       </c>
       <c r="R48" t="inlineStr">
         <is>
@@ -4481,13 +4499,13 @@
         <v>1</v>
       </c>
       <c r="O49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P49" t="n">
-        <v>0.7583</v>
+        <v>0.76</v>
       </c>
       <c r="Q49" t="n">
-        <v>582.932</v>
+        <v>887.1277</v>
       </c>
       <c r="R49" t="inlineStr">
         <is>
@@ -4496,7 +4514,7 @@
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>STG (First Out New Money Term Loans) | STG (TL) | BlackHawk Industrial (Incremental TL) | BlackHawk Industrial (TL) | BlackHawk Industrial (Revolver)</t>
+          <t>STG (First Out New Money Term Loans) | STG (Second Out Term Loans) | STG (TL) | Plimpton &amp; Hills (TL) | Plimpton &amp; Hills (DDTL)</t>
         </is>
       </c>
       <c r="T49" t="b">
@@ -4571,7 +4589,7 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>461.5108</v>
+        <v>667.8467000000001</v>
       </c>
       <c r="R50" t="inlineStr">
         <is>
@@ -4655,7 +4673,7 @@
         <v>0.9834000000000001</v>
       </c>
       <c r="Q51" t="n">
-        <v>384.8888</v>
+        <v>537.6147</v>
       </c>
       <c r="R51" t="inlineStr">
         <is>
@@ -4664,7 +4682,7 @@
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>4Wall Entertainment (Term Loan) | 4Wall Entertainment (DDTL) | AKW Holdings (Term Loan) | AKW Holdings (Common) | 4Wall Entertainment (Revolver)</t>
+          <t>4Wall Entertainment (Term Loan) | 4Wall Entertainment (DDTL) | 4Wall Entertainment (Revolver) | AKW Holdings (Term Loan) | AKW Holdings (Common)</t>
         </is>
       </c>
       <c r="T51" t="b">
@@ -4736,14 +4754,14 @@
         <v>1</v>
       </c>
       <c r="P52" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>459.0776</v>
+        <v>688.3133</v>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>A1 Garage | Guild Garage Group | A2 Garge | None | Omnia</t>
+          <t>A1 Garage | A2 Garge | None | Guild Garage Group | Omnia</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
@@ -4823,7 +4841,7 @@
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>471.6733</v>
+        <v>709.112</v>
       </c>
       <c r="R53" t="inlineStr">
         <is>
@@ -4907,7 +4925,7 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>567.4974999999999</v>
+        <v>820.9715</v>
       </c>
       <c r="R54" t="inlineStr">
         <is>
@@ -4916,7 +4934,7 @@
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>Beta+ (TL) | Altamira (TL) | Nuvei (Term Loan) | API Technologies (TL) | Lynx Technologies (TL)</t>
+          <t>Beta+ (TL) | API Technologies (TL) | Lynx Technologies (TL) | Altamira (TL) | Nuvei (Term Loan)</t>
         </is>
       </c>
       <c r="T54" t="b">
@@ -4991,7 +5009,7 @@
         <v>0.9499</v>
       </c>
       <c r="Q55" t="n">
-        <v>294.7243</v>
+        <v>411.894</v>
       </c>
       <c r="R55" t="inlineStr">
         <is>
@@ -5000,7 +5018,7 @@
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>Sparq (TL) | AKW Holdings (Term Loan) | AKW Holdings (Common) | Sparq (Common Equity) | Sparq (DDTL)</t>
+          <t>Sparq (TL) | AKW Holdings (Term Loan) | AKW Holdings (Common) | Sparq (DDTL) | Sparq (Common Equity)</t>
         </is>
       </c>
       <c r="T55" t="b">
@@ -5075,7 +5093,7 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>670.9543</v>
+        <v>941.8649</v>
       </c>
       <c r="R56" t="inlineStr">
         <is>
@@ -5159,7 +5177,7 @@
         <v>1</v>
       </c>
       <c r="Q57" t="n">
-        <v>634.9015000000001</v>
+        <v>942.0512</v>
       </c>
       <c r="R57" t="inlineStr">
         <is>
@@ -5227,23 +5245,23 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>Comprehensive Rehab Consultants (Term Loan)</t>
+          <t>Comprehensive Rehab Consultants (Revolver)</t>
         </is>
       </c>
       <c r="M58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N58" t="b">
         <v>1</v>
       </c>
       <c r="O58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P58" t="n">
         <v>0.9812</v>
       </c>
       <c r="Q58" t="n">
-        <v>310.6171</v>
+        <v>475.5515</v>
       </c>
       <c r="R58" t="inlineStr">
         <is>
@@ -5252,7 +5270,7 @@
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>Comprehensive Rehab Consultants (Term Loan) | Comprehensive Rehab Consultants (Revolver) | Comprehensive Rehab Consultants (Common Equity) | Confluent Health (TL) | Ro Health (Term Loan)</t>
+          <t>Comprehensive Rehab Consultants (Revolver) | Comprehensive Rehab Consultants (Term Loan) | Comprehensive Rehab Consultants (Common Equity) | Ro Health (Revolver) | Nevada Behavioral Health Systems (Revolver)</t>
         </is>
       </c>
       <c r="T58" t="b">
@@ -5327,7 +5345,7 @@
         <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>536.6979</v>
+        <v>763.0334</v>
       </c>
       <c r="R59" t="inlineStr">
         <is>
@@ -5411,7 +5429,7 @@
         <v>0.8954</v>
       </c>
       <c r="Q60" t="n">
-        <v>356.2388</v>
+        <v>499.4792</v>
       </c>
       <c r="R60" t="inlineStr">
         <is>
@@ -5495,7 +5513,7 @@
         <v>0.9586</v>
       </c>
       <c r="Q61" t="n">
-        <v>553.5313</v>
+        <v>778.59</v>
       </c>
       <c r="R61" t="inlineStr">
         <is>
@@ -5504,7 +5522,7 @@
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>Evans Network (1L) | Evans Network (2L) | Connatix (Term Loan) | Connatix (Revolver) | Connatix (DDTL)</t>
+          <t>Evans Network (1L) | Evans Network (2L) | Planview (TL) | Rosco (Term Loan) | Connatix (Common Equity)</t>
         </is>
       </c>
       <c r="T61" t="b">
@@ -5579,7 +5597,7 @@
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>643.9983</v>
+        <v>924.6727</v>
       </c>
       <c r="R62" t="inlineStr">
         <is>
@@ -5647,23 +5665,23 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>Infinity Home Services (Term Loan)</t>
+          <t>Infinity Home Services (Revolver)</t>
         </is>
       </c>
       <c r="M63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N63" t="b">
         <v>1</v>
       </c>
       <c r="O63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P63" t="n">
         <v>1</v>
       </c>
       <c r="Q63" t="n">
-        <v>461.2423</v>
+        <v>722.9121</v>
       </c>
       <c r="R63" t="inlineStr">
         <is>
@@ -5672,7 +5690,7 @@
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>Infinity Home Services (Term Loan) | Infinity Home Services (Revolver) | Infinity Home Services (Common Equity) | Infinity Home Services (DDTL) | Infinity Home Services (DDTL) CAD</t>
+          <t>Infinity Home Services (Revolver) | Infinity Home Services (Common Equity) | Infinity Home Services (Term Loan) | Infinity Home Services (DDTL) | Infinity Home Services (DDTL) CAD</t>
         </is>
       </c>
       <c r="T63" t="b">
@@ -5747,7 +5765,7 @@
         <v>0.9834000000000001</v>
       </c>
       <c r="Q64" t="n">
-        <v>346.1993</v>
+        <v>484.679</v>
       </c>
       <c r="R64" t="inlineStr">
         <is>
@@ -5831,7 +5849,7 @@
         <v>1</v>
       </c>
       <c r="Q65" t="n">
-        <v>341.2175</v>
+        <v>862.566</v>
       </c>
       <c r="R65" t="inlineStr">
         <is>
@@ -5915,7 +5933,7 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>224.8001</v>
+        <v>543.4204999999999</v>
       </c>
       <c r="R66" t="inlineStr">
         <is>
@@ -5983,7 +6001,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>Any Hour Services (Term Loan)</t>
+          <t>Any Hour Services (Revolver)</t>
         </is>
       </c>
       <c r="M67" t="b">
@@ -5999,7 +6017,7 @@
         <v>1</v>
       </c>
       <c r="Q67" t="n">
-        <v>406.0594</v>
+        <v>991.8898</v>
       </c>
       <c r="R67" t="inlineStr">
         <is>
@@ -6008,7 +6026,7 @@
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>Any Hour Services (Term Loan) | Any Hour Services (Revolver) | Any Hour Services (Common Equity) | Any Hour Services (DDTL) | Any Hour Services (DDTL II)</t>
+          <t>Any Hour Services (Revolver) | Any Hour Services (Term Loan) | Any Hour Services (Common Equity) | Any Hour Services (DDTL) | Any Hour Services (DDTL II)</t>
         </is>
       </c>
       <c r="T67" t="b">
@@ -6067,7 +6085,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>Any Hour Services (Term Loan)</t>
+          <t>Any Hour Services (Revolver)</t>
         </is>
       </c>
       <c r="M68" t="b">
@@ -6083,7 +6101,7 @@
         <v>1</v>
       </c>
       <c r="Q68" t="n">
-        <v>406.0594</v>
+        <v>991.8898</v>
       </c>
       <c r="R68" t="inlineStr">
         <is>
@@ -6092,7 +6110,7 @@
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>Any Hour Services (Term Loan) | Any Hour Services (Revolver) | Any Hour Services (Common Equity) | Any Hour Services (DDTL) | Any Hour Services (DDTL II)</t>
+          <t>Any Hour Services (Revolver) | Any Hour Services (Term Loan) | Any Hour Services (Common Equity) | Any Hour Services (DDTL) | Any Hour Services (DDTL II)</t>
         </is>
       </c>
       <c r="T68" t="b">
@@ -6151,23 +6169,23 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>Cano Health (Term Loan)</t>
+          <t>Cano Health (Equity)</t>
         </is>
       </c>
       <c r="M69" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N69" t="b">
         <v>1</v>
       </c>
       <c r="O69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P69" t="n">
         <v>1</v>
       </c>
       <c r="Q69" t="n">
-        <v>317.6277</v>
+        <v>739.448</v>
       </c>
       <c r="R69" t="inlineStr">
         <is>
@@ -6176,7 +6194,7 @@
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>Cano Health (Term Loan) | Cano Health (Equity) | Ro Health (Revolver) | Confluent Health (TL) | Ro Health (Term Loan)</t>
+          <t>Cano Health (Equity) | Cano Health (Term Loan) | Ro Health (Revolver) | Confluent Health (TL) | Ro Health (Term Loan)</t>
         </is>
       </c>
       <c r="T69" t="b">
@@ -6251,7 +6269,7 @@
         <v>1</v>
       </c>
       <c r="Q70" t="n">
-        <v>324.8583</v>
+        <v>814.5942</v>
       </c>
       <c r="R70" t="inlineStr">
         <is>
@@ -6335,7 +6353,7 @@
         <v>1</v>
       </c>
       <c r="Q71" t="n">
-        <v>367.8091</v>
+        <v>945.4287</v>
       </c>
       <c r="R71" t="inlineStr">
         <is>
@@ -6416,10 +6434,10 @@
         <v>3</v>
       </c>
       <c r="P72" t="n">
-        <v>0.9462</v>
+        <v>0.9476</v>
       </c>
       <c r="Q72" t="n">
-        <v>205.575</v>
+        <v>518.7523</v>
       </c>
       <c r="R72" t="inlineStr">
         <is>
@@ -6487,23 +6505,23 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>Recteq (TL)</t>
+          <t>Recteq (Equity)</t>
         </is>
       </c>
       <c r="M73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N73" t="b">
         <v>1</v>
       </c>
       <c r="O73" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P73" t="n">
         <v>1</v>
       </c>
       <c r="Q73" t="n">
-        <v>197.82</v>
+        <v>459.7254</v>
       </c>
       <c r="R73" t="inlineStr">
         <is>
@@ -6512,7 +6530,7 @@
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>Recteq (TL) | Recteq (Equity) | Recteq (Revolver)</t>
+          <t>Recteq (Equity) | Recteq (Revolver) | Recteq (TL)</t>
         </is>
       </c>
       <c r="T73" t="b">
@@ -6587,7 +6605,7 @@
         <v>1</v>
       </c>
       <c r="Q74" t="n">
-        <v>443.6071</v>
+        <v>650.7361</v>
       </c>
       <c r="R74" t="inlineStr">
         <is>
@@ -6671,7 +6689,7 @@
         <v>1</v>
       </c>
       <c r="Q75" t="n">
-        <v>349.183</v>
+        <v>525.0438</v>
       </c>
       <c r="R75" t="inlineStr">
         <is>
@@ -6755,7 +6773,7 @@
         <v>1</v>
       </c>
       <c r="Q76" t="n">
-        <v>506.8933</v>
+        <v>744.9492</v>
       </c>
       <c r="R76" t="inlineStr">
         <is>
@@ -6839,7 +6857,7 @@
         <v>1</v>
       </c>
       <c r="Q77" t="n">
-        <v>420.1781</v>
+        <v>586.803</v>
       </c>
       <c r="R77" t="inlineStr">
         <is>
@@ -6923,7 +6941,7 @@
         <v>1</v>
       </c>
       <c r="Q78" t="n">
-        <v>495.3074</v>
+        <v>694.8678</v>
       </c>
       <c r="R78" t="inlineStr">
         <is>
@@ -7004,10 +7022,10 @@
         <v>3</v>
       </c>
       <c r="P79" t="n">
-        <v>0.7583</v>
+        <v>0.76</v>
       </c>
       <c r="Q79" t="n">
-        <v>581.7938</v>
+        <v>883.1317</v>
       </c>
       <c r="R79" t="inlineStr">
         <is>
@@ -7016,7 +7034,7 @@
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>STG (Second Out Term Loans) | STG (First Out New Money Term Loans) | STG (TL) | BlackHawk Industrial (Incremental TL) | BlackHawk Industrial (TL)</t>
+          <t>STG (Second Out Term Loans) | STG (First Out New Money Term Loans) | STG (TL) | Plimpton &amp; Hills (TL) | Plimpton &amp; Hills (DDTL)</t>
         </is>
       </c>
       <c r="T79" t="b">
@@ -7082,16 +7100,16 @@
         <v>0</v>
       </c>
       <c r="N80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O80" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P80" t="n">
         <v>0.9499</v>
       </c>
       <c r="Q80" t="n">
-        <v>273.1139</v>
+        <v>382.3594</v>
       </c>
       <c r="R80" t="inlineStr">
         <is>
@@ -7100,7 +7118,7 @@
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>Sparq (TL) | AKW Holdings (Term Loan) | AKW Holdings (Common) | Sparq (Common Equity) | Sparq (DDTL)</t>
+          <t>Sparq (TL) | AKW Holdings (Term Loan) | AKW Holdings (Common) | Sparq (Revolver) | Sparq (Common Equity)</t>
         </is>
       </c>
       <c r="T80" t="b">
@@ -7175,7 +7193,7 @@
         <v>1</v>
       </c>
       <c r="Q81" t="n">
-        <v>522.6645</v>
+        <v>761.2319</v>
       </c>
       <c r="R81" t="inlineStr">
         <is>
@@ -7184,7 +7202,7 @@
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>Schlesinger (Equity) | Schlesinger (Term Loan) | UniTek (Common Eq) | Premiere Global Services (PGi) (Term Loan) | Premiere Global Services (PGi) (Priority Revolver)</t>
+          <t>Schlesinger (Equity) | Schlesinger (Term Loan) | UniTek (Common Eq) | Schlesinger (Revolver) | Schlesinger (DDTL)</t>
         </is>
       </c>
       <c r="T81" t="b">
@@ -7259,7 +7277,7 @@
         <v>0.9647</v>
       </c>
       <c r="Q82" t="n">
-        <v>310.9658</v>
+        <v>436.6165</v>
       </c>
       <c r="R82" t="inlineStr">
         <is>
@@ -7340,10 +7358,10 @@
         <v>1</v>
       </c>
       <c r="P83" t="n">
-        <v>1.106</v>
+        <v>0.901</v>
       </c>
       <c r="Q83" t="n">
-        <v>323.1901</v>
+        <v>454.638</v>
       </c>
       <c r="R83" t="inlineStr">
         <is>
@@ -7424,10 +7442,10 @@
         <v>1</v>
       </c>
       <c r="P84" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="Q84" t="n">
-        <v>686.5144</v>
+        <v>963.2418</v>
       </c>
       <c r="R84" t="inlineStr">
         <is>
@@ -7436,7 +7454,7 @@
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>BiggerPockets (Common Equity) | BiggerPockets (TL) | BiggerPockets (Revolver) | 48Forty (Common Equity) | 48Forty (Term Loan)</t>
+          <t>BiggerPockets (Common Equity) | BiggerPockets (TL) | BiggerPockets (Revolver) | 48Forty (Common Equity) | Harris (Common Equity)</t>
         </is>
       </c>
       <c r="T84" t="b">
@@ -7508,19 +7526,19 @@
         <v>1</v>
       </c>
       <c r="P85" t="n">
-        <v>0.7903</v>
+        <v>0.5929</v>
       </c>
       <c r="Q85" t="n">
-        <v>263.9853</v>
+        <v>389.6323</v>
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>Harris | BioDerm | C5MI | Cascade | Northwinds</t>
+          <t>Harris | BioDerm | C5MI | Cascade | Magnolia</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>C5MI (Preferred Equity) | Harris (Preferred Equity) | BioDerm (Preferred Equity) | Cascade (Preferred Equity) | C5MI (Common Equity)</t>
+          <t>C5MI (Preferred Equity) | Harris (Preferred Equity) | BioDerm (Preferred Equity) | Cascade (Preferred Equity) | Magnolia (Preferred Equity)</t>
         </is>
       </c>
       <c r="T85" t="b">
@@ -7592,10 +7610,10 @@
         <v>1</v>
       </c>
       <c r="P86" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="Q86" t="n">
-        <v>409.2311</v>
+        <v>605.0894</v>
       </c>
       <c r="R86" t="inlineStr">
         <is>
@@ -7676,10 +7694,10 @@
         <v>1</v>
       </c>
       <c r="P87" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="Q87" t="n">
-        <v>345.5332</v>
+        <v>508.5554</v>
       </c>
       <c r="R87" t="inlineStr">
         <is>
@@ -7688,7 +7706,7 @@
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>Connatix (Common Equity) | RTIC (Preferred Equity B) | RTIC (Preferred Equity A) | Vertex (Preferred Equity) | RTIC (Preferred Equity C)</t>
+          <t>Connatix (Common Equity) | Vertex (Preferred Equity) | RTIC (Preferred Equity B) | RTIC (Preferred Equity A) | RTIC (Preferred Equity C)</t>
         </is>
       </c>
       <c r="T87" t="b">
@@ -7760,10 +7778,10 @@
         <v>1</v>
       </c>
       <c r="P88" t="n">
-        <v>1.1831</v>
+        <v>0.9832</v>
       </c>
       <c r="Q88" t="n">
-        <v>337.9748</v>
+        <v>474.6021</v>
       </c>
       <c r="R88" t="inlineStr">
         <is>
@@ -7844,14 +7862,14 @@
         <v>1</v>
       </c>
       <c r="P89" t="n">
-        <v>1.1919</v>
+        <v>0.992</v>
       </c>
       <c r="Q89" t="n">
-        <v>459.7261</v>
+        <v>657.6972</v>
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>Tranzact | 48Forty | Harris | Aechelon | AKW Holdings</t>
+          <t>Tranzact | AKW Holdings | 48Forty | Harris | Aechelon</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
@@ -7928,14 +7946,14 @@
         <v>1</v>
       </c>
       <c r="P90" t="n">
-        <v>1.0656</v>
+        <v>0.8658</v>
       </c>
       <c r="Q90" t="n">
-        <v>254.6661</v>
+        <v>357.3443</v>
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>Tyto Athene | 48Forty | Harris | Aechelon | AKW Holdings</t>
+          <t>Tyto Athene | AKW Holdings | 48Forty | Harris | Aechelon</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
@@ -8012,19 +8030,19 @@
         <v>1</v>
       </c>
       <c r="P91" t="n">
-        <v>1.0656</v>
+        <v>0.8658</v>
       </c>
       <c r="Q91" t="n">
-        <v>243.8015</v>
+        <v>341.3221</v>
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>Tyto Athene | Harris | BioDerm | C5MI | AKW Holdings</t>
+          <t>Tyto Athene | AKW Holdings | Harris | BioDerm | C5MI</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>Tyto Athene (Pref) | BioDerm (Preferred Equity) | Tyto Athene (Equity) | Harris (Preferred Equity) | C5MI (Preferred Equity)</t>
+          <t>Tyto Athene (Pref) | BioDerm (Preferred Equity) | Harris (Preferred Equity) | Tyto Athene (Equity) | C5MI (Preferred Equity)</t>
         </is>
       </c>
       <c r="T91" t="b">
@@ -8096,10 +8114,10 @@
         <v>1</v>
       </c>
       <c r="P92" t="n">
-        <v>1.1278</v>
+        <v>0.928</v>
       </c>
       <c r="Q92" t="n">
-        <v>344.0517</v>
+        <v>495.753</v>
       </c>
       <c r="R92" t="inlineStr">
         <is>
@@ -8180,10 +8198,10 @@
         <v>1</v>
       </c>
       <c r="P93" t="n">
-        <v>1.1329</v>
+        <v>0.9332</v>
       </c>
       <c r="Q93" t="n">
-        <v>390.6513</v>
+        <v>566.9647</v>
       </c>
       <c r="R93" t="inlineStr">
         <is>
@@ -8232,17 +8250,17 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Watchtower Holdings</t>
+          <t>Watchtower</t>
         </is>
       </c>
       <c r="H94" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I94" t="b">
         <v>1</v>
       </c>
       <c r="J94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
@@ -8264,19 +8282,19 @@
         <v>1</v>
       </c>
       <c r="P94" t="n">
-        <v>1.1889</v>
+        <v>1</v>
       </c>
       <c r="Q94" t="n">
-        <v>333.6397</v>
+        <v>495.1412</v>
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>Watchtower Holdings | Watchtower | Watchtower Buyer | 48Forty | AKW Holdings</t>
+          <t>Watchtower | Watchtower Holdings | Watchtower Buyer | AKW Holdings | 48Forty</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>Watchtower Holding (Common Equity) | AKW Holdings (Common) | 48Forty (Common Equity) | 48Forty (Term Loan) | AKW Holdings (Term Loan)</t>
+          <t>Watchtower Holding (Common Equity) | AKW Holdings (Common) | 48Forty (Common Equity) | Watchtower (TL) | Watchtower (Revolver)</t>
         </is>
       </c>
       <c r="T94" t="b">
@@ -8348,14 +8366,14 @@
         <v>1</v>
       </c>
       <c r="P95" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="Q95" t="n">
-        <v>471.985</v>
+        <v>690.3403</v>
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>Watterson | 48Forty | Harris | Aechelon | AKW Holdings</t>
+          <t>Watterson | AKW Holdings | 48Forty | Harris | Aechelon</t>
         </is>
       </c>
       <c r="S95" t="inlineStr">
@@ -8496,14 +8514,14 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -8517,14 +8535,14 @@
         <v>13</v>
       </c>
       <c r="C3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>92.3%</t>
+          <t>84.6%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -8593,14 +8611,14 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>92.9%</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -8647,14 +8665,14 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -8679,14 +8697,14 @@
         <v>31</v>
       </c>
       <c r="C6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>87.1%</t>
+          <t>90.3%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -8701,25 +8719,25 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>74.2%</t>
+          <t>80.6%</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>80.6%</t>
+          <t>87.1%</t>
         </is>
       </c>
     </row>
@@ -8755,14 +8773,14 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>61.1%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="L7" t="n">

--- a/evaluation_results.xlsx
+++ b/evaluation_results.xlsx
@@ -1172,19 +1172,19 @@
         <v>1</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9023</v>
+        <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>605.7479</v>
+        <v>1</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Bland Landscaping | Watchtower Holdings</t>
+          <t>Bland Landscaping</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>Bland Landscaping (DDTL) | Bland Landscaping (Term Loan) | Bland Landscaping (Revolver) | Watchtower Holding (Common Equity)</t>
+          <t>Bland Landscaping (DDTL)</t>
         </is>
       </c>
       <c r="T9" t="b">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>Centauri Health | Watchtower Buyer | APHIX | Carisk Partners | Connatix</t>
+          <t>Centauri Health | Watchtower Buyer | 360DG | Integrated Data Services | Tranzact</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>Centauri Health (TL) | Centauri Health (Revolver) | Watchtower Buyer (Revolver) | Centauri Health (DDTL) | Carisk Partners (Revolver)</t>
+          <t>Centauri Health (TL) | Centauri Health (Revolver) | Watchtower Buyer (Revolver) | Centauri Health (DDTL) | 360DG (Revolver)</t>
         </is>
       </c>
       <c r="T14" t="b">
@@ -2264,14 +2264,14 @@
         <v>5</v>
       </c>
       <c r="P22" t="n">
-        <v>0.8549</v>
+        <v>0.8537</v>
       </c>
       <c r="Q22" t="n">
-        <v>85.36020000000001</v>
+        <v>86.6747</v>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>OSG Billing Services | U.S. Well | ImagineAcquisitionCo | AKW Holdings | None</t>
+          <t>OSG Billing Services | U.S. Well | ImagineAcquisitionCo | None | AKW Holdings</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2758,10 +2758,10 @@
       </c>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="n">
-        <v>0.6002999999999999</v>
+        <v>0.5628</v>
       </c>
       <c r="Q28" t="n">
-        <v>36.3303</v>
+        <v>36.6381</v>
       </c>
       <c r="R28" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>432.755</v>
+        <v>435.0036</v>
       </c>
       <c r="R30" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>PlayPower (Term Loan)</t>
+          <t>PlayPower (Term Loan) | Bluebird (Term Loan) | BlueHalo (Term Loan) | Aechelon (Term Loan) | 360DG (Term Loan)</t>
         </is>
       </c>
       <c r="T30" t="b">
@@ -3087,13 +3087,13 @@
         <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="P32" t="n">
         <v>0.7469</v>
       </c>
       <c r="Q32" t="n">
-        <v>391.6117</v>
+        <v>396.0039</v>
       </c>
       <c r="R32" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>APT Healthcare (Incr. DDTL) | Zips (DDTL) | APT Healthcare (Term Loan) | Lilly Lashes (TL) | APT Healthcare (Common Equity)</t>
+          <t>APT Healthcare (Incr. DDTL) | Zips (DDTL) | Bland Landscaping (DDTL) | AFC Industries (DDTL) | Carnegie Dartlet (DDTL)</t>
         </is>
       </c>
       <c r="T32" t="b">
@@ -3170,10 +3170,10 @@
       </c>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="n">
-        <v>0.8365</v>
+        <v>0.8363</v>
       </c>
       <c r="Q33" t="n">
-        <v>394.7907</v>
+        <v>399.9936</v>
       </c>
       <c r="R33" t="inlineStr">
         <is>
@@ -3254,19 +3254,19 @@
         <v>1</v>
       </c>
       <c r="P34" t="n">
-        <v>0.9995000000000001</v>
+        <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>618.7388999999999</v>
+        <v>1</v>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>48Forty | Smartronix / Trident | Altamira | Douglas | Engine &amp; Transmission Exchange</t>
+          <t>48Forty</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>48Forty (Common Equity) | 48Forty (Term Loan) | Altamira (Common Equity) | Smartronix / Trident (Common Equity) | Engine &amp; Transmission Exchange (Common Equity)</t>
+          <t>48Forty (Common Equity)</t>
         </is>
       </c>
       <c r="T34" t="b">
@@ -3338,19 +3338,19 @@
         <v>1</v>
       </c>
       <c r="P35" t="n">
-        <v>0.9834000000000001</v>
+        <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>537.6147</v>
+        <v>1</v>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>4Wall Entertainment | AKW Holdings</t>
+          <t>4Wall Entertainment</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>4Wall Entertainment (Term Loan) | 4Wall Entertainment (DDTL) | 4Wall Entertainment (Revolver) | AKW Holdings (Term Loan) | AKW Holdings (Common)</t>
+          <t>4Wall Entertainment (Term Loan)</t>
         </is>
       </c>
       <c r="T35" t="b">
@@ -3425,16 +3425,16 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>706.376</v>
+        <v>1</v>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>BBB Industries | STG Logistics | Adweek | Aspect Software | Health-E Commerce</t>
+          <t>BBB Industries</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>BBB Industries (First Lien Term Loan) | BBB Industries (Second Lien Term Loan) | STG (TL) | Adweek (Term Loan) | Adweek (DDTL)</t>
+          <t>BBB Industries (First Lien Term Loan)</t>
         </is>
       </c>
       <c r="T36" t="b">
@@ -3509,16 +3509,16 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>658.7212</v>
+        <v>1</v>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>Big Top Manufacturing | None | AKW Holdings</t>
+          <t>Big Top Manufacturing</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>Big Top Manufacturing (Term Loan) | Big Top Manufacturing (Revolver) | Big Top Manufacturing (Common Equity) | AKW Holdings (Term Loan) | IMIA (Term Loan)</t>
+          <t>Big Top Manufacturing (Term Loan)</t>
         </is>
       </c>
       <c r="T37" t="b">
@@ -3558,17 +3558,17 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>BlueHalo</t>
         </is>
       </c>
       <c r="H38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I38" t="b">
         <v>1</v>
       </c>
       <c r="J38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -3577,32 +3577,32 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Global (Term Loan)</t>
+          <t>BlueHalo (Term Loan)</t>
         </is>
       </c>
       <c r="M38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N38" t="b">
         <v>1</v>
       </c>
       <c r="O38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P38" t="n">
-        <v>0.8559</v>
+        <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>374.5238</v>
+        <v>1</v>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>Global | BlueHalo | Insight Global | Schlesinger | UniTek</t>
+          <t>BlueHalo</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>Global (Term Loan) | BlueHalo (Term Loan) | Insight Global (TL) | Schlesinger (Term Loan) | Schlesinger (DDTL)</t>
+          <t>BlueHalo (Term Loan)</t>
         </is>
       </c>
       <c r="T38" t="b">
@@ -3677,16 +3677,16 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>571.072</v>
+        <v>1</v>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>Integrated Data Services | Watchtower Buyer | nThrive | Big Top Manufacturing | APHIX</t>
+          <t>Integrated Data Services</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>Integrated Data Services (TL) | Integrated Data Services (Rev) | Watchtower Buyer (TL) | Watchtower Buyer (DDTL) | Aphix (Term Loan)</t>
+          <t>Integrated Data Services (TL)</t>
         </is>
       </c>
       <c r="T39" t="b">
@@ -3758,19 +3758,19 @@
         <v>1</v>
       </c>
       <c r="P40" t="n">
-        <v>0.9758</v>
+        <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>458.7628</v>
+        <v>1</v>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>KNS | STG Logistics | Adweek | Aspect Software | Health-E Commerce</t>
+          <t>KNS</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>KNS (Term Loan) | STG (TL) | Adweek (Term Loan) | Adweek (DDTL) | Health-E Commerce (Term Loan)</t>
+          <t>KNS (Term Loan)</t>
         </is>
       </c>
       <c r="T40" t="b">
@@ -3845,16 +3845,16 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>649.8196</v>
+        <v>1</v>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>Radius Aerospace | Cadence Aerospace | MAG Aerospace</t>
+          <t>Radius Aerospace</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>Radius Aerospace (Term Loan) | Radius Aerospace (Revolver) | MAG Aerospace (TL) | Cadence Aerospace</t>
+          <t>Radius Aerospace (Term Loan)</t>
         </is>
       </c>
       <c r="T41" t="b">
@@ -3929,7 +3929,7 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>538.772</v>
+        <v>1</v>
       </c>
       <c r="R42" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>Roofed Right America (Term Loan) | Roofed Right America (DDTL 2) | Roofed Right America (DDTL 1) | Roofed Right America (Revolver)</t>
+          <t>Roofed Right America (Term Loan)</t>
         </is>
       </c>
       <c r="T42" t="b">
@@ -4009,7 +4009,7 @@
         <v>0.7544</v>
       </c>
       <c r="Q43" t="n">
-        <v>391.6918</v>
+        <v>396.3347</v>
       </c>
       <c r="R43" t="inlineStr">
         <is>
@@ -4018,7 +4018,7 @@
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>US Fertility (DDTL) | TVC (DDTL) | TVC (TL) | US Fertility (Term Loan) | TVC (Revolver)</t>
+          <t>US Fertility (DDTL) | TVC (DDTL) | TVC (TL) | US Fertility (Term Loan) | Bland Landscaping (DDTL)</t>
         </is>
       </c>
       <c r="T43" t="b">
@@ -4089,7 +4089,7 @@
         <v>0.7544</v>
       </c>
       <c r="Q44" t="n">
-        <v>292.8177</v>
+        <v>294.2774</v>
       </c>
       <c r="R44" t="inlineStr">
         <is>
@@ -4098,7 +4098,7 @@
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>TVC (TL) | US Fertility (Term Loan) | US Fertility (DDTL) | TVC (DDTL) | TVC (Revolver)</t>
+          <t>TVC (TL) | US Fertility (Term Loan) | US Fertility (DDTL) | TVC (DDTL) | MeritDirect (Term Loan)</t>
         </is>
       </c>
       <c r="T44" t="b">
@@ -4173,7 +4173,7 @@
         <v>0.999</v>
       </c>
       <c r="Q45" t="n">
-        <v>590.5582000000001</v>
+        <v>591.8692</v>
       </c>
       <c r="R45" t="inlineStr">
         <is>
@@ -4182,7 +4182,7 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>Aeronix (DDTL) | Aeronix (Common Equity) | AKW Holdings (Term Loan) | Aeronix (TL) | AKW Holdings (Common)</t>
+          <t>Aeronix (DDTL) | Aeronix (Common Equity) | AKW Holdings (Term Loan) | Aeronix (TL) | 4Wall Entertainment (Term Loan)</t>
         </is>
       </c>
       <c r="T45" t="b">
@@ -4254,19 +4254,19 @@
         <v>1</v>
       </c>
       <c r="P46" t="n">
-        <v>0.8377</v>
+        <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>488.6119</v>
+        <v>1</v>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>Dr. Scholl's | Apex Service Partners | API Technologies | Wheel Pros | Paris Presents</t>
+          <t>Dr. Scholl's</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>Dr. Scholl's (Term Loan) | Dr. Scholl's (Revolver) | API Technologies (TL) | Apex (DDTL III) | Wheel Pros (1L)</t>
+          <t>Dr. Scholl's (Term Loan)</t>
         </is>
       </c>
       <c r="T46" t="b">
@@ -4338,19 +4338,19 @@
         <v>1</v>
       </c>
       <c r="P47" t="n">
-        <v>0.8461</v>
+        <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>583.1864</v>
+        <v>1</v>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>MCR | Sabel Systems | Signature Systems Group | Nevada Behavioral Health Systems | None</t>
+          <t>MCR</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>MCR (Term Loan) | MCR (Revolver) | Kentucky Downs (DDTL A) | FlexPrint (DDTL) | Research Horizons (DDTL)</t>
+          <t>MCR (Term Loan)</t>
         </is>
       </c>
       <c r="T47" t="b">
@@ -4418,10 +4418,10 @@
       </c>
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="n">
-        <v>0.5482</v>
+        <v>0.5505</v>
       </c>
       <c r="Q48" t="n">
-        <v>233.9925</v>
+        <v>235.981</v>
       </c>
       <c r="R48" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>STG (TL)</t>
+          <t>STG (First Out New Money Term Loans)</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -4493,28 +4493,28 @@
         </is>
       </c>
       <c r="M49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N49" t="b">
         <v>1</v>
       </c>
       <c r="O49" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P49" t="n">
-        <v>0.76</v>
+        <v>1</v>
       </c>
       <c r="Q49" t="n">
-        <v>887.1277</v>
+        <v>1</v>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>STG Logistics | Plimpton &amp; Hills | BlackHawk Industrial | WhiteHawk Industrial</t>
+          <t>STG Logistics</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>STG (First Out New Money Term Loans) | STG (Second Out Term Loans) | STG (TL) | Plimpton &amp; Hills (TL) | Plimpton &amp; Hills (DDTL)</t>
+          <t>STG (First Out New Money Term Loans)</t>
         </is>
       </c>
       <c r="T49" t="b">
@@ -4589,7 +4589,7 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>667.8467000000001</v>
+        <v>672.4636</v>
       </c>
       <c r="R50" t="inlineStr">
         <is>
@@ -4670,19 +4670,19 @@
         <v>1</v>
       </c>
       <c r="P51" t="n">
-        <v>0.9834000000000001</v>
+        <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>537.6147</v>
+        <v>1</v>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>4Wall Entertainment | AKW Holdings</t>
+          <t>4Wall Entertainment</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>4Wall Entertainment (Term Loan) | 4Wall Entertainment (DDTL) | 4Wall Entertainment (Revolver) | AKW Holdings (Term Loan) | AKW Holdings (Common)</t>
+          <t>4Wall Entertainment (Term Loan)</t>
         </is>
       </c>
       <c r="T51" t="b">
@@ -4757,16 +4757,16 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>688.3133</v>
+        <v>1</v>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>A1 Garage | A2 Garge | None | Guild Garage Group | Omnia</t>
+          <t>A1 Garage</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>A1 Garage (Common Equity) | A1 Garage (Revolver) | A1 Garage (Term Loan) | A1 Garage (DDTL) | Guild Garage Group (Common Equity)</t>
+          <t>A1 Garage (Common Equity)</t>
         </is>
       </c>
       <c r="T52" t="b">
@@ -4841,7 +4841,7 @@
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>709.112</v>
+        <v>1</v>
       </c>
       <c r="R53" t="inlineStr">
         <is>
@@ -4850,7 +4850,7 @@
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>Archer Lewis (Revolver) | Archer Lewis (Term Loan) | Archer Lewis (Unfunded DDTL B) | Archer Lewis (Unfunded DDTL A) | Archer Lewis (Common Equity)</t>
+          <t>Archer Lewis (Revolver)</t>
         </is>
       </c>
       <c r="T53" t="b">
@@ -4925,16 +4925,16 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>820.9715</v>
+        <v>1</v>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>Beta+ | API Technologies | Altamira | Nuvei | Lynx Technologies</t>
+          <t>Beta+</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>Beta+ (TL) | API Technologies (TL) | Lynx Technologies (TL) | Altamira (TL) | Nuvei (Term Loan)</t>
+          <t>Beta+ (TL)</t>
         </is>
       </c>
       <c r="T54" t="b">
@@ -5006,19 +5006,19 @@
         <v>1</v>
       </c>
       <c r="P55" t="n">
-        <v>0.9499</v>
+        <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>411.894</v>
+        <v>1</v>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>Sparq | AKW Holdings</t>
+          <t>Sparq</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>Sparq (TL) | AKW Holdings (Term Loan) | AKW Holdings (Common) | Sparq (DDTL) | Sparq (Common Equity)</t>
+          <t>Sparq (TL)</t>
         </is>
       </c>
       <c r="T55" t="b">
@@ -5093,7 +5093,7 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>941.8649</v>
+        <v>1</v>
       </c>
       <c r="R56" t="inlineStr">
         <is>
@@ -5102,7 +5102,7 @@
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>BiggerPockets (Revolver) | BiggerPockets (TL) | BiggerPockets (Common Equity)</t>
+          <t>BiggerPockets (Revolver)</t>
         </is>
       </c>
       <c r="T56" t="b">
@@ -5177,7 +5177,7 @@
         <v>1</v>
       </c>
       <c r="Q57" t="n">
-        <v>942.0512</v>
+        <v>1</v>
       </c>
       <c r="R57" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>Carnegie Dartlet (DDTL) | Carnegie Dartlet (Term Loan) | Carnegie Dartlet (Revolver) | Carnegie Dartlet (Common Equity)</t>
+          <t>Carnegie Dartlet (DDTL)</t>
         </is>
       </c>
       <c r="T57" t="b">
@@ -5258,19 +5258,19 @@
         <v>1</v>
       </c>
       <c r="P58" t="n">
-        <v>0.9812</v>
+        <v>1</v>
       </c>
       <c r="Q58" t="n">
-        <v>475.5515</v>
+        <v>1</v>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>Comprehensive Rehab Consultants | Ro Health | Confluent Health | Cano Health | Nevada Behavioral Health Systems</t>
+          <t>Comprehensive Rehab Consultants</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>Comprehensive Rehab Consultants (Revolver) | Comprehensive Rehab Consultants (Term Loan) | Comprehensive Rehab Consultants (Common Equity) | Ro Health (Revolver) | Nevada Behavioral Health Systems (Revolver)</t>
+          <t>Comprehensive Rehab Consultants (Revolver)</t>
         </is>
       </c>
       <c r="T58" t="b">
@@ -5345,16 +5345,16 @@
         <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>763.0334</v>
+        <v>1</v>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>Engine &amp; Transmission Exchange | Infosoft | Lilly Lashes | Loving Tan | Schlesinger</t>
+          <t>Engine &amp; Transmission Exchange</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>Engine &amp; Transmission Exchange (Common Equity) | Engine &amp; Transmission Exchange (Promissory Note) | Infosoft (Common Equity) | Schlesinger (Equity) | Lilly Lashes (Equity)</t>
+          <t>Engine &amp; Transmission Exchange (Common Equity)</t>
         </is>
       </c>
       <c r="T59" t="b">
@@ -5426,19 +5426,19 @@
         <v>1</v>
       </c>
       <c r="P60" t="n">
-        <v>0.8954</v>
+        <v>1</v>
       </c>
       <c r="Q60" t="n">
-        <v>499.4792</v>
+        <v>1</v>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>Epiq | ImagineAcquisitionCo</t>
+          <t>Epiq</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>Epiq (Common) | Imagine Topco. L.P. (Common Equity - Series B) | Imagine Topco. L.P. (Preferred Equity - Series A) | Epiq (TL) | Epiq (Revolver)</t>
+          <t>Epiq (Common)</t>
         </is>
       </c>
       <c r="T60" t="b">
@@ -5510,19 +5510,19 @@
         <v>1</v>
       </c>
       <c r="P61" t="n">
-        <v>0.9586</v>
+        <v>1</v>
       </c>
       <c r="Q61" t="n">
-        <v>778.59</v>
+        <v>1</v>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>Evans Network | Connatix | Planview | Rancho Medical | Rosco</t>
+          <t>Evans Network</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>Evans Network (1L) | Evans Network (2L) | Planview (TL) | Rosco (Term Loan) | Connatix (Common Equity)</t>
+          <t>Evans Network (1L)</t>
         </is>
       </c>
       <c r="T61" t="b">
@@ -5597,16 +5597,16 @@
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>924.6727</v>
+        <v>1</v>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>Federal Advisory Partners | None | First Medical Associates</t>
+          <t>Federal Advisory Partners</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>Federal Advisory Partners (First Lien Term Loan) | Federal Advisory Partners (Term Loan) | Federal Advisory Partners (Revolver) | First Medical Associates (Term Loan) | First Medical Associates (DDTL)</t>
+          <t>Federal Advisory Partners (First Lien Term Loan)</t>
         </is>
       </c>
       <c r="T62" t="b">
@@ -5681,16 +5681,16 @@
         <v>1</v>
       </c>
       <c r="Q63" t="n">
-        <v>722.9121</v>
+        <v>1</v>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>Infinity Home Services | United Land Services | Any Hour Services | Applied Technical Services | IDC Infusion Services</t>
+          <t>Infinity Home Services</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>Infinity Home Services (Revolver) | Infinity Home Services (Common Equity) | Infinity Home Services (Term Loan) | Infinity Home Services (DDTL) | Infinity Home Services (DDTL) CAD</t>
+          <t>Infinity Home Services (Revolver)</t>
         </is>
       </c>
       <c r="T63" t="b">
@@ -5849,7 +5849,7 @@
         <v>1</v>
       </c>
       <c r="Q65" t="n">
-        <v>862.566</v>
+        <v>873.5107</v>
       </c>
       <c r="R65" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>543.4204999999999</v>
+        <v>546.4172</v>
       </c>
       <c r="R66" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
         <v>1</v>
       </c>
       <c r="Q67" t="n">
-        <v>991.8898</v>
+        <v>1005.7311</v>
       </c>
       <c r="R67" t="inlineStr">
         <is>
@@ -6101,7 +6101,7 @@
         <v>1</v>
       </c>
       <c r="Q68" t="n">
-        <v>991.8898</v>
+        <v>1005.7311</v>
       </c>
       <c r="R68" t="inlineStr">
         <is>
@@ -6185,7 +6185,7 @@
         <v>1</v>
       </c>
       <c r="Q69" t="n">
-        <v>739.448</v>
+        <v>746.6063</v>
       </c>
       <c r="R69" t="inlineStr">
         <is>
@@ -6269,16 +6269,16 @@
         <v>1</v>
       </c>
       <c r="Q70" t="n">
-        <v>814.5942</v>
+        <v>1</v>
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>Dr. Scholl's | Dr. Squatch</t>
+          <t>Dr. Scholl's</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>Dr. Scholl's (Revolver) | Dr. Scholl's (Term Loan) | Dr. Squatch (Term Loan) | Dr. Squatch (Revolver) | Dr. Squatch (DDTL)</t>
+          <t>Dr. Scholl's (Revolver)</t>
         </is>
       </c>
       <c r="T70" t="b">
@@ -6353,7 +6353,7 @@
         <v>1</v>
       </c>
       <c r="Q71" t="n">
-        <v>945.4287</v>
+        <v>949.814</v>
       </c>
       <c r="R71" t="inlineStr">
         <is>
@@ -6434,10 +6434,10 @@
         <v>3</v>
       </c>
       <c r="P72" t="n">
-        <v>0.9476</v>
+        <v>0.9471000000000001</v>
       </c>
       <c r="Q72" t="n">
-        <v>518.7523</v>
+        <v>524.371</v>
       </c>
       <c r="R72" t="inlineStr">
         <is>
@@ -6521,7 +6521,7 @@
         <v>1</v>
       </c>
       <c r="Q73" t="n">
-        <v>459.7254</v>
+        <v>1</v>
       </c>
       <c r="R73" t="inlineStr">
         <is>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>Recteq (Equity) | Recteq (Revolver) | Recteq (TL)</t>
+          <t>Recteq (Equity)</t>
         </is>
       </c>
       <c r="T73" t="b">
@@ -6605,16 +6605,16 @@
         <v>1</v>
       </c>
       <c r="Q74" t="n">
-        <v>650.7361</v>
+        <v>1</v>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>Watterson | AKW Holdings</t>
+          <t>Watterson</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>Watterson (Revolver) | Watterson (TL) | Watterson (Equity) | Watterson (DDTL) | AKW Holdings (Term Loan)</t>
+          <t>Watterson (Revolver)</t>
         </is>
       </c>
       <c r="T74" t="b">
@@ -6689,16 +6689,16 @@
         <v>1</v>
       </c>
       <c r="Q75" t="n">
-        <v>525.0438</v>
+        <v>1</v>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>Watchtower Buyer | Watchtower | Watchtower Holdings | APHIX | Carisk Partners</t>
+          <t>Watchtower Buyer</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>Watchtower Buyer (Revolver) | Watchtower Buyer (TL) | Watchtower Buyer (DDTL) | Watchtower (Revolver) | Carisk Partners (Revolver)</t>
+          <t>Watchtower Buyer (Revolver)</t>
         </is>
       </c>
       <c r="T75" t="b">
@@ -6773,7 +6773,7 @@
         <v>1</v>
       </c>
       <c r="Q76" t="n">
-        <v>744.9492</v>
+        <v>1</v>
       </c>
       <c r="R76" t="inlineStr">
         <is>
@@ -6857,16 +6857,16 @@
         <v>1</v>
       </c>
       <c r="Q77" t="n">
-        <v>586.803</v>
+        <v>1</v>
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>Tranzact | Watchtower Buyer | APHIX | Carisk Partners | Connatix</t>
+          <t>Tranzact</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>Tranzact (Term Loan) | Tranzact (DDTL) | Tranzact (Revolver) | Watchtower Buyer (TL) | Watchtower Buyer (DDTL)</t>
+          <t>Tranzact (Term Loan)</t>
         </is>
       </c>
       <c r="T77" t="b">
@@ -6941,7 +6941,7 @@
         <v>1</v>
       </c>
       <c r="Q78" t="n">
-        <v>694.8678</v>
+        <v>1</v>
       </c>
       <c r="R78" t="inlineStr">
         <is>
@@ -6950,7 +6950,7 @@
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>TransGo (Equity) | TransGo (TL) | TransGo (Revolver)</t>
+          <t>TransGo (Equity)</t>
         </is>
       </c>
       <c r="T78" t="b">
@@ -7004,7 +7004,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>STG (TL)</t>
+          <t>STG (Second Out Term Loans)</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -7013,28 +7013,28 @@
         </is>
       </c>
       <c r="M79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N79" t="b">
         <v>1</v>
       </c>
       <c r="O79" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P79" t="n">
-        <v>0.76</v>
+        <v>1</v>
       </c>
       <c r="Q79" t="n">
-        <v>883.1317</v>
+        <v>1</v>
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>STG Logistics | Plimpton &amp; Hills | BlackHawk Industrial | WhiteHawk Industrial</t>
+          <t>STG Logistics</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>STG (Second Out Term Loans) | STG (First Out New Money Term Loans) | STG (TL) | Plimpton &amp; Hills (TL) | Plimpton &amp; Hills (DDTL)</t>
+          <t>STG (Second Out Term Loans)</t>
         </is>
       </c>
       <c r="T79" t="b">
@@ -7100,10 +7100,10 @@
         <v>0</v>
       </c>
       <c r="N80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P80" t="n">
         <v>0.9499</v>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>Sparq (TL) | AKW Holdings (Term Loan) | AKW Holdings (Common) | Sparq (Revolver) | Sparq (Common Equity)</t>
+          <t>Sparq (TL) | Watterson (Revolver) | Dr. Scholl's (Revolver) | AKW Holdings (Term Loan) | AKW Holdings (Common)</t>
         </is>
       </c>
       <c r="T80" t="b">
@@ -7193,16 +7193,16 @@
         <v>1</v>
       </c>
       <c r="Q81" t="n">
-        <v>761.2319</v>
+        <v>1</v>
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>Schlesinger | Global | Insight Global | UniTek | Premiere Global Services (PGi)</t>
+          <t>Schlesinger</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>Schlesinger (Equity) | Schlesinger (Term Loan) | UniTek (Common Eq) | Schlesinger (Revolver) | Schlesinger (DDTL)</t>
+          <t>Schlesinger (Equity)</t>
         </is>
       </c>
       <c r="T81" t="b">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>ProSearch (TL)</t>
+          <t>ProSearch (Revolver)</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -7265,28 +7265,28 @@
         </is>
       </c>
       <c r="M82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N82" t="b">
         <v>1</v>
       </c>
       <c r="O82" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P82" t="n">
-        <v>0.9647</v>
+        <v>1</v>
       </c>
       <c r="Q82" t="n">
-        <v>436.6165</v>
+        <v>1</v>
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>ProSearch | Peninsula Pacific Entertainment | None | STG Logistics | Adweek</t>
+          <t>ProSearch</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>ProSearch (Revolver) | ProSearch (TL) | ProSearch (DDTL) | Colonial Downs (DDTL) | Datalot (Revolver)</t>
+          <t>ProSearch (Revolver)</t>
         </is>
       </c>
       <c r="T82" t="b">
@@ -7358,19 +7358,19 @@
         <v>1</v>
       </c>
       <c r="P83" t="n">
-        <v>0.901</v>
+        <v>1</v>
       </c>
       <c r="Q83" t="n">
-        <v>454.638</v>
+        <v>1</v>
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>Aechelon | GCOM | QuantiTech | Federal Advisory Partners | Athene</t>
+          <t>Aechelon</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>Aechelon (Common Equity) | GCOM (Common Equity) | QuantiTech (Common Equity I) | Federal Advisory Partners (Common Equity) | QuantiTech (Common Equity II)</t>
+          <t>Aechelon (Common Equity)</t>
         </is>
       </c>
       <c r="T83" t="b">
@@ -7445,16 +7445,16 @@
         <v>1</v>
       </c>
       <c r="Q84" t="n">
-        <v>963.2418</v>
+        <v>1</v>
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>BiggerPockets | 48Forty | Harris | Aechelon | Altamira</t>
+          <t>BiggerPockets</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>BiggerPockets (Common Equity) | BiggerPockets (TL) | BiggerPockets (Revolver) | 48Forty (Common Equity) | Harris (Common Equity)</t>
+          <t>BiggerPockets (Common Equity)</t>
         </is>
       </c>
       <c r="T84" t="b">
@@ -7494,17 +7494,17 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Harris</t>
+          <t>C5MI</t>
         </is>
       </c>
       <c r="H85" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I85" t="b">
         <v>1</v>
       </c>
       <c r="J85" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
@@ -7526,19 +7526,19 @@
         <v>1</v>
       </c>
       <c r="P85" t="n">
-        <v>0.5929</v>
+        <v>1</v>
       </c>
       <c r="Q85" t="n">
-        <v>389.6323</v>
+        <v>1</v>
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>Harris | BioDerm | C5MI | Cascade | Magnolia</t>
+          <t>C5MI</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>C5MI (Preferred Equity) | Harris (Preferred Equity) | BioDerm (Preferred Equity) | Cascade (Preferred Equity) | Magnolia (Preferred Equity)</t>
+          <t>C5MI (Preferred Equity)</t>
         </is>
       </c>
       <c r="T85" t="b">
@@ -7613,16 +7613,16 @@
         <v>1</v>
       </c>
       <c r="Q86" t="n">
-        <v>605.0894</v>
+        <v>1</v>
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>Connatix | Rosco | NORA | RTIC | Rancho Medical</t>
+          <t>Connatix</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>Connatix (Common Equity) | Rosco (Common Equity) | NORA (Common Equity) | RTIC (Common Equity) | Rancho (Equity)</t>
+          <t>Connatix (Common Equity)</t>
         </is>
       </c>
       <c r="T86" t="b">
@@ -7697,16 +7697,16 @@
         <v>1</v>
       </c>
       <c r="Q87" t="n">
-        <v>508.5554</v>
+        <v>1</v>
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>Connatix | RTIC | Vertex | Rancho Medical | Rosco</t>
+          <t>Connatix</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>Connatix (Common Equity) | Vertex (Preferred Equity) | RTIC (Preferred Equity B) | RTIC (Preferred Equity A) | RTIC (Preferred Equity C)</t>
+          <t>Connatix (Common Equity)</t>
         </is>
       </c>
       <c r="T87" t="b">
@@ -7778,19 +7778,19 @@
         <v>1</v>
       </c>
       <c r="P88" t="n">
-        <v>0.9832</v>
+        <v>1</v>
       </c>
       <c r="Q88" t="n">
-        <v>474.6021</v>
+        <v>1</v>
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>Rancho Medical | Connatix | Rosco | NORA | RTIC</t>
+          <t>Rancho Medical</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>Rancho (Equity) | Connatix (Common Equity) | Rosco (Common Equity) | NORA (Common Equity) | RTIC (Common Equity)</t>
+          <t>Rancho (Equity)</t>
         </is>
       </c>
       <c r="T88" t="b">
@@ -7862,19 +7862,19 @@
         <v>1</v>
       </c>
       <c r="P89" t="n">
-        <v>0.992</v>
+        <v>1</v>
       </c>
       <c r="Q89" t="n">
-        <v>657.6972</v>
+        <v>1</v>
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>Tranzact | AKW Holdings | 48Forty | Harris | Aechelon</t>
+          <t>Tranzact</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>Tranzact (Common Equity) | Tranzact (DDTL) | Tranzact (Revolver) | Tranzact (Term Loan) | AKW Holdings (Common)</t>
+          <t>Tranzact (Common Equity)</t>
         </is>
       </c>
       <c r="T89" t="b">
@@ -7946,19 +7946,19 @@
         <v>1</v>
       </c>
       <c r="P90" t="n">
-        <v>0.8658</v>
+        <v>1</v>
       </c>
       <c r="Q90" t="n">
-        <v>357.3443</v>
+        <v>1</v>
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>Tyto Athene | AKW Holdings | 48Forty | Harris | Aechelon</t>
+          <t>Tyto Athene</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>Tyto Athene (Equity) | AKW Holdings (Common) | Tyto Athene (Pref) | 48Forty (Common Equity) | Harris (Common Equity)</t>
+          <t>Tyto Athene (Equity)</t>
         </is>
       </c>
       <c r="T90" t="b">
@@ -8030,19 +8030,19 @@
         <v>1</v>
       </c>
       <c r="P91" t="n">
-        <v>0.8658</v>
+        <v>1</v>
       </c>
       <c r="Q91" t="n">
-        <v>341.3221</v>
+        <v>1</v>
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>Tyto Athene | AKW Holdings | Harris | BioDerm | C5MI</t>
+          <t>Tyto Athene</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>Tyto Athene (Pref) | BioDerm (Preferred Equity) | Harris (Preferred Equity) | Tyto Athene (Equity) | C5MI (Preferred Equity)</t>
+          <t>Tyto Athene (Pref)</t>
         </is>
       </c>
       <c r="T91" t="b">
@@ -8114,19 +8114,19 @@
         <v>1</v>
       </c>
       <c r="P92" t="n">
-        <v>0.928</v>
+        <v>1</v>
       </c>
       <c r="Q92" t="n">
-        <v>495.753</v>
+        <v>1</v>
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>Vertex | Connatix | Rosco | NORA | RTIC</t>
+          <t>Vertex</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>Vertex (Common Equity) | Vertex (Preferred Equity) | NORA (Common Equity) | RTIC (Common Equity) | Connatix (Common Equity)</t>
+          <t>Vertex (Common Equity)</t>
         </is>
       </c>
       <c r="T92" t="b">
@@ -8198,19 +8198,19 @@
         <v>1</v>
       </c>
       <c r="P93" t="n">
-        <v>0.9332</v>
+        <v>1</v>
       </c>
       <c r="Q93" t="n">
-        <v>566.9647</v>
+        <v>1</v>
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>Vertex | RTIC | Rancho Medical | Connatix | Rosco</t>
+          <t>Vertex</t>
         </is>
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>Vertex (Preferred Equity) | RTIC (Preferred Equity B) | RTIC (Preferred Equity A) | Vertex (Common Equity) | RTIC (Preferred Equity C)</t>
+          <t>Vertex (Preferred Equity)</t>
         </is>
       </c>
       <c r="T93" t="b">
@@ -8245,23 +8245,21 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
+          <t>Watchtower</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
           <t>Watchtower Holdings</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>Watchtower</t>
         </is>
       </c>
       <c r="H94" t="b">
         <v>0</v>
       </c>
       <c r="I94" t="b">
-        <v>1</v>
-      </c>
-      <c r="J94" t="n">
-        <v>2</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr">
         <is>
           <t>Watchtower Holding (Common Equity)</t>
@@ -8285,16 +8283,16 @@
         <v>1</v>
       </c>
       <c r="Q94" t="n">
-        <v>495.1412</v>
+        <v>1</v>
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>Watchtower | Watchtower Holdings | Watchtower Buyer | AKW Holdings | 48Forty</t>
+          <t>Watchtower Holdings</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>Watchtower Holding (Common Equity) | AKW Holdings (Common) | 48Forty (Common Equity) | Watchtower (TL) | Watchtower (Revolver)</t>
+          <t>Watchtower Holding (Common Equity)</t>
         </is>
       </c>
       <c r="T94" t="b">
@@ -8369,16 +8367,16 @@
         <v>1</v>
       </c>
       <c r="Q95" t="n">
-        <v>690.3403</v>
+        <v>1</v>
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>Watterson | AKW Holdings | 48Forty | Harris | Aechelon</t>
+          <t>Watterson</t>
         </is>
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>Watterson (Equity) | Watterson (TL) | Watterson (Revolver) | Watterson (DDTL) | AKW Holdings (Common)</t>
+          <t>Watterson (Equity)</t>
         </is>
       </c>
       <c r="T95" t="b">
@@ -8503,25 +8501,25 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>88.9%</t>
         </is>
       </c>
     </row>
@@ -8535,25 +8533,25 @@
         <v>13</v>
       </c>
       <c r="C3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>84.6%</t>
+          <t>92.3%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>92.3%</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -8751,14 +8749,14 @@
         <v>18</v>
       </c>
       <c r="C7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>72.2%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -8773,14 +8771,14 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="L7" t="n">

--- a/evaluation_results.xlsx
+++ b/evaluation_results.xlsx
@@ -1599,12 +1599,12 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>Centauri Health | Watchtower Buyer | 360DG | Integrated Data Services | Tranzact</t>
+          <t>Centauri Health | Watchtower Buyer | APHIX | Carisk Partners | Connatix</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>Centauri Health (TL) | Centauri Health (Revolver) | Watchtower Buyer (Revolver) | Centauri Health (DDTL) | 360DG (Revolver)</t>
+          <t>Centauri Health (TL) | Centauri Health (Revolver) | Watchtower Buyer (Revolver) | Centauri Health (DDTL) | Carisk Partners (Revolver)</t>
         </is>
       </c>
       <c r="T14" t="b">

--- a/evaluation_results.xlsx
+++ b/evaluation_results.xlsx
@@ -1589,10 +1589,10 @@
         <v>1</v>
       </c>
       <c r="O14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9533</v>
+        <v>1</v>
       </c>
       <c r="Q14" t="n">
         <v>345.8854</v>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>Centauri Health (TL) | Centauri Health (Revolver) | Watchtower Buyer (Revolver) | Centauri Health (DDTL) | Carisk Partners (Revolver)</t>
+          <t>Centauri Health (TL) | Watchtower Buyer (Revolver) | Centauri Health (Revolver) | Centauri Health (DDTL) | Centauri Health (Equity)</t>
         </is>
       </c>
       <c r="T14" t="b">
@@ -2264,10 +2264,10 @@
         <v>5</v>
       </c>
       <c r="P22" t="n">
-        <v>0.8537</v>
+        <v>0.8538</v>
       </c>
       <c r="Q22" t="n">
-        <v>86.6747</v>
+        <v>87.51949999999999</v>
       </c>
       <c r="R22" t="inlineStr">
         <is>
@@ -2730,16 +2730,18 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>AKW Holdings</t>
+          <t>Fairbanks Morse Defense</t>
         </is>
       </c>
       <c r="H28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" t="b">
-        <v>0</v>
-      </c>
-      <c r="J28" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1</v>
+      </c>
       <c r="K28" t="inlineStr">
         <is>
           <t>Fairbanks Morse Defense (Term Loan)</t>
@@ -2747,30 +2749,32 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>AKW Holdings (Term Loan)</t>
+          <t>Fairbanks Morse Defense (Term Loan)</t>
         </is>
       </c>
       <c r="M28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N28" t="b">
-        <v>0</v>
-      </c>
-      <c r="O28" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1</v>
+      </c>
       <c r="P28" t="n">
-        <v>0.5628</v>
+        <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>36.6381</v>
+        <v>1</v>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>AKW Holdings</t>
+          <t>Fairbanks Morse Defense</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>AKW Holdings (Term Loan) | AKW Holdings (Common)</t>
+          <t>Fairbanks Morse Defense (Term Loan)</t>
         </is>
       </c>
       <c r="T28" t="b">
@@ -2925,7 +2929,7 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>435.0036</v>
+        <v>434.7123</v>
       </c>
       <c r="R30" t="inlineStr">
         <is>
@@ -3058,17 +3062,17 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>APT Healthcare</t>
+          <t>The Creative Group</t>
         </is>
       </c>
       <c r="H32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I32" t="b">
         <v>1</v>
       </c>
       <c r="J32" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -3077,32 +3081,32 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>APT Healthcare (Incr. DDTL)</t>
+          <t>The Creative Group (Term Loan)</t>
         </is>
       </c>
       <c r="M32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O32" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="P32" t="n">
-        <v>0.7469</v>
+        <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>396.0039</v>
+        <v>1</v>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>APT Healthcare | Lilly Lashes | Zips | The Creative Group | The Original Cakerie</t>
+          <t>The Creative Group</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>APT Healthcare (Incr. DDTL) | Zips (DDTL) | Bland Landscaping (DDTL) | AFC Industries (DDTL) | Carnegie Dartlet (DDTL)</t>
+          <t>The Creative Group (Term Loan)</t>
         </is>
       </c>
       <c r="T32" t="b">
@@ -3142,16 +3146,18 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Boss Industries</t>
+          <t>360DG</t>
         </is>
       </c>
       <c r="H33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I33" t="b">
-        <v>0</v>
-      </c>
-      <c r="J33" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1</v>
+      </c>
       <c r="K33" t="inlineStr">
         <is>
           <t>360DG (DDTL A)</t>
@@ -3159,30 +3165,32 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>AFC Industries (DDTL)</t>
+          <t>360DG (DDTL A)</t>
         </is>
       </c>
       <c r="M33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N33" t="b">
-        <v>0</v>
-      </c>
-      <c r="O33" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="O33" t="n">
+        <v>1</v>
+      </c>
       <c r="P33" t="n">
-        <v>0.8363</v>
+        <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>399.9936</v>
+        <v>1</v>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>Boss Industries | ECM Industries | AFC Acquisitions | DermaRite | Nsi Industries</t>
+          <t>360DG</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>AFC Industries (DDTL) | Nsi Industries (DDTL) | AFC Industries (TL) | Boss Industries (Term Loan) | ECM Industries (TL)</t>
+          <t>360DG (DDTL A)</t>
         </is>
       </c>
       <c r="T33" t="b">
@@ -3978,16 +3986,18 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>TVC</t>
+          <t>A1 Garage</t>
         </is>
       </c>
       <c r="H43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I43" t="b">
-        <v>0</v>
-      </c>
-      <c r="J43" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1</v>
+      </c>
       <c r="K43" t="inlineStr">
         <is>
           <t>A1 Garage (DDTL)</t>
@@ -3995,30 +4005,32 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>US Fertility (DDTL)</t>
+          <t>A1 Garage (DDTL)</t>
         </is>
       </c>
       <c r="M43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N43" t="b">
-        <v>0</v>
-      </c>
-      <c r="O43" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="O43" t="n">
+        <v>1</v>
+      </c>
       <c r="P43" t="n">
-        <v>0.7544</v>
+        <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>396.3347</v>
+        <v>1</v>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>TVC | US Fertility</t>
+          <t>A1 Garage</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>US Fertility (DDTL) | TVC (DDTL) | TVC (TL) | US Fertility (Term Loan) | Bland Landscaping (DDTL)</t>
+          <t>A1 Garage (DDTL)</t>
         </is>
       </c>
       <c r="T43" t="b">
@@ -4058,16 +4070,18 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>TVC</t>
+          <t>A1 Garage</t>
         </is>
       </c>
       <c r="H44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I44" t="b">
-        <v>0</v>
-      </c>
-      <c r="J44" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J44" t="n">
+        <v>1</v>
+      </c>
       <c r="K44" t="inlineStr">
         <is>
           <t>A1 Garage (Term Loan)</t>
@@ -4075,30 +4089,32 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>TVC (TL)</t>
+          <t>A1 Garage (Term Loan)</t>
         </is>
       </c>
       <c r="M44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N44" t="b">
-        <v>0</v>
-      </c>
-      <c r="O44" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="O44" t="n">
+        <v>1</v>
+      </c>
       <c r="P44" t="n">
-        <v>0.7544</v>
+        <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>294.2774</v>
+        <v>1</v>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>TVC | US Fertility</t>
+          <t>A1 Garage</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>TVC (TL) | US Fertility (Term Loan) | US Fertility (DDTL) | TVC (DDTL) | MeritDirect (Term Loan)</t>
+          <t>A1 Garage (Term Loan)</t>
         </is>
       </c>
       <c r="T44" t="b">
@@ -4164,16 +4180,16 @@
         <v>0</v>
       </c>
       <c r="N45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P45" t="n">
         <v>0.999</v>
       </c>
       <c r="Q45" t="n">
-        <v>591.8692</v>
+        <v>591.5267</v>
       </c>
       <c r="R45" t="inlineStr">
         <is>
@@ -4182,7 +4198,7 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>Aeronix (DDTL) | Aeronix (Common Equity) | AKW Holdings (Term Loan) | Aeronix (TL) | 4Wall Entertainment (Term Loan)</t>
+          <t>Aeronix (DDTL) | Aeronix (Common Equity) | AKW Holdings (Term Loan) | 4Wall Entertainment (Term Loan) | Dr. Scholl's (Term Loan)</t>
         </is>
       </c>
       <c r="T45" t="b">
@@ -4390,16 +4406,18 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Simplicity Group</t>
+          <t>Smartronix / Trident</t>
         </is>
       </c>
       <c r="H48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I48" t="b">
-        <v>0</v>
-      </c>
-      <c r="J48" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J48" t="n">
+        <v>1</v>
+      </c>
       <c r="K48" t="inlineStr">
         <is>
           <t>Smartronix / Trident (TL)</t>
@@ -4407,30 +4425,32 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>STV Group (TL)</t>
+          <t>Smartronix / Trident (TL)</t>
         </is>
       </c>
       <c r="M48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N48" t="b">
-        <v>0</v>
-      </c>
-      <c r="O48" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="O48" t="n">
+        <v>1</v>
+      </c>
       <c r="P48" t="n">
-        <v>0.5505</v>
+        <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>235.981</v>
+        <v>1</v>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>Simplicity Group | None | Case Works Group | Guild Garage Group | STV Group</t>
+          <t>Smartronix / Trident</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>STV Group (TL) | Simplicity Group (TL) | Case Works Group (Term Loan) | Guild Garage Group (Term Loan) | Simplicity Group (DDTL)</t>
+          <t>Smartronix / Trident (TL)</t>
         </is>
       </c>
       <c r="T48" t="b">
@@ -4589,7 +4609,7 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>672.4636</v>
+        <v>672.6747</v>
       </c>
       <c r="R50" t="inlineStr">
         <is>
@@ -5849,7 +5869,7 @@
         <v>1</v>
       </c>
       <c r="Q65" t="n">
-        <v>873.5107</v>
+        <v>875.8619</v>
       </c>
       <c r="R65" t="inlineStr">
         <is>
@@ -5858,7 +5878,7 @@
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>4Wall Entertainment (Revolver) | 4Wall Entertainment (Term Loan) | 4Wall Entertainment (DDTL) | ECL Entertainment (Term Loan) | Peninsula Pacific Entertainment (Term Loan B)</t>
+          <t>4Wall Entertainment (Revolver) | 4Wall Entertainment (Term Loan) | 4Wall Entertainment (DDTL)</t>
         </is>
       </c>
       <c r="T65" t="b">
@@ -5933,7 +5953,7 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>546.4172</v>
+        <v>547.049</v>
       </c>
       <c r="R66" t="inlineStr">
         <is>
@@ -6017,7 +6037,7 @@
         <v>1</v>
       </c>
       <c r="Q67" t="n">
-        <v>1005.7311</v>
+        <v>1008.9297</v>
       </c>
       <c r="R67" t="inlineStr">
         <is>
@@ -6101,7 +6121,7 @@
         <v>1</v>
       </c>
       <c r="Q68" t="n">
-        <v>1005.7311</v>
+        <v>1008.9297</v>
       </c>
       <c r="R68" t="inlineStr">
         <is>
@@ -6185,7 +6205,7 @@
         <v>1</v>
       </c>
       <c r="Q69" t="n">
-        <v>746.6063</v>
+        <v>748.769</v>
       </c>
       <c r="R69" t="inlineStr">
         <is>
@@ -6194,7 +6214,7 @@
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>Cano Health (Equity) | Cano Health (Term Loan) | Ro Health (Revolver) | Confluent Health (TL) | Ro Health (Term Loan)</t>
+          <t>Cano Health (Equity) | Centauri Health (TL) | Comprehensive Rehab Consultants (Revolver)</t>
         </is>
       </c>
       <c r="T69" t="b">
@@ -6353,7 +6373,7 @@
         <v>1</v>
       </c>
       <c r="Q71" t="n">
-        <v>949.814</v>
+        <v>952.9135</v>
       </c>
       <c r="R71" t="inlineStr">
         <is>
@@ -6434,10 +6454,10 @@
         <v>3</v>
       </c>
       <c r="P72" t="n">
-        <v>0.9471000000000001</v>
+        <v>0.9472</v>
       </c>
       <c r="Q72" t="n">
-        <v>524.371</v>
+        <v>525.5556</v>
       </c>
       <c r="R72" t="inlineStr">
         <is>
@@ -7100,13 +7120,13 @@
         <v>0</v>
       </c>
       <c r="N80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O80" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P80" t="n">
-        <v>0.9499</v>
+        <v>1</v>
       </c>
       <c r="Q80" t="n">
         <v>382.3594</v>
@@ -7118,7 +7138,7 @@
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>Sparq (TL) | Watterson (Revolver) | Dr. Scholl's (Revolver) | AKW Holdings (Term Loan) | AKW Holdings (Common)</t>
+          <t>Sparq (TL) | Watterson (Revolver) | Dr. Scholl's (Revolver) | Sparq (Revolver) | Sparq (Common Equity)</t>
         </is>
       </c>
       <c r="T80" t="b">
@@ -8512,14 +8532,14 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -8695,47 +8715,47 @@
         <v>31</v>
       </c>
       <c r="C6" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>90.3%</t>
+          <t>96.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
+        <v>30</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>96.8%</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>27</v>
+      </c>
+      <c r="J6" t="n">
+        <v>4</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>87.1%</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
         <v>29</v>
       </c>
-      <c r="G6" t="n">
+      <c r="M6" t="n">
         <v>2</v>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>93.5%</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>25</v>
-      </c>
-      <c r="J6" t="n">
-        <v>6</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>80.6%</t>
-        </is>
-      </c>
-      <c r="L6" t="n">
-        <v>27</v>
-      </c>
-      <c r="M6" t="n">
-        <v>4</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>87.1%</t>
         </is>
       </c>
     </row>
@@ -8749,47 +8769,47 @@
         <v>18</v>
       </c>
       <c r="C7" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="J7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="M7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>94.4%</t>
         </is>
       </c>
     </row>

--- a/evaluation_results.xlsx
+++ b/evaluation_results.xlsx
@@ -540,11 +540,7 @@
           <t>Events Buyer T/L</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>events buyer</t>
-        </is>
-      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>360DG</t>
@@ -624,11 +620,7 @@
           <t>48Forty Intermediate Holdings C/S</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>48forty intermediate holdings</t>
-        </is>
-      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>48Forty</t>
@@ -708,11 +700,7 @@
           <t>Ad.net Acquisition T/L</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>ad net acquisition</t>
-        </is>
-      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>Ad.net</t>
@@ -792,11 +780,7 @@
           <t>Aechelon Technology  T/L</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>aechelon technology</t>
-        </is>
-      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>Aechelon</t>
@@ -876,11 +860,7 @@
           <t>AFC-Dell Holding DD T/L (12/23)</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>afc dell holding</t>
-        </is>
-      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>AFC Acquisitions</t>
@@ -960,11 +940,7 @@
           <t>AFC-Dell Holding T/L</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>afc dell holding</t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>AFC Acquisitions</t>
@@ -1044,11 +1020,7 @@
           <t>Burgess Point Purchaser Corporation (BBB)  T/L (06/22)</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>burgess point purchaser corporation</t>
-        </is>
-      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>BBB Industries</t>
@@ -1128,11 +1100,7 @@
           <t>BLC Holding Company DD T/L</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>blc holding</t>
-        </is>
-      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>Bland Landscaping</t>
@@ -1212,11 +1180,7 @@
           <t>Bluebird Group T/L</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>bluebird group the</t>
-        </is>
-      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>Bluebird</t>
@@ -1296,11 +1260,7 @@
           <t>Aegis Technologies Group (BlueHalo) 4th Amend T/L</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>aegis technologies group the</t>
-        </is>
-      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>BlueHalo</t>
@@ -1380,11 +1340,7 @@
           <t>BlueHalo Global (Aegis) T/L 4th Amend  **DUPLICATE - PLEASE USE BL0623316**</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>bluehalo global holdings</t>
-        </is>
-      </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>BlueHalo</t>
@@ -1464,11 +1420,7 @@
           <t>By Light Professional R/C 2</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>by light professional it services</t>
-        </is>
-      </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>By Light</t>
@@ -1589,13 +1541,13 @@
         <v>1</v>
       </c>
       <c r="O14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P14" t="n">
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>345.8854</v>
+        <v>0.9141060695160412</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
@@ -1604,7 +1556,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>Centauri Health (TL) | Watchtower Buyer (Revolver) | Centauri Health (Revolver) | Centauri Health (DDTL) | Centauri Health (Equity)</t>
+          <t>Centauri Health (TL) | Centauri Health (Revolver) | Centauri Health (DDTL) | Centauri Health (Equity)</t>
         </is>
       </c>
       <c r="T14" t="b">
@@ -1632,11 +1584,7 @@
           <t>Dr. Squatch T/L</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>dr squatch</t>
-        </is>
-      </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>Dr. Squatch</t>
@@ -1716,11 +1664,7 @@
           <t>GGG Midco DD T/L</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>ggg midco</t>
-        </is>
-      </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>Guild Garage Group</t>
@@ -1800,11 +1744,7 @@
           <t>Infinity Home Services Holdco Amend. 1 DD T/L</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>infinity home services holdco</t>
-        </is>
-      </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>Infinity Home Services</t>
@@ -1884,11 +1824,7 @@
           <t>Lash Opco Restatement T/L--MC178414</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>lash opco</t>
-        </is>
-      </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
           <t>Lilly Lashes</t>
@@ -1968,11 +1904,7 @@
           <t>OSP Embedded Purchaser Incremental T/L (11/24)</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>osp embedded purchaser</t>
-        </is>
-      </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
           <t>Lynx Technologies</t>
@@ -2052,11 +1984,7 @@
           <t>Anteriad (MeritDirect) Incremental T/L B</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>anteriad</t>
-        </is>
-      </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>MeritDirect</t>
@@ -2136,11 +2064,7 @@
           <t>MeritDirect T/L A (MeritB2B/Anteriad)</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>meritdirect</t>
-        </is>
-      </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>MeritDirect</t>
@@ -2267,7 +2191,7 @@
         <v>0.8538</v>
       </c>
       <c r="Q22" t="n">
-        <v>87.51949999999999</v>
+        <v>0.7006573962868813</v>
       </c>
       <c r="R22" t="inlineStr">
         <is>
@@ -2304,11 +2228,7 @@
           <t>Pragmatic Institute C/S (03/25)</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>pragmatic institute</t>
-        </is>
-      </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>Pragmatic Institute</t>
@@ -2388,11 +2308,7 @@
           <t>Paving Lessor Initial T/L</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>paving lessor</t>
-        </is>
-      </c>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>C&amp;K Paving Contractors</t>
@@ -2472,11 +2388,7 @@
           <t>Lightspeed Buyer T/L</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>lightspeed buyer</t>
-        </is>
-      </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>Centauri Health</t>
@@ -2496,19 +2408,25 @@
       <c r="J25" t="n">
         <v>1</v>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Centauri Health (TL)</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>Centauri Health (TL)</t>
         </is>
       </c>
       <c r="M25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N25" t="b">
-        <v>0</v>
-      </c>
-      <c r="O25" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1</v>
+      </c>
       <c r="P25" t="n">
         <v>1</v>
       </c>
@@ -2550,11 +2468,7 @@
           <t>NFS - CFP Holdings Incremental T/L</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>nfs cfp holdings</t>
-        </is>
-      </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
           <t>Commercial Fire Protection</t>
@@ -2634,11 +2548,7 @@
           <t>DRS Holdings III Amendment No. 4 Incremental T/L</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>drs holdings iii</t>
-        </is>
-      </c>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
           <t>Dr. Scholl's</t>
@@ -2718,11 +2628,7 @@
           <t>Arcline FM Holdings T/L (7/24) (Fairbanks Morse) - Target</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>arcline fm holdings</t>
-        </is>
-      </c>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
           <t>Fairbanks Morse Defense</t>
@@ -2802,11 +2708,7 @@
           <t>Management Consulting &amp; Research T/L (Systems Planning and Analysis)</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>management consulting research</t>
-        </is>
-      </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
           <t>MCR</t>
@@ -2929,7 +2831,7 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>434.7123</v>
+        <v>0.9497369696524071</v>
       </c>
       <c r="R30" t="inlineStr">
         <is>
@@ -2938,7 +2840,7 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>PlayPower (Term Loan) | Bluebird (Term Loan) | BlueHalo (Term Loan) | Aechelon (Term Loan) | 360DG (Term Loan)</t>
+          <t>PlayPower (Term Loan)</t>
         </is>
       </c>
       <c r="T30" t="b">
@@ -2966,11 +2868,7 @@
           <t>PlayPower T/L (08/24)</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>playpower</t>
-        </is>
-      </c>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
           <t>PlayPower</t>
@@ -3050,11 +2948,7 @@
           <t>The Track Branson Opco DDTL</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>the track branson opco</t>
-        </is>
-      </c>
+      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
           <t>The Creative Group</t>
@@ -3134,11 +3028,7 @@
           <t>Sath Industries LLC Delayed Draw Term Loan (360DG)</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>sath industries</t>
-        </is>
-      </c>
+      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
           <t>360DG</t>
@@ -3218,11 +3108,7 @@
           <t>48Forty Intermediate Holdings Inc Common Equity</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>48forty intermediate holdings</t>
-        </is>
-      </c>
+      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
           <t>48Forty</t>
@@ -3302,11 +3188,7 @@
           <t>LAV Gear Holdings Inc Fourteenth Amendment Priority Term Loan</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>lav gear holdings</t>
-        </is>
-      </c>
+      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
           <t>4Wall Entertainment</t>
@@ -3386,11 +3268,7 @@
           <t>Burgess Point Purchaser Corporation Initial Term Loan</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>burgess point purchaser corporation</t>
-        </is>
-      </c>
+      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
           <t>BBB Industries</t>
@@ -3470,11 +3348,7 @@
           <t>Big Top Holdings LLC Term Loan</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>big top holdings</t>
-        </is>
-      </c>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
           <t>Big Top Manufacturing</t>
@@ -3554,11 +3428,7 @@
           <t>BlueHalo Global Holdings LLC Initial Term Loan</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>bluehalo global holdings</t>
-        </is>
-      </c>
+      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
           <t>BlueHalo</t>
@@ -3638,11 +3508,7 @@
           <t>ACP Falcon Buyer Inc Initial Term Loan</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>acp falcon buyer</t>
-        </is>
-      </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
           <t>Integrated Data Services</t>
@@ -3722,11 +3588,7 @@
           <t>Kinetic Purchaser LLC Closing Date Term Loan</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>kinetic purchaser</t>
-        </is>
-      </c>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
           <t>KNS</t>
@@ -3806,11 +3668,7 @@
           <t>Radius Aerospace Inc UK Term Loan</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>radius aerospace</t>
-        </is>
-      </c>
+      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
           <t>Radius Aerospace</t>
@@ -3890,11 +3748,7 @@
           <t>RRA Corporate LLC Initial Term Loan</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>rra corporate</t>
-        </is>
-      </c>
+      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
           <t>Roofed Right America</t>
@@ -3974,11 +3828,7 @@
           <t>TMII Enterprises LLC DDTL</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>tmii enterprises</t>
-        </is>
-      </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
           <t>A1 Garage</t>
@@ -4058,11 +3908,7 @@
           <t>TMII Enterprises LLC Term Loan A</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>tmii enterprises</t>
-        </is>
-      </c>
+      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
           <t>A1 Garage</t>
@@ -4180,16 +4026,16 @@
         <v>0</v>
       </c>
       <c r="N45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O45" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P45" t="n">
         <v>0.999</v>
       </c>
       <c r="Q45" t="n">
-        <v>591.5267</v>
+        <v>0.9977809191868882</v>
       </c>
       <c r="R45" t="inlineStr">
         <is>
@@ -4198,7 +4044,7 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>Aeronix (DDTL) | Aeronix (Common Equity) | AKW Holdings (Term Loan) | 4Wall Entertainment (Term Loan) | Dr. Scholl's (Term Loan)</t>
+          <t>Aeronix (DDTL) | Aeronix (Common Equity) | AKW Holdings (Term Loan) | Aeronix (TL) | AKW Holdings (Common)</t>
         </is>
       </c>
       <c r="T45" t="b">
@@ -4226,11 +4072,7 @@
           <t>DRS Holdings III Inc 3/25 Term Loan</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>drs holdings iii</t>
-        </is>
-      </c>
+      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
           <t>Dr. Scholl's</t>
@@ -4310,11 +4152,7 @@
           <t>Systems Planning and Analysis Inc Delayed Draw Term Loan A</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>systems planning and analysis</t>
-        </is>
-      </c>
+      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
           <t>MCR</t>
@@ -4394,11 +4232,7 @@
           <t>SMX Group LLC Term Loan (Smartronix/Trident)</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>smx group</t>
-        </is>
-      </c>
+      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
           <t>Smartronix / Trident</t>
@@ -4478,11 +4312,7 @@
           <t>STG Distribution LLC First Out New Money Term Loan</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>stg distribution</t>
-        </is>
-      </c>
+      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
           <t>STG Logistics</t>
@@ -4609,7 +4439,7 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>672.6747</v>
+        <v>1</v>
       </c>
       <c r="R50" t="inlineStr">
         <is>
@@ -4646,11 +4476,7 @@
           <t>LAV Gear Holdings, Inc. First Lien - Term Loan - 12th Amend. - Priority FOTL</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>lav gear holdings</t>
-        </is>
-      </c>
+      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
           <t>4Wall Entertainment</t>
@@ -4730,11 +4556,7 @@
           <t>A1 Garage Equity, LLC Common Equity</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>a1 garage equity</t>
-        </is>
-      </c>
+      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
           <t>A1 Garage</t>
@@ -4814,11 +4636,7 @@
           <t>Archer Lewis, LLC First Lien - Revolver - Revolver</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>archer lewis</t>
-        </is>
-      </c>
+      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
           <t>Archer Lewis</t>
@@ -4898,11 +4716,7 @@
           <t>Beta Plus Technologies, Inc. Initial Term Loan</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>beta plus technologies</t>
-        </is>
-      </c>
+      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
           <t>Beta+</t>
@@ -4982,11 +4796,7 @@
           <t>Rural Sourcing Holdings, Inc. Amendment No. 1 Incremental Term Loans</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>rural sourcing holdings</t>
-        </is>
-      </c>
+      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
           <t>Sparq</t>
@@ -5066,11 +4876,7 @@
           <t>TCG 3.0 Jogger Acquisitionco, Inc. First Lien - Revolver - Revolver</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>tcg 3 0 jogger acquisitionco</t>
-        </is>
-      </c>
+      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
           <t>BiggerPockets</t>
@@ -5150,11 +4956,7 @@
           <t>Carnegie Dartlet, LLC First Lien - DDTL - DDTL</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>carnegie dartlet</t>
-        </is>
-      </c>
+      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
           <t>Carnegie Dartlet</t>
@@ -5234,11 +5036,7 @@
           <t>Medina Health, LLC Revolving Loan</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>medina health</t>
-        </is>
-      </c>
+      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
           <t>Comprehensive Rehab Consultants</t>
@@ -5318,11 +5116,7 @@
           <t>GAUGE ETE BLOCKER LLC Common Equity</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>gauge ete blocker</t>
-        </is>
-      </c>
+      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
           <t>Engine &amp; Transmission Exchange</t>
@@ -5402,11 +5196,7 @@
           <t>EDS TOPCO, LP Common Equity</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>eds topco</t>
-        </is>
-      </c>
+      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
           <t>Epiq</t>
@@ -5486,11 +5276,7 @@
           <t>ENC Parent Corporation Initial Term Loan (First Lien)</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>enc parent corporation</t>
-        </is>
-      </c>
+      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
           <t>Evans Network</t>
@@ -5570,11 +5356,7 @@
           <t>Best Practice Associates, LLC First Lien - Term Loan</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>best practice associates</t>
-        </is>
-      </c>
+      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
           <t>Federal Advisory Partners</t>
@@ -5654,11 +5436,7 @@
           <t>Infinity Home Services Holdco, Inc. Revolving Loan</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>infinity home services holdco</t>
-        </is>
-      </c>
+      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
           <t>Infinity Home Services</t>
@@ -5785,7 +5563,7 @@
         <v>0.9834000000000001</v>
       </c>
       <c r="Q64" t="n">
-        <v>484.679</v>
+        <v>0.9667040928729312</v>
       </c>
       <c r="R64" t="inlineStr">
         <is>
@@ -5869,7 +5647,7 @@
         <v>1</v>
       </c>
       <c r="Q65" t="n">
-        <v>875.8619</v>
+        <v>1</v>
       </c>
       <c r="R65" t="inlineStr">
         <is>
@@ -5953,7 +5731,7 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>547.049</v>
+        <v>0.9855858611976858</v>
       </c>
       <c r="R66" t="inlineStr">
         <is>
@@ -6037,7 +5815,7 @@
         <v>1</v>
       </c>
       <c r="Q67" t="n">
-        <v>1008.9297</v>
+        <v>1</v>
       </c>
       <c r="R67" t="inlineStr">
         <is>
@@ -6121,7 +5899,7 @@
         <v>1</v>
       </c>
       <c r="Q68" t="n">
-        <v>1008.9297</v>
+        <v>1</v>
       </c>
       <c r="R68" t="inlineStr">
         <is>
@@ -6205,7 +5983,7 @@
         <v>1</v>
       </c>
       <c r="Q69" t="n">
-        <v>748.769</v>
+        <v>1</v>
       </c>
       <c r="R69" t="inlineStr">
         <is>
@@ -6214,7 +5992,7 @@
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>Cano Health (Equity) | Centauri Health (TL) | Comprehensive Rehab Consultants (Revolver)</t>
+          <t>Cano Health (Equity)</t>
         </is>
       </c>
       <c r="T69" t="b">
@@ -6242,11 +6020,7 @@
           <t>Dr. Scholl's</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>dr scholls</t>
-        </is>
-      </c>
+      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
           <t>Dr. Scholl's</t>
@@ -6373,7 +6147,7 @@
         <v>1</v>
       </c>
       <c r="Q71" t="n">
-        <v>952.9135</v>
+        <v>1</v>
       </c>
       <c r="R71" t="inlineStr">
         <is>
@@ -6457,7 +6231,7 @@
         <v>0.9472</v>
       </c>
       <c r="Q72" t="n">
-        <v>525.5556</v>
+        <v>0.9793332744374675</v>
       </c>
       <c r="R72" t="inlineStr">
         <is>
@@ -6494,11 +6268,7 @@
           <t>Recteq</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>recteq</t>
-        </is>
-      </c>
+      <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
           <t>Recteq</t>
@@ -6578,11 +6348,7 @@
           <t>HV Watterson Holdings, LLC - Unfunded Revolver</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>hv watterson holdings</t>
-        </is>
-      </c>
+      <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
           <t>Watterson</t>
@@ -6662,11 +6428,7 @@
           <t>Watchtower Buyer, LLC - Unfunded Revolver</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>watchtower buyer</t>
-        </is>
-      </c>
+      <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
           <t>Watchtower Buyer</t>
@@ -6746,11 +6508,7 @@
           <t>Univista Insurance - Common Equity</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>univista insurance</t>
-        </is>
-      </c>
+      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
           <t>UniVista</t>
@@ -6830,11 +6588,7 @@
           <t>Project Granite Buyer, Inc. - Unfunded Term Loan</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>project granite buyer</t>
-        </is>
-      </c>
+      <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
           <t>Tranzact</t>
@@ -6914,11 +6668,7 @@
           <t>Aftermarket Drivetrain Products Holdings, LLC - Common Equity</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>transgo</t>
-        </is>
-      </c>
+      <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
           <t>TransGo</t>
@@ -6998,11 +6748,7 @@
           <t>STG Distribution, LLC - Second Out Term Loans</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>stg distribution</t>
-        </is>
-      </c>
+      <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
           <t>STG Logistics</t>
@@ -7123,13 +6869,13 @@
         <v>1</v>
       </c>
       <c r="O80" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P80" t="n">
         <v>1</v>
       </c>
       <c r="Q80" t="n">
-        <v>382.3594</v>
+        <v>0.9297311349197671</v>
       </c>
       <c r="R80" t="inlineStr">
         <is>
@@ -7138,7 +6884,7 @@
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>Sparq (TL) | Watterson (Revolver) | Dr. Scholl's (Revolver) | Sparq (Revolver) | Sparq (Common Equity)</t>
+          <t>Sparq (TL) | Sparq (Revolver) | Sparq (Common Equity) | Sparq (DDTL)</t>
         </is>
       </c>
       <c r="T80" t="b">
@@ -7166,11 +6912,7 @@
           <t>Gauge Schlesinger Coinvest, LLC - Common Equity</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>schlesinger global</t>
-        </is>
-      </c>
+      <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
           <t>Schlesinger</t>
@@ -7250,11 +6992,7 @@
           <t>Pacific Purchaser, LLC - Unfunded Revolver</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>pacific purchaser</t>
-        </is>
-      </c>
+      <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
           <t>ProSearch</t>
@@ -7334,11 +7072,7 @@
           <t>Aechelon InvestCo, LP - Common Equity</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>aechelon investco common equity</t>
-        </is>
-      </c>
+      <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
           <t>Aechelon</t>
@@ -7418,11 +7152,7 @@
           <t>TCG 3.0 Jogger Co-Invest, LP - Common Equity</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>tcg 3 0 jogger invest common equity</t>
-        </is>
-      </c>
+      <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
           <t>BiggerPockets</t>
@@ -7502,11 +7232,7 @@
           <t>Knexus Holdco, LLC - Preferred Equity</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>knexus holdco preferred equity</t>
-        </is>
-      </c>
+      <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
           <t>C5MI</t>
@@ -7586,11 +7312,7 @@
           <t>Connatix Parent, LLC - Common Equity</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>connatix parent common equity</t>
-        </is>
-      </c>
+      <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
           <t>Connatix</t>
@@ -7670,11 +7392,7 @@
           <t>Connatix Parent, LLC - Preferred Equity</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>connatix parent preferred equity</t>
-        </is>
-      </c>
+      <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
           <t>Connatix</t>
@@ -7754,11 +7472,7 @@
           <t>RFMG Parent, LP - Common Equity</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>rfmg parent common equity</t>
-        </is>
-      </c>
+      <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
           <t>Rancho Medical</t>
@@ -7838,11 +7552,7 @@
           <t>Project Granite Holdings, LLC - Common Equity</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>project granite holdings common equity</t>
-        </is>
-      </c>
+      <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
           <t>Tranzact</t>
@@ -7922,11 +7632,7 @@
           <t>NXOF Holdings, Inc. - Common Equity</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>nxof holdings common equity</t>
-        </is>
-      </c>
+      <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
           <t>Tyto Athene</t>
@@ -8006,11 +7712,7 @@
           <t>NXOF Holdings, Inc. - Preferred Equity</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>nxof holdings preferred equity</t>
-        </is>
-      </c>
+      <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
           <t>Tyto Athene</t>
@@ -8090,11 +7792,7 @@
           <t>TWD Parent Holdings, LLC - Common Equity</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>twd parent holdings common equity</t>
-        </is>
-      </c>
+      <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
           <t>Vertex</t>
@@ -8174,11 +7872,7 @@
           <t>TWD Parent Holdings, LLC - Preferred Equity</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>twd parent holdings preferred equity</t>
-        </is>
-      </c>
+      <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
           <t>Vertex</t>
@@ -8258,14 +7952,10 @@
           <t>Watchtower Holdings, LLC - Common Equity</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>watchtower holdings common equity</t>
-        </is>
-      </c>
+      <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Watchtower</t>
+          <t>Watchtower Holdings</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -8274,12 +7964,14 @@
         </is>
       </c>
       <c r="H94" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I94" t="b">
-        <v>0</v>
-      </c>
-      <c r="J94" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J94" t="n">
+        <v>1</v>
+      </c>
       <c r="K94" t="inlineStr">
         <is>
           <t>Watchtower Holding (Common Equity)</t>
@@ -8340,11 +8032,7 @@
           <t>HV Watterson Holdings, LLC - Common Equity</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>hv watterson holdings common equity</t>
-        </is>
-      </c>
+      <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr">
         <is>
           <t>Watterson</t>
@@ -8553,25 +8241,25 @@
         <v>13</v>
       </c>
       <c r="C3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>92.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>92.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -8737,25 +8425,25 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>87.1%</t>
+          <t>90.3%</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>93.5%</t>
+          <t>96.8%</t>
         </is>
       </c>
     </row>
@@ -8802,14 +8490,14 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>94.4%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>

--- a/evaluation_results.xlsx
+++ b/evaluation_results.xlsx
@@ -1500,11 +1500,7 @@
           <t>Lightspeed Buyer VT1 R/C</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>lightspeed buyer</t>
-        </is>
-      </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>Centauri Health</t>
@@ -2144,11 +2140,7 @@
           <t>OSG Topco Holdings LLC - Class A Unit</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>osg topco holdings class a unit</t>
-        </is>
-      </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
           <t>OSG Billing Services</t>
@@ -2156,11 +2148,11 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>OSG Billing Services</t>
+          <t>U.S. Well</t>
         </is>
       </c>
       <c r="H22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I22" t="b">
         <v>1</v>
@@ -2188,7 +2180,7 @@
         <v>5</v>
       </c>
       <c r="P22" t="n">
-        <v>0.8538</v>
+        <v>0.6781</v>
       </c>
       <c r="Q22" t="n">
         <v>0.7006573962868813</v>
@@ -2788,11 +2780,7 @@
           <t>PlayPower T/L (5/19)</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>playpower</t>
-        </is>
-      </c>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
           <t>Planview</t>
@@ -3988,11 +3976,7 @@
           <t>SV-Aero Holdings LLC Term Loan</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>sv aero holdings</t>
-        </is>
-      </c>
+      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
           <t>Aeronix</t>
@@ -4392,11 +4376,7 @@
           <t>Zips Car Wash LLC Roll Up Term Loan</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>zips car wash</t>
-        </is>
-      </c>
+      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
           <t>Zips</t>
@@ -5516,11 +5496,7 @@
           <t>MidOcean JF Holdings Corp. 5th Amendment Term Loan</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>midocean jf holdings</t>
-        </is>
-      </c>
+      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
           <t>Jones &amp; Frank</t>
@@ -5600,11 +5576,7 @@
           <t>4Wall Entertainment</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>4wall entertainment</t>
-        </is>
-      </c>
+      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
           <t>4Wall Entertainment</t>
@@ -5684,11 +5656,7 @@
           <t>Aeronix</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>aeronix</t>
-        </is>
-      </c>
+      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
           <t>Aeronix</t>
@@ -5768,11 +5736,7 @@
           <t>Any Hour Services</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>any hour services</t>
-        </is>
-      </c>
+      <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
           <t>Any Hour Services</t>
@@ -5852,11 +5816,7 @@
           <t>Any Hour Services</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>any hour services</t>
-        </is>
-      </c>
+      <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
           <t>Any Hour Services</t>
@@ -5936,11 +5896,7 @@
           <t>Cano Health</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>cano health</t>
-        </is>
-      </c>
+      <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
           <t>Cano Health</t>
@@ -6100,11 +6056,7 @@
           <t>Infinity Home Services</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>infinity home services</t>
-        </is>
-      </c>
+      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
           <t>Infinity Home Services</t>
@@ -6184,11 +6136,7 @@
           <t>KNS</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>kns</t>
-        </is>
-      </c>
+      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
           <t>KNS</t>
@@ -6828,11 +6776,7 @@
           <t>Rural Sourcing Holdings, Inc. - Unfunded Revolver</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>rural sourcing holdings</t>
-        </is>
-      </c>
+      <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
           <t>Sparq</t>
@@ -8403,14 +8347,14 @@
         <v>31</v>
       </c>
       <c r="C6" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>96.8%</t>
+          <t>93.5%</t>
         </is>
       </c>
       <c r="F6" t="n">
